--- a/data/processed/scores_LQdFPC_vs_dFPC.xlsx
+++ b/data/processed/scores_LQdFPC_vs_dFPC.xlsx
@@ -442,10 +442,10 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>1.958356685614624</v>
+        <v>-2.006633394345457</v>
       </c>
       <c r="C2" t="n">
-        <v>265.5377972643317</v>
+        <v>-328.6022003258042</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8035913285283833</v>
+        <v>-1.69863111722018</v>
       </c>
       <c r="C3" t="n">
-        <v>67.92977126047096</v>
+        <v>-97.69839097279157</v>
       </c>
     </row>
     <row r="4">
@@ -464,10 +464,10 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4005464238988992</v>
+        <v>0.7504726312310206</v>
       </c>
       <c r="C4" t="n">
-        <v>91.00712612915758</v>
+        <v>-80.09310097907786</v>
       </c>
     </row>
     <row r="5">
@@ -475,10 +475,10 @@
         <v>45631</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.185181118257078</v>
+        <v>2.214950382811713</v>
       </c>
       <c r="C5" t="n">
-        <v>-72.35894784377523</v>
+        <v>146.7734941673269</v>
       </c>
     </row>
     <row r="6">
@@ -486,10 +486,10 @@
         <v>45632</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.7367513148878663</v>
+        <v>1.975190185627391</v>
       </c>
       <c r="C6" t="n">
-        <v>-60.47619139456452</v>
+        <v>93.86544482765854</v>
       </c>
     </row>
     <row r="7">
@@ -497,10 +497,10 @@
         <v>45635</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7004580098479121</v>
+        <v>-1.115379130520231</v>
       </c>
       <c r="C7" t="n">
-        <v>92.84415206275897</v>
+        <v>-109.035078892553</v>
       </c>
     </row>
     <row r="8">
@@ -508,10 +508,10 @@
         <v>45636</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.8067881154811281</v>
+        <v>1.806403463695434</v>
       </c>
       <c r="C8" t="n">
-        <v>-51.48644251551049</v>
+        <v>108.3259000436015</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +519,10 @@
         <v>45637</v>
       </c>
       <c r="B9" t="n">
-        <v>3.788000104728074</v>
+        <v>-10.17432154652104</v>
       </c>
       <c r="C9" t="n">
-        <v>288.8134749065307</v>
+        <v>-541.3536573989444</v>
       </c>
     </row>
     <row r="10">
@@ -530,10 +530,10 @@
         <v>45638</v>
       </c>
       <c r="B10" t="n">
-        <v>1.137669721888422</v>
+        <v>-2.531870838538045</v>
       </c>
       <c r="C10" t="n">
-        <v>165.4061565258836</v>
+        <v>-224.0278382636907</v>
       </c>
     </row>
     <row r="11">
@@ -541,10 +541,10 @@
         <v>45639</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.8384009375313284</v>
+        <v>2.258735389985342</v>
       </c>
       <c r="C11" t="n">
-        <v>-50.71341128013967</v>
+        <v>108.3352450268928</v>
       </c>
     </row>
     <row r="12">
@@ -552,10 +552,10 @@
         <v>45642</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.9591562543131644</v>
+        <v>2.622930471071168</v>
       </c>
       <c r="C12" t="n">
-        <v>-58.73877673677941</v>
+        <v>126.265807067926</v>
       </c>
     </row>
     <row r="13">
@@ -563,10 +563,10 @@
         <v>45643</v>
       </c>
       <c r="B13" t="n">
-        <v>3.675703199664823</v>
+        <v>-6.211999923070231</v>
       </c>
       <c r="C13" t="n">
-        <v>309.6653453882263</v>
+        <v>-521.7983519036489</v>
       </c>
     </row>
     <row r="14">
@@ -574,10 +574,10 @@
         <v>45644</v>
       </c>
       <c r="B14" t="n">
-        <v>2.704141645799291</v>
+        <v>-4.252572568769071</v>
       </c>
       <c r="C14" t="n">
-        <v>314.5110639517496</v>
+        <v>-467.5759632629653</v>
       </c>
     </row>
     <row r="15">
@@ -585,10 +585,10 @@
         <v>45645</v>
       </c>
       <c r="B15" t="n">
-        <v>1.59293920888317</v>
+        <v>-2.595676141199938</v>
       </c>
       <c r="C15" t="n">
-        <v>139.8752567973716</v>
+        <v>-216.4845225195966</v>
       </c>
     </row>
     <row r="16">
@@ -596,10 +596,10 @@
         <v>45646</v>
       </c>
       <c r="B16" t="n">
-        <v>1.66705829757284</v>
+        <v>-2.721747771055405</v>
       </c>
       <c r="C16" t="n">
-        <v>120.2418624606921</v>
+        <v>-210.8981452347402</v>
       </c>
     </row>
     <row r="17">
@@ -607,10 +607,10 @@
         <v>45649</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.5153538982007982</v>
+        <v>1.143240353202331</v>
       </c>
       <c r="C17" t="n">
-        <v>-44.3319314362886</v>
+        <v>85.36558777659761</v>
       </c>
     </row>
     <row r="18">
@@ -618,10 +618,10 @@
         <v>45652</v>
       </c>
       <c r="B18" t="n">
-        <v>0.156434201446434</v>
+        <v>0.5154314617883302</v>
       </c>
       <c r="C18" t="n">
-        <v>7.02826828157928</v>
+        <v>-15.11334747364093</v>
       </c>
     </row>
     <row r="19">
@@ -629,10 +629,10 @@
         <v>45653</v>
       </c>
       <c r="B19" t="n">
-        <v>1.682689372286276</v>
+        <v>-1.931358322290735</v>
       </c>
       <c r="C19" t="n">
-        <v>238.7034675482045</v>
+        <v>-291.123933355711</v>
       </c>
     </row>
     <row r="20">
@@ -640,10 +640,10 @@
         <v>45656</v>
       </c>
       <c r="B20" t="n">
-        <v>0.3182446870078257</v>
+        <v>0.9745828131046468</v>
       </c>
       <c r="C20" t="n">
-        <v>125.8992708073008</v>
+        <v>-99.28423357764348</v>
       </c>
     </row>
     <row r="21">
@@ -651,10 +651,10 @@
         <v>45659</v>
       </c>
       <c r="B21" t="n">
-        <v>2.261644982756497</v>
+        <v>-4.030494608216963</v>
       </c>
       <c r="C21" t="n">
-        <v>227.1405970047398</v>
+        <v>-333.4453080102134</v>
       </c>
     </row>
     <row r="22">
@@ -662,10 +662,10 @@
         <v>45660</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.2762625561798449</v>
+        <v>-0.05661025446422672</v>
       </c>
       <c r="C22" t="n">
-        <v>-30.64517587025007</v>
+        <v>40.66243161741001</v>
       </c>
     </row>
     <row r="23">
@@ -673,10 +673,10 @@
         <v>45663</v>
       </c>
       <c r="B23" t="n">
-        <v>1.998867383387668</v>
+        <v>-4.932690479768279</v>
       </c>
       <c r="C23" t="n">
-        <v>170.5405145352503</v>
+        <v>-276.3264758777318</v>
       </c>
     </row>
     <row r="24">
@@ -684,10 +684,10 @@
         <v>45664</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.1843844519801889</v>
+        <v>0.7915936178563658</v>
       </c>
       <c r="C24" t="n">
-        <v>-39.4899882721144</v>
+        <v>50.06755228476621</v>
       </c>
     </row>
     <row r="25">
@@ -695,10 +695,10 @@
         <v>45665</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.5386955220853565</v>
+        <v>1.101268170514453</v>
       </c>
       <c r="C25" t="n">
-        <v>-48.13197451649904</v>
+        <v>67.94351646475478</v>
       </c>
     </row>
     <row r="26">
@@ -706,10 +706,10 @@
         <v>45666</v>
       </c>
       <c r="B26" t="n">
-        <v>-2.094832664640359</v>
+        <v>4.56079544404723</v>
       </c>
       <c r="C26" t="n">
-        <v>-183.6024318025087</v>
+        <v>300.243849493477</v>
       </c>
     </row>
     <row r="27">
@@ -717,10 +717,10 @@
         <v>45667</v>
       </c>
       <c r="B27" t="n">
-        <v>1.099618410702528</v>
+        <v>-2.659115716978549</v>
       </c>
       <c r="C27" t="n">
-        <v>96.76648727192696</v>
+        <v>-145.2523986192917</v>
       </c>
     </row>
     <row r="28">
@@ -728,10 +728,10 @@
         <v>45670</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.4668832185390526</v>
+        <v>1.290384880384979</v>
       </c>
       <c r="C28" t="n">
-        <v>-53.75552018946463</v>
+        <v>87.79410782460741</v>
       </c>
     </row>
     <row r="29">
@@ -739,10 +739,10 @@
         <v>45671</v>
       </c>
       <c r="B29" t="n">
-        <v>2.441780347415474</v>
+        <v>-4.944617096165411</v>
       </c>
       <c r="C29" t="n">
-        <v>222.3305392275938</v>
+        <v>-347.7932960828746</v>
       </c>
     </row>
     <row r="30">
@@ -750,10 +750,10 @@
         <v>45672</v>
       </c>
       <c r="B30" t="n">
-        <v>1.096850836250794</v>
+        <v>-2.662382922769793</v>
       </c>
       <c r="C30" t="n">
-        <v>108.5143019038077</v>
+        <v>-174.0164363969481</v>
       </c>
     </row>
     <row r="31">
@@ -761,10 +761,10 @@
         <v>45673</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.7624912783059458</v>
+        <v>2.353367519817517</v>
       </c>
       <c r="C31" t="n">
-        <v>-23.47477483386983</v>
+        <v>77.3691809374192</v>
       </c>
     </row>
     <row r="32">
@@ -772,10 +772,10 @@
         <v>45674</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.793183072740931</v>
+        <v>1.782504896803305</v>
       </c>
       <c r="C32" t="n">
-        <v>-57.89062936855147</v>
+        <v>102.5210588480534</v>
       </c>
     </row>
     <row r="33">
@@ -783,10 +783,10 @@
         <v>45677</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3239106212613694</v>
+        <v>0.2234111220570207</v>
       </c>
       <c r="C33" t="n">
-        <v>89.91630718849581</v>
+        <v>-81.1229799598413</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         <v>45678</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.3751591033773422</v>
+        <v>1.775756747283255</v>
       </c>
       <c r="C34" t="n">
-        <v>13.95662055865853</v>
+        <v>34.73834302481301</v>
       </c>
     </row>
     <row r="35">
@@ -805,10 +805,10 @@
         <v>45679</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.9040013262353958</v>
+        <v>2.275386396176594</v>
       </c>
       <c r="C35" t="n">
-        <v>-40.59026357537862</v>
+        <v>111.2090301577908</v>
       </c>
     </row>
     <row r="36">
@@ -816,10 +816,10 @@
         <v>45680</v>
       </c>
       <c r="B36" t="n">
-        <v>1.177878025268143</v>
+        <v>-2.463367900363986</v>
       </c>
       <c r="C36" t="n">
-        <v>124.0331159524956</v>
+        <v>-178.3176470499194</v>
       </c>
     </row>
     <row r="37">
@@ -827,10 +827,10 @@
         <v>45681</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.9901445505520226</v>
+        <v>3.165223146724338</v>
       </c>
       <c r="C37" t="n">
-        <v>-4.445918744806904</v>
+        <v>98.40190469910445</v>
       </c>
     </row>
     <row r="38">
@@ -838,10 +838,10 @@
         <v>45684</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6161812467856032</v>
+        <v>-1.140911884744513</v>
       </c>
       <c r="C38" t="n">
-        <v>80.21952881490375</v>
+        <v>-107.1259905657375</v>
       </c>
     </row>
     <row r="39">
@@ -849,10 +849,10 @@
         <v>45685</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.973658903773158</v>
+        <v>3.74151772593736</v>
       </c>
       <c r="C39" t="n">
-        <v>-177.4424905091779</v>
+        <v>276.6851884559315</v>
       </c>
     </row>
     <row r="40">
@@ -860,10 +860,10 @@
         <v>45686</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.219236536537644</v>
+        <v>1.501014622777574</v>
       </c>
       <c r="C40" t="n">
-        <v>88.41709967204388</v>
+        <v>-32.49753838015749</v>
       </c>
     </row>
     <row r="41">
@@ -871,10 +871,10 @@
         <v>45687</v>
       </c>
       <c r="B41" t="n">
-        <v>1.380674352874246</v>
+        <v>-3.029108896171412</v>
       </c>
       <c r="C41" t="n">
-        <v>108.2103565360326</v>
+        <v>-184.5071378762299</v>
       </c>
     </row>
     <row r="42">
@@ -882,10 +882,10 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2457567418654774</v>
+        <v>0.7204089894531632</v>
       </c>
       <c r="C42" t="n">
-        <v>85.83006286084338</v>
+        <v>-64.69888794515271</v>
       </c>
     </row>
     <row r="43">
@@ -893,10 +893,10 @@
         <v>45691</v>
       </c>
       <c r="B43" t="n">
-        <v>1.234321184111209</v>
+        <v>-1.05176207369789</v>
       </c>
       <c r="C43" t="n">
-        <v>199.6383172595184</v>
+        <v>-236.1543575935328</v>
       </c>
     </row>
     <row r="44">
@@ -904,10 +904,10 @@
         <v>45692</v>
       </c>
       <c r="B44" t="n">
-        <v>0.08703772671582018</v>
+        <v>-0.6765495811758773</v>
       </c>
       <c r="C44" t="n">
-        <v>-25.26143413478598</v>
+        <v>8.823564711069727</v>
       </c>
     </row>
     <row r="45">
@@ -915,10 +915,10 @@
         <v>45693</v>
       </c>
       <c r="B45" t="n">
-        <v>0.626505287212203</v>
+        <v>-0.653087522249954</v>
       </c>
       <c r="C45" t="n">
-        <v>96.29068016007514</v>
+        <v>-102.189788985628</v>
       </c>
     </row>
     <row r="46">
@@ -926,10 +926,10 @@
         <v>45694</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2565099394655986</v>
+        <v>0.1061569610706832</v>
       </c>
       <c r="C46" t="n">
-        <v>58.81412391561417</v>
+        <v>-48.55771526517876</v>
       </c>
     </row>
     <row r="47">
@@ -937,10 +937,10 @@
         <v>45695</v>
       </c>
       <c r="B47" t="n">
-        <v>0.4105717541311224</v>
+        <v>0.2480358355610003</v>
       </c>
       <c r="C47" t="n">
-        <v>141.2341954133683</v>
+        <v>-131.5868716115598</v>
       </c>
     </row>
     <row r="48">
@@ -948,10 +948,10 @@
         <v>45698</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.2709270234183199</v>
+        <v>-0.0331516850894781</v>
       </c>
       <c r="C48" t="n">
-        <v>-29.44649096629921</v>
+        <v>47.55528503260076</v>
       </c>
     </row>
     <row r="49">
@@ -959,10 +959,10 @@
         <v>45699</v>
       </c>
       <c r="B49" t="n">
-        <v>-1.45553332804174</v>
+        <v>2.347662042862233</v>
       </c>
       <c r="C49" t="n">
-        <v>-214.1122992504652</v>
+        <v>274.8431160674321</v>
       </c>
     </row>
     <row r="50">
@@ -970,10 +970,10 @@
         <v>45700</v>
       </c>
       <c r="B50" t="n">
-        <v>2.487833854228257</v>
+        <v>-5.589571586281059</v>
       </c>
       <c r="C50" t="n">
-        <v>234.1455061283179</v>
+        <v>-362.9402351690296</v>
       </c>
     </row>
     <row r="51">
@@ -981,10 +981,10 @@
         <v>45701</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.8012367081973729</v>
+        <v>1.770188509559536</v>
       </c>
       <c r="C51" t="n">
-        <v>-13.54216242555573</v>
+        <v>75.75299330868499</v>
       </c>
     </row>
     <row r="52">
@@ -992,10 +992,10 @@
         <v>45702</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.2223330697682003</v>
+        <v>-0.02777332397786845</v>
       </c>
       <c r="C52" t="n">
-        <v>-84.27294583865164</v>
+        <v>69.81810559970339</v>
       </c>
     </row>
     <row r="53">
@@ -1003,10 +1003,10 @@
         <v>45705</v>
       </c>
       <c r="B53" t="n">
-        <v>-3.053993742490919</v>
+        <v>6.452506446573011</v>
       </c>
       <c r="C53" t="n">
-        <v>-252.0392005202147</v>
+        <v>408.5945935306785</v>
       </c>
     </row>
     <row r="54">
@@ -1014,10 +1014,10 @@
         <v>45706</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.695711314712448</v>
+        <v>2.955630800838541</v>
       </c>
       <c r="C54" t="n">
-        <v>-182.2502373991995</v>
+        <v>257.2634001902556</v>
       </c>
     </row>
     <row r="55">
@@ -1025,10 +1025,10 @@
         <v>45707</v>
       </c>
       <c r="B55" t="n">
-        <v>-1.181068691323866</v>
+        <v>2.670345928681336</v>
       </c>
       <c r="C55" t="n">
-        <v>-123.5719837949031</v>
+        <v>192.1365096273763</v>
       </c>
     </row>
     <row r="56">
@@ -1036,10 +1036,10 @@
         <v>45708</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.465211028781511</v>
+        <v>3.011939780069228</v>
       </c>
       <c r="C56" t="n">
-        <v>-143.4560606826269</v>
+        <v>218.8931466396187</v>
       </c>
     </row>
     <row r="57">
@@ -1047,10 +1047,10 @@
         <v>45709</v>
       </c>
       <c r="B57" t="n">
-        <v>0.5207416725656645</v>
+        <v>-0.4055652861896114</v>
       </c>
       <c r="C57" t="n">
-        <v>73.84546876432748</v>
+        <v>-79.18647893273169</v>
       </c>
     </row>
     <row r="58">
@@ -1058,10 +1058,10 @@
         <v>45712</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.08904866894223885</v>
+        <v>0.71036984354651</v>
       </c>
       <c r="C58" t="n">
-        <v>1.306579122346188</v>
+        <v>-0.3877541727016605</v>
       </c>
     </row>
     <row r="59">
@@ -1069,10 +1069,10 @@
         <v>45713</v>
       </c>
       <c r="B59" t="n">
-        <v>0.7958353257038218</v>
+        <v>-0.1585156079680797</v>
       </c>
       <c r="C59" t="n">
-        <v>174.1690139561524</v>
+        <v>-168.6790059422137</v>
       </c>
     </row>
     <row r="60">
@@ -1080,10 +1080,10 @@
         <v>45714</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.7997912754948946</v>
+        <v>2.370663670180016</v>
       </c>
       <c r="C60" t="n">
-        <v>11.49435780306703</v>
+        <v>63.12773516219679</v>
       </c>
     </row>
     <row r="61">
@@ -1091,10 +1091,10 @@
         <v>45715</v>
       </c>
       <c r="B61" t="n">
-        <v>-0.03928566665788821</v>
+        <v>0.3477280193383002</v>
       </c>
       <c r="C61" t="n">
-        <v>39.43868672376279</v>
+        <v>-10.42574485403287</v>
       </c>
     </row>
     <row r="62">
@@ -1102,10 +1102,10 @@
         <v>45716</v>
       </c>
       <c r="B62" t="n">
-        <v>1.039540877753068</v>
+        <v>-1.760075572321569</v>
       </c>
       <c r="C62" t="n">
-        <v>80.70570332326044</v>
+        <v>-146.0516917983404</v>
       </c>
     </row>
     <row r="63">
@@ -1113,10 +1113,10 @@
         <v>45722</v>
       </c>
       <c r="B63" t="n">
-        <v>3.816640168256153</v>
+        <v>-7.752262985699446</v>
       </c>
       <c r="C63" t="n">
-        <v>354.0699905396923</v>
+        <v>-565.1662193274753</v>
       </c>
     </row>
     <row r="64">
@@ -1124,10 +1124,10 @@
         <v>45723</v>
       </c>
       <c r="B64" t="n">
-        <v>2.532537241487398</v>
+        <v>-5.797329400334047</v>
       </c>
       <c r="C64" t="n">
-        <v>218.4691155576874</v>
+        <v>-371.3944859431891</v>
       </c>
     </row>
     <row r="65">
@@ -1135,10 +1135,10 @@
         <v>45726</v>
       </c>
       <c r="B65" t="n">
-        <v>1.49819538328567</v>
+        <v>-2.976787387531346</v>
       </c>
       <c r="C65" t="n">
-        <v>151.9917259622813</v>
+        <v>-219.303176590108</v>
       </c>
     </row>
     <row r="66">
@@ -1146,10 +1146,10 @@
         <v>45727</v>
       </c>
       <c r="B66" t="n">
-        <v>-0.2472968045204452</v>
+        <v>0.4605349168169706</v>
       </c>
       <c r="C66" t="n">
-        <v>-16.59733746103305</v>
+        <v>44.94550742134248</v>
       </c>
     </row>
     <row r="67">
@@ -1157,10 +1157,10 @@
         <v>45728</v>
       </c>
       <c r="B67" t="n">
-        <v>1.61870195056887</v>
+        <v>-1.656979367162924</v>
       </c>
       <c r="C67" t="n">
-        <v>190.696642302666</v>
+        <v>-250.0414212841408</v>
       </c>
     </row>
     <row r="68">
@@ -1168,10 +1168,10 @@
         <v>45729</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.8810794286732705</v>
+        <v>1.359644181725009</v>
       </c>
       <c r="C68" t="n">
-        <v>-103.6489479251398</v>
+        <v>144.9203547797435</v>
       </c>
     </row>
     <row r="69">
@@ -1179,10 +1179,10 @@
         <v>45730</v>
       </c>
       <c r="B69" t="n">
-        <v>-0.05873225778701514</v>
+        <v>0.4990001035693637</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6992874994356106</v>
+        <v>-6.396486326737774</v>
       </c>
     </row>
     <row r="70">
@@ -1190,10 +1190,10 @@
         <v>45733</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.787083313936452</v>
+        <v>1.550457094232317</v>
       </c>
       <c r="C70" t="n">
-        <v>-80.82286345404447</v>
+        <v>111.1770589178681</v>
       </c>
     </row>
     <row r="71">
@@ -1201,10 +1201,10 @@
         <v>45734</v>
       </c>
       <c r="B71" t="n">
-        <v>1.596923143312957</v>
+        <v>-3.053573027047911</v>
       </c>
       <c r="C71" t="n">
-        <v>130.6439021852134</v>
+        <v>-216.5236762832164</v>
       </c>
     </row>
     <row r="72">
@@ -1212,10 +1212,10 @@
         <v>45735</v>
       </c>
       <c r="B72" t="n">
-        <v>0.6504982808875597</v>
+        <v>-0.6237326299969035</v>
       </c>
       <c r="C72" t="n">
-        <v>37.23263121611294</v>
+        <v>-71.06190635760387</v>
       </c>
     </row>
     <row r="73">
@@ -1223,10 +1223,10 @@
         <v>45736</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.631081880835517</v>
+        <v>3.398186620089535</v>
       </c>
       <c r="C73" t="n">
-        <v>-192.8390905105993</v>
+        <v>264.5987571779311</v>
       </c>
     </row>
     <row r="74">
@@ -1234,10 +1234,10 @@
         <v>45737</v>
       </c>
       <c r="B74" t="n">
-        <v>-1.81867231372127</v>
+        <v>3.604777679140551</v>
       </c>
       <c r="C74" t="n">
-        <v>-189.2913171421818</v>
+        <v>277.7418888239928</v>
       </c>
     </row>
     <row r="75">
@@ -1245,10 +1245,10 @@
         <v>45740</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.6799517345240296</v>
+        <v>0.4647685545256413</v>
       </c>
       <c r="C75" t="n">
-        <v>-107.4280145990516</v>
+        <v>139.7042782973037</v>
       </c>
     </row>
     <row r="76">
@@ -1256,10 +1256,10 @@
         <v>45741</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0669311402207463</v>
+        <v>-0.2591947808190816</v>
       </c>
       <c r="C76" t="n">
-        <v>-47.68772087373122</v>
+        <v>34.48051543592364</v>
       </c>
     </row>
     <row r="77">
@@ -1267,10 +1267,10 @@
         <v>45742</v>
       </c>
       <c r="B77" t="n">
-        <v>0.06384092164896329</v>
+        <v>0.2155148177854758</v>
       </c>
       <c r="C77" t="n">
-        <v>-43.05351470491169</v>
+        <v>39.17413368739821</v>
       </c>
     </row>
     <row r="78">
@@ -1278,10 +1278,10 @@
         <v>45743</v>
       </c>
       <c r="B78" t="n">
-        <v>0.7053232652110411</v>
+        <v>-2.556291150369133</v>
       </c>
       <c r="C78" t="n">
-        <v>27.69365013586946</v>
+        <v>-71.91185125195338</v>
       </c>
     </row>
     <row r="79">
@@ -1289,10 +1289,10 @@
         <v>45744</v>
       </c>
       <c r="B79" t="n">
-        <v>0.8499358884300527</v>
+        <v>-1.91220041520139</v>
       </c>
       <c r="C79" t="n">
-        <v>36.9229742964354</v>
+        <v>-88.05980303965121</v>
       </c>
     </row>
     <row r="80">
@@ -1300,10 +1300,10 @@
         <v>45747</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.08608079109392669</v>
+        <v>-0.04933596607231816</v>
       </c>
       <c r="C80" t="n">
-        <v>11.32524599952576</v>
+        <v>9.036423128350005</v>
       </c>
     </row>
     <row r="81">
@@ -1311,10 +1311,10 @@
         <v>45748</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1948852577856293</v>
+        <v>-0.4475562715287616</v>
       </c>
       <c r="C81" t="n">
-        <v>-2.617700531587017</v>
+        <v>1.548218196653885</v>
       </c>
     </row>
     <row r="82">
@@ -1322,10 +1322,10 @@
         <v>45749</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.208909763768373</v>
+        <v>1.854048774242071</v>
       </c>
       <c r="C82" t="n">
-        <v>-120.5645672504365</v>
+        <v>187.1342835848201</v>
       </c>
     </row>
     <row r="83">
@@ -1333,10 +1333,10 @@
         <v>45750</v>
       </c>
       <c r="B83" t="n">
-        <v>3.693390709958256</v>
+        <v>-8.857591663744252</v>
       </c>
       <c r="C83" t="n">
-        <v>308.3197835869978</v>
+        <v>-521.6373133282217</v>
       </c>
     </row>
     <row r="84">
@@ -1344,10 +1344,10 @@
         <v>45751</v>
       </c>
       <c r="B84" t="n">
-        <v>5.702981487508214</v>
+        <v>-13.71633687469764</v>
       </c>
       <c r="C84" t="n">
-        <v>420.5506558183063</v>
+        <v>-775.021859094202</v>
       </c>
     </row>
     <row r="85">
@@ -1355,10 +1355,10 @@
         <v>45754</v>
       </c>
       <c r="B85" t="n">
-        <v>7.753915357006658</v>
+        <v>-21.04078534484285</v>
       </c>
       <c r="C85" t="n">
-        <v>516.2631678732736</v>
+        <v>-976.3195716846582</v>
       </c>
     </row>
     <row r="86">
@@ -1366,10 +1366,10 @@
         <v>45755</v>
       </c>
       <c r="B86" t="n">
-        <v>6.265965083866666</v>
+        <v>-13.90027934044885</v>
       </c>
       <c r="C86" t="n">
-        <v>437.9271119694867</v>
+        <v>-835.06061635344</v>
       </c>
     </row>
     <row r="87">
@@ -1377,10 +1377,10 @@
         <v>45756</v>
       </c>
       <c r="B87" t="n">
-        <v>7.751523347998763</v>
+        <v>-20.83538688241709</v>
       </c>
       <c r="C87" t="n">
-        <v>515.5164180937312</v>
+        <v>-979.5404589447497</v>
       </c>
     </row>
     <row r="88">
@@ -1388,10 +1388,10 @@
         <v>45757</v>
       </c>
       <c r="B88" t="n">
-        <v>6.768797941785852</v>
+        <v>-13.78767857897568</v>
       </c>
       <c r="C88" t="n">
-        <v>526.4804038863051</v>
+        <v>-912.4842073015703</v>
       </c>
     </row>
     <row r="89">
@@ -1399,10 +1399,10 @@
         <v>45758</v>
       </c>
       <c r="B89" t="n">
-        <v>4.787869232808615</v>
+        <v>-9.626929437155654</v>
       </c>
       <c r="C89" t="n">
-        <v>421.4153129080926</v>
+        <v>-686.3446015820999</v>
       </c>
     </row>
     <row r="90">
@@ -1410,10 +1410,10 @@
         <v>45761</v>
       </c>
       <c r="B90" t="n">
-        <v>3.348587841389024</v>
+        <v>-6.442405177496946</v>
       </c>
       <c r="C90" t="n">
-        <v>312.6511996777165</v>
+        <v>-487.5817677271463</v>
       </c>
     </row>
     <row r="91">
@@ -1421,10 +1421,10 @@
         <v>45762</v>
       </c>
       <c r="B91" t="n">
-        <v>2.258048136063703</v>
+        <v>-3.57256116039238</v>
       </c>
       <c r="C91" t="n">
-        <v>203.0297125686773</v>
+        <v>-317.4894021320558</v>
       </c>
     </row>
     <row r="92">
@@ -1432,10 +1432,10 @@
         <v>45763</v>
       </c>
       <c r="B92" t="n">
-        <v>3.706421676882869</v>
+        <v>-6.214522256945862</v>
       </c>
       <c r="C92" t="n">
-        <v>315.0857679204601</v>
+        <v>-530.9696943974407</v>
       </c>
     </row>
     <row r="93">
@@ -1443,10 +1443,10 @@
         <v>45764</v>
       </c>
       <c r="B93" t="n">
-        <v>2.056155193253538</v>
+        <v>-3.087896449956135</v>
       </c>
       <c r="C93" t="n">
-        <v>173.1860845255364</v>
+        <v>-289.2397386688562</v>
       </c>
     </row>
     <row r="94">
@@ -1454,10 +1454,10 @@
         <v>45769</v>
       </c>
       <c r="B94" t="n">
-        <v>1.935424835246344</v>
+        <v>-2.832867734609572</v>
       </c>
       <c r="C94" t="n">
-        <v>212.8144804815165</v>
+        <v>-300.3244171418455</v>
       </c>
     </row>
     <row r="95">
@@ -1465,10 +1465,10 @@
         <v>45770</v>
       </c>
       <c r="B95" t="n">
-        <v>3.165598371313482</v>
+        <v>-5.646917552449637</v>
       </c>
       <c r="C95" t="n">
-        <v>287.3048669509106</v>
+        <v>-454.6405524925922</v>
       </c>
     </row>
     <row r="96">
@@ -1476,10 +1476,10 @@
         <v>45771</v>
       </c>
       <c r="B96" t="n">
-        <v>1.408051793945887</v>
+        <v>-2.629419643242011</v>
       </c>
       <c r="C96" t="n">
-        <v>128.3050196011291</v>
+        <v>-196.030615847166</v>
       </c>
     </row>
     <row r="97">
@@ -1487,10 +1487,10 @@
         <v>45772</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1096992999385887</v>
+        <v>0.525692616493759</v>
       </c>
       <c r="C97" t="n">
-        <v>35.45364831127648</v>
+        <v>-16.96796617982003</v>
       </c>
     </row>
     <row r="98">
@@ -1498,10 +1498,10 @@
         <v>45775</v>
       </c>
       <c r="B98" t="n">
-        <v>0.4041349803111598</v>
+        <v>-0.4412306685380978</v>
       </c>
       <c r="C98" t="n">
-        <v>42.42127844121038</v>
+        <v>-48.07824084852557</v>
       </c>
     </row>
     <row r="99">
@@ -1509,10 +1509,10 @@
         <v>45776</v>
       </c>
       <c r="B99" t="n">
-        <v>0.08853671575095484</v>
+        <v>0.6809051120701772</v>
       </c>
       <c r="C99" t="n">
-        <v>35.97212576282271</v>
+        <v>-18.54986021859151</v>
       </c>
     </row>
     <row r="100">
@@ -1520,10 +1520,10 @@
         <v>45777</v>
       </c>
       <c r="B100" t="n">
-        <v>1.24095465732718</v>
+        <v>-2.265041562707024</v>
       </c>
       <c r="C100" t="n">
-        <v>122.0067522235215</v>
+        <v>-178.1197254495219</v>
       </c>
     </row>
     <row r="101">
@@ -1531,10 +1531,10 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>0.8840852384289154</v>
+        <v>-1.691555837599752</v>
       </c>
       <c r="C101" t="n">
-        <v>88.431397294601</v>
+        <v>-121.4881765318655</v>
       </c>
     </row>
     <row r="102">
@@ -1542,10 +1542,10 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.0203373876813996</v>
+        <v>-0.5043097933745269</v>
       </c>
       <c r="C102" t="n">
-        <v>30.90057942396791</v>
+        <v>-34.2560458822251</v>
       </c>
     </row>
     <row r="103">
@@ -1553,10 +1553,10 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>-0.1560317876560216</v>
+        <v>0.8504734100434332</v>
       </c>
       <c r="C103" t="n">
-        <v>37.70505529562924</v>
+        <v>0.3769715264994269</v>
       </c>
     </row>
     <row r="104">
@@ -1564,10 +1564,10 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>-0.3891159099161144</v>
+        <v>1.661404205931486</v>
       </c>
       <c r="C104" t="n">
-        <v>-18.82237320331297</v>
+        <v>58.05440393712158</v>
       </c>
     </row>
     <row r="105">
@@ -1575,10 +1575,10 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>3.013564685026451</v>
+        <v>-6.982938908685049</v>
       </c>
       <c r="C105" t="n">
-        <v>250.5169649680574</v>
+        <v>-423.1661454028888</v>
       </c>
     </row>
     <row r="106">
@@ -1586,10 +1586,10 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>-1.971213302964143</v>
+        <v>4.020354756149344</v>
       </c>
       <c r="C106" t="n">
-        <v>-232.8265164151051</v>
+        <v>326.1979241317166</v>
       </c>
     </row>
     <row r="107">
@@ -1597,10 +1597,10 @@
         <v>45789</v>
       </c>
       <c r="B107" t="n">
-        <v>0.5015690680789299</v>
+        <v>-1.030347581797169</v>
       </c>
       <c r="C107" t="n">
-        <v>40.99095894755651</v>
+        <v>-57.14592369672582</v>
       </c>
     </row>
     <row r="108">
@@ -1608,10 +1608,10 @@
         <v>45790</v>
       </c>
       <c r="B108" t="n">
-        <v>0.07389101107395445</v>
+        <v>0.3694461324886809</v>
       </c>
       <c r="C108" t="n">
-        <v>-3.603471270326633</v>
+        <v>-19.64499462307355</v>
       </c>
     </row>
     <row r="109">
@@ -1619,10 +1619,10 @@
         <v>45791</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.008297976823126203</v>
+        <v>1.093178748502707</v>
       </c>
       <c r="C109" t="n">
-        <v>30.28711931162179</v>
+        <v>-5.74191510876066</v>
       </c>
     </row>
     <row r="110">
@@ -1630,10 +1630,10 @@
         <v>45792</v>
       </c>
       <c r="B110" t="n">
-        <v>1.316696407679176</v>
+        <v>-1.494329986933975</v>
       </c>
       <c r="C110" t="n">
-        <v>148.4424492095821</v>
+        <v>-196.0411561652218</v>
       </c>
     </row>
     <row r="111">
@@ -1641,10 +1641,10 @@
         <v>45793</v>
       </c>
       <c r="B111" t="n">
-        <v>1.738279018224222</v>
+        <v>-3.145038892566254</v>
       </c>
       <c r="C111" t="n">
-        <v>183.6142850017422</v>
+        <v>-256.4032004356965</v>
       </c>
     </row>
     <row r="112">
@@ -1652,10 +1652,10 @@
         <v>45796</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.9280643500510728</v>
+        <v>2.611063664189384</v>
       </c>
       <c r="C112" t="n">
-        <v>-5.908376053543332</v>
+        <v>94.46230521612065</v>
       </c>
     </row>
     <row r="113">
@@ -1663,10 +1663,10 @@
         <v>45797</v>
       </c>
       <c r="B113" t="n">
-        <v>0.1072439837823551</v>
+        <v>0.7708424596949111</v>
       </c>
       <c r="C113" t="n">
-        <v>89.43466408929606</v>
+        <v>-50.12173113872061</v>
       </c>
     </row>
     <row r="114">
@@ -1674,10 +1674,10 @@
         <v>45798</v>
       </c>
       <c r="B114" t="n">
-        <v>0.9071003069725188</v>
+        <v>-0.5181195605479377</v>
       </c>
       <c r="C114" t="n">
-        <v>131.132031891943</v>
+        <v>-163.2806973838176</v>
       </c>
     </row>
     <row r="115">
@@ -1685,10 +1685,10 @@
         <v>45799</v>
       </c>
       <c r="B115" t="n">
-        <v>1.916677550313644</v>
+        <v>-3.631081035506907</v>
       </c>
       <c r="C115" t="n">
-        <v>185.6363398421307</v>
+        <v>-276.1556190152284</v>
       </c>
     </row>
     <row r="116">
@@ -1696,10 +1696,10 @@
         <v>45800</v>
       </c>
       <c r="B116" t="n">
-        <v>3.887093952814809</v>
+        <v>-8.217947066679724</v>
       </c>
       <c r="C116" t="n">
-        <v>320.7504564574061</v>
+        <v>-552.1237553470916</v>
       </c>
     </row>
     <row r="117">
@@ -1707,10 +1707,10 @@
         <v>45803</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.8032080059701712</v>
+        <v>1.232656895492062</v>
       </c>
       <c r="C117" t="n">
-        <v>-150.0780238247445</v>
+        <v>178.9609613302002</v>
       </c>
     </row>
     <row r="118">
@@ -1718,10 +1718,10 @@
         <v>45804</v>
       </c>
       <c r="B118" t="n">
-        <v>1.127845258014332</v>
+        <v>-2.836928169444979</v>
       </c>
       <c r="C118" t="n">
-        <v>113.7847536666156</v>
+        <v>-192.7589912289127</v>
       </c>
     </row>
     <row r="119">
@@ -1729,10 +1729,10 @@
         <v>45805</v>
       </c>
       <c r="B119" t="n">
-        <v>-1.056710583165386</v>
+        <v>2.090361560105866</v>
       </c>
       <c r="C119" t="n">
-        <v>-84.80743660364909</v>
+        <v>156.8682508695815</v>
       </c>
     </row>
     <row r="120">
@@ -1740,10 +1740,10 @@
         <v>45806</v>
       </c>
       <c r="B120" t="n">
-        <v>0.3984681766586362</v>
+        <v>-0.06981452497487424</v>
       </c>
       <c r="C120" t="n">
-        <v>60.55364115874468</v>
+        <v>-58.97366171963015</v>
       </c>
     </row>
     <row r="121">
@@ -1751,10 +1751,10 @@
         <v>45807</v>
       </c>
       <c r="B121" t="n">
-        <v>1.020603031682482</v>
+        <v>-1.272563356557896</v>
       </c>
       <c r="C121" t="n">
-        <v>173.0009090083107</v>
+        <v>-194.9152694660424</v>
       </c>
     </row>
     <row r="122">
@@ -1762,10 +1762,10 @@
         <v>45810</v>
       </c>
       <c r="B122" t="n">
-        <v>2.060282096564862</v>
+        <v>-4.668604973480686</v>
       </c>
       <c r="C122" t="n">
-        <v>176.9235493026125</v>
+        <v>-294.9606636066221</v>
       </c>
     </row>
     <row r="123">
@@ -1773,10 +1773,10 @@
         <v>45811</v>
       </c>
       <c r="B123" t="n">
-        <v>0.4265241047329653</v>
+        <v>-1.479088269586642</v>
       </c>
       <c r="C123" t="n">
-        <v>-14.34961822073087</v>
+        <v>-10.95991895464176</v>
       </c>
     </row>
     <row r="124">
@@ -1784,10 +1784,10 @@
         <v>45812</v>
       </c>
       <c r="B124" t="n">
-        <v>1.351208824589682</v>
+        <v>-1.886894750495536</v>
       </c>
       <c r="C124" t="n">
-        <v>149.7401307301073</v>
+        <v>-207.950624312778</v>
       </c>
     </row>
     <row r="125">
@@ -1795,10 +1795,10 @@
         <v>45813</v>
       </c>
       <c r="B125" t="n">
-        <v>-0.06564633766064319</v>
+        <v>1.284024024779573</v>
       </c>
       <c r="C125" t="n">
-        <v>33.53594437655583</v>
+        <v>-3.778894685287907</v>
       </c>
     </row>
     <row r="126">
@@ -1806,10 +1806,10 @@
         <v>45814</v>
       </c>
       <c r="B126" t="n">
-        <v>0.9250171838060341</v>
+        <v>-1.446756723139216</v>
       </c>
       <c r="C126" t="n">
-        <v>90.01719725226977</v>
+        <v>-125.7671215138738</v>
       </c>
     </row>
     <row r="127">
@@ -1817,10 +1817,10 @@
         <v>45817</v>
       </c>
       <c r="B127" t="n">
-        <v>1.810480555167409</v>
+        <v>-3.794773351191459</v>
       </c>
       <c r="C127" t="n">
-        <v>144.7984669586056</v>
+        <v>-235.7779118157591</v>
       </c>
     </row>
     <row r="128">
@@ -1828,10 +1828,10 @@
         <v>45818</v>
       </c>
       <c r="B128" t="n">
-        <v>0.6142460798612109</v>
+        <v>-0.4835829067568562</v>
       </c>
       <c r="C128" t="n">
-        <v>41.97799464658856</v>
+        <v>-64.19166638193768</v>
       </c>
     </row>
     <row r="129">
@@ -1839,10 +1839,10 @@
         <v>45819</v>
       </c>
       <c r="B129" t="n">
-        <v>2.188850997656571</v>
+        <v>-3.867879975633832</v>
       </c>
       <c r="C129" t="n">
-        <v>206.4542426044863</v>
+        <v>-321.074968764453</v>
       </c>
     </row>
     <row r="130">
@@ -1850,10 +1850,10 @@
         <v>45820</v>
       </c>
       <c r="B130" t="n">
-        <v>0.05774616172889706</v>
+        <v>0.4067597668413697</v>
       </c>
       <c r="C130" t="n">
-        <v>28.40412292119514</v>
+        <v>-32.56802139852535</v>
       </c>
     </row>
     <row r="131">
@@ -1861,10 +1861,10 @@
         <v>45821</v>
       </c>
       <c r="B131" t="n">
-        <v>0.1855870291819618</v>
+        <v>-0.6843635298676521</v>
       </c>
       <c r="C131" t="n">
-        <v>-6.791737560757129</v>
+        <v>0.3802996463394546</v>
       </c>
     </row>
     <row r="132">
@@ -1872,10 +1872,10 @@
         <v>45824</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.7670117672826676</v>
+        <v>1.423961437089044</v>
       </c>
       <c r="C132" t="n">
-        <v>-58.29716857873922</v>
+        <v>102.5407425381143</v>
       </c>
     </row>
     <row r="133">
@@ -1883,10 +1883,10 @@
         <v>45825</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.5518536558181613</v>
+        <v>1.86896658968343</v>
       </c>
       <c r="C133" t="n">
-        <v>-23.84043300943822</v>
+        <v>74.95736240616426</v>
       </c>
     </row>
     <row r="134">
@@ -1894,10 +1894,10 @@
         <v>45826</v>
       </c>
       <c r="B134" t="n">
-        <v>0.6959480671956993</v>
+        <v>-0.4625085509628304</v>
       </c>
       <c r="C134" t="n">
-        <v>107.2397618116098</v>
+        <v>-119.8414869808794</v>
       </c>
     </row>
     <row r="135">
@@ -1905,10 +1905,10 @@
         <v>45828</v>
       </c>
       <c r="B135" t="n">
-        <v>0.6821237773134434</v>
+        <v>-1.299579864781375</v>
       </c>
       <c r="C135" t="n">
-        <v>74.64481022783859</v>
+        <v>-95.39157056682249</v>
       </c>
     </row>
     <row r="136">
@@ -1916,10 +1916,10 @@
         <v>45831</v>
       </c>
       <c r="B136" t="n">
-        <v>-1.75183496811186</v>
+        <v>3.966316056216108</v>
       </c>
       <c r="C136" t="n">
-        <v>-79.27217277621922</v>
+        <v>195.6816337081363</v>
       </c>
     </row>
     <row r="137">
@@ -1927,10 +1927,10 @@
         <v>45832</v>
       </c>
       <c r="B137" t="n">
-        <v>0.5287489457337694</v>
+        <v>-1.006545083876223</v>
       </c>
       <c r="C137" t="n">
-        <v>58.49102244281859</v>
+        <v>-74.18615500082295</v>
       </c>
     </row>
     <row r="138">
@@ -1938,10 +1938,10 @@
         <v>45833</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.578741404116373</v>
+        <v>1.298866359812219</v>
       </c>
       <c r="C138" t="n">
-        <v>-34.5397448591068</v>
+        <v>82.49102302607382</v>
       </c>
     </row>
     <row r="139">
@@ -1949,10 +1949,10 @@
         <v>45834</v>
       </c>
       <c r="B139" t="n">
-        <v>-1.482752251204714</v>
+        <v>3.394723693122898</v>
       </c>
       <c r="C139" t="n">
-        <v>-116.8088464235333</v>
+        <v>208.2178261211774</v>
       </c>
     </row>
     <row r="140">
@@ -1960,10 +1960,10 @@
         <v>45835</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.9286727634885656</v>
+        <v>2.277640572177042</v>
       </c>
       <c r="C140" t="n">
-        <v>-93.76476816722196</v>
+        <v>155.3401529437562</v>
       </c>
     </row>
     <row r="141">
@@ -1971,10 +1971,10 @@
         <v>45838</v>
       </c>
       <c r="B141" t="n">
-        <v>0.356977993512092</v>
+        <v>-0.7099423812016167</v>
       </c>
       <c r="C141" t="n">
-        <v>89.28722036252803</v>
+        <v>-100.6065306802798</v>
       </c>
     </row>
     <row r="142">
@@ -1982,10 +1982,10 @@
         <v>45839</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.5422137501246564</v>
+        <v>1.891236282292674</v>
       </c>
       <c r="C142" t="n">
-        <v>25.5816303293471</v>
+        <v>46.5938513168433</v>
       </c>
     </row>
     <row r="143">
@@ -1993,10 +1993,10 @@
         <v>45840</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.9921191424971042</v>
+        <v>1.503389925694478</v>
       </c>
       <c r="C143" t="n">
-        <v>-96.25508335017459</v>
+        <v>159.7629097695554</v>
       </c>
     </row>
     <row r="144">
@@ -2004,10 +2004,10 @@
         <v>45841</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.6899044744917117</v>
+        <v>0.7976457015634488</v>
       </c>
       <c r="C144" t="n">
-        <v>-83.35645189156781</v>
+        <v>122.4338973664214</v>
       </c>
     </row>
     <row r="145">
@@ -2015,10 +2015,10 @@
         <v>45842</v>
       </c>
       <c r="B145" t="n">
-        <v>-5.383356781794961</v>
+        <v>9.462284055037781</v>
       </c>
       <c r="C145" t="n">
-        <v>-577.1119370708043</v>
+        <v>750.8001332158851</v>
       </c>
     </row>
     <row r="146">
@@ -2026,10 +2026,10 @@
         <v>45845</v>
       </c>
       <c r="B146" t="n">
-        <v>-2.331313689098647</v>
+        <v>4.652032038423202</v>
       </c>
       <c r="C146" t="n">
-        <v>-203.3609477098092</v>
+        <v>301.5869156507804</v>
       </c>
     </row>
     <row r="147">
@@ -2037,10 +2037,10 @@
         <v>45846</v>
       </c>
       <c r="B147" t="n">
-        <v>0.08217780576241616</v>
+        <v>0.3802934526488015</v>
       </c>
       <c r="C147" t="n">
-        <v>44.38888275103075</v>
+        <v>-25.94638909160066</v>
       </c>
     </row>
     <row r="148">
@@ -2048,10 +2048,10 @@
         <v>45847</v>
       </c>
       <c r="B148" t="n">
-        <v>-1.097743090680726</v>
+        <v>2.037804062523072</v>
       </c>
       <c r="C148" t="n">
-        <v>-120.6446425624054</v>
+        <v>173.2813483306986</v>
       </c>
     </row>
     <row r="149">
@@ -2059,10 +2059,10 @@
         <v>45848</v>
       </c>
       <c r="B149" t="n">
-        <v>2.021277832496201</v>
+        <v>-4.563015470806369</v>
       </c>
       <c r="C149" t="n">
-        <v>183.5230604345884</v>
+        <v>-285.8282889890628</v>
       </c>
     </row>
     <row r="150">
@@ -2070,10 +2070,10 @@
         <v>45849</v>
       </c>
       <c r="B150" t="n">
-        <v>-1.77784335172491</v>
+        <v>3.479182408988788</v>
       </c>
       <c r="C150" t="n">
-        <v>-185.0284845313526</v>
+        <v>270.6897379411297</v>
       </c>
     </row>
     <row r="151">
@@ -2081,10 +2081,10 @@
         <v>45852</v>
       </c>
       <c r="B151" t="n">
-        <v>-1.530540132762689</v>
+        <v>2.190393313878433</v>
       </c>
       <c r="C151" t="n">
-        <v>-154.4572178249859</v>
+        <v>219.2758062402822</v>
       </c>
     </row>
     <row r="152">
@@ -2092,10 +2092,10 @@
         <v>45853</v>
       </c>
       <c r="B152" t="n">
-        <v>0.6163581579278929</v>
+        <v>-0.8199398360856824</v>
       </c>
       <c r="C152" t="n">
-        <v>61.74194089327204</v>
+        <v>-74.2537150035668</v>
       </c>
     </row>
     <row r="153">
@@ -2103,10 +2103,10 @@
         <v>45854</v>
       </c>
       <c r="B153" t="n">
-        <v>0.8121955277251708</v>
+        <v>-1.773587833392475</v>
       </c>
       <c r="C153" t="n">
-        <v>77.51702250619074</v>
+        <v>-110.1766923048222</v>
       </c>
     </row>
     <row r="154">
@@ -2114,10 +2114,10 @@
         <v>45855</v>
       </c>
       <c r="B154" t="n">
-        <v>0.9546081723701939</v>
+        <v>-1.110417481093018</v>
       </c>
       <c r="C154" t="n">
-        <v>133.1572239289574</v>
+        <v>-151.8454171944886</v>
       </c>
     </row>
     <row r="155">
@@ -2125,10 +2125,10 @@
         <v>45856</v>
       </c>
       <c r="B155" t="n">
-        <v>0.04871055084569401</v>
+        <v>-0.3173562694420948</v>
       </c>
       <c r="C155" t="n">
-        <v>9.56891898777889</v>
+        <v>-5.33163384585681</v>
       </c>
     </row>
     <row r="156">
@@ -2136,10 +2136,10 @@
         <v>45859</v>
       </c>
       <c r="B156" t="n">
-        <v>-0.1793600665264673</v>
+        <v>0.4889779382766768</v>
       </c>
       <c r="C156" t="n">
-        <v>28.54540253604599</v>
+        <v>1.404195732134372</v>
       </c>
     </row>
     <row r="157">
@@ -2147,10 +2147,10 @@
         <v>45860</v>
       </c>
       <c r="B157" t="n">
-        <v>0.5652785873178593</v>
+        <v>0.1068829103345189</v>
       </c>
       <c r="C157" t="n">
-        <v>119.8267105293776</v>
+        <v>-116.381551068521</v>
       </c>
     </row>
     <row r="158">
@@ -2158,10 +2158,10 @@
         <v>45861</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.1609898281457661</v>
+        <v>-0.1389037398526872</v>
       </c>
       <c r="C158" t="n">
-        <v>-10.52714418766556</v>
+        <v>28.18744387963879</v>
       </c>
     </row>
     <row r="159">
@@ -2169,10 +2169,10 @@
         <v>45862</v>
       </c>
       <c r="B159" t="n">
-        <v>-2.23961823995939</v>
+        <v>4.313782215036052</v>
       </c>
       <c r="C159" t="n">
-        <v>-209.4684216672826</v>
+        <v>324.0367919642745</v>
       </c>
     </row>
     <row r="160">
@@ -2180,10 +2180,10 @@
         <v>45863</v>
       </c>
       <c r="B160" t="n">
-        <v>-1.71252394199846</v>
+        <v>3.653326587663688</v>
       </c>
       <c r="C160" t="n">
-        <v>-160.1593516281583</v>
+        <v>246.7714990413627</v>
       </c>
     </row>
     <row r="161">
@@ -2191,10 +2191,10 @@
         <v>45866</v>
       </c>
       <c r="B161" t="n">
-        <v>-1.743668184313267</v>
+        <v>2.77161924504975</v>
       </c>
       <c r="C161" t="n">
-        <v>-206.5947898717006</v>
+        <v>269.028322375981</v>
       </c>
     </row>
     <row r="162">
@@ -2202,10 +2202,10 @@
         <v>45867</v>
       </c>
       <c r="B162" t="n">
-        <v>-2.289528194505851</v>
+        <v>4.533825585574937</v>
       </c>
       <c r="C162" t="n">
-        <v>-226.2991203817432</v>
+        <v>344.421304033272</v>
       </c>
     </row>
     <row r="163">
@@ -2213,10 +2213,10 @@
         <v>45868</v>
       </c>
       <c r="B163" t="n">
-        <v>4.33258917584777</v>
+        <v>-10.37578554875634</v>
       </c>
       <c r="C163" t="n">
-        <v>347.3964362056084</v>
+        <v>-604.2537583554611</v>
       </c>
     </row>
     <row r="164">
@@ -2224,10 +2224,10 @@
         <v>45869</v>
       </c>
       <c r="B164" t="n">
-        <v>1.587447915689395</v>
+        <v>-2.998054824407309</v>
       </c>
       <c r="C164" t="n">
-        <v>153.8897764811942</v>
+        <v>-230.1915030636591</v>
       </c>
     </row>
     <row r="165">
@@ -2235,10 +2235,10 @@
         <v>45873</v>
       </c>
       <c r="B165" t="n">
-        <v>1.71261746008725</v>
+        <v>-4.023300671073682</v>
       </c>
       <c r="C165" t="n">
-        <v>141.3775111552712</v>
+        <v>-241.0096355460459</v>
       </c>
     </row>
     <row r="166">
@@ -2246,10 +2246,10 @@
         <v>45874</v>
       </c>
       <c r="B166" t="n">
-        <v>1.56405891376041</v>
+        <v>-2.464922784072057</v>
       </c>
       <c r="C166" t="n">
-        <v>171.487508382521</v>
+        <v>-232.2417319438808</v>
       </c>
     </row>
     <row r="167">
@@ -2257,10 +2257,10 @@
         <v>45875</v>
       </c>
       <c r="B167" t="n">
-        <v>1.1790986490365</v>
+        <v>-2.103874239373782</v>
       </c>
       <c r="C167" t="n">
-        <v>135.7107757787759</v>
+        <v>-176.0580583004421</v>
       </c>
     </row>
     <row r="168">
@@ -2268,10 +2268,10 @@
         <v>45876</v>
       </c>
       <c r="B168" t="n">
-        <v>0.4650838734870963</v>
+        <v>-0.6085475475171371</v>
       </c>
       <c r="C168" t="n">
-        <v>70.66620659281064</v>
+        <v>-78.67696349140489</v>
       </c>
     </row>
     <row r="169">
@@ -2279,10 +2279,10 @@
         <v>45877</v>
       </c>
       <c r="B169" t="n">
-        <v>-0.4321887759356882</v>
+        <v>1.637932504809495</v>
       </c>
       <c r="C169" t="n">
-        <v>30.74478314545513</v>
+        <v>32.32147511264827</v>
       </c>
     </row>
     <row r="170">
@@ -2290,10 +2290,10 @@
         <v>45880</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.6662016139019559</v>
+        <v>1.832489709126789</v>
       </c>
       <c r="C170" t="n">
-        <v>-58.8946827173627</v>
+        <v>111.0011499081572</v>
       </c>
     </row>
     <row r="171">
@@ -2301,10 +2301,10 @@
         <v>45881</v>
       </c>
       <c r="B171" t="n">
-        <v>0.8752292354531845</v>
+        <v>-1.898060788485386</v>
       </c>
       <c r="C171" t="n">
-        <v>89.52153054155468</v>
+        <v>-139.2619587470824</v>
       </c>
     </row>
     <row r="172">
@@ -2312,10 +2312,10 @@
         <v>45882</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.9900588193843824</v>
+        <v>2.127343704444425</v>
       </c>
       <c r="C172" t="n">
-        <v>-33.29636999697182</v>
+        <v>107.4832273763246</v>
       </c>
     </row>
     <row r="173">
@@ -2323,10 +2323,10 @@
         <v>45883</v>
       </c>
       <c r="B173" t="n">
-        <v>0.9885302089767862</v>
+        <v>-2.003330058537357</v>
       </c>
       <c r="C173" t="n">
-        <v>89.2729753868512</v>
+        <v>-127.8966579265923</v>
       </c>
     </row>
     <row r="174">
@@ -2334,10 +2334,10 @@
         <v>45884</v>
       </c>
       <c r="B174" t="n">
-        <v>-0.1856748413800654</v>
+        <v>1.542618460769455</v>
       </c>
       <c r="C174" t="n">
-        <v>16.51128353797455</v>
+        <v>22.28278301939874</v>
       </c>
     </row>
     <row r="175">
@@ -2345,10 +2345,10 @@
         <v>45887</v>
       </c>
       <c r="B175" t="n">
-        <v>-2.515909679089398</v>
+        <v>4.485139529388952</v>
       </c>
       <c r="C175" t="n">
-        <v>-236.0881743170349</v>
+        <v>354.81839718958</v>
       </c>
     </row>
     <row r="176">
@@ -2356,10 +2356,10 @@
         <v>45888</v>
       </c>
       <c r="B176" t="n">
-        <v>1.746608532097565</v>
+        <v>-4.1539929321573</v>
       </c>
       <c r="C176" t="n">
-        <v>180.7212581067617</v>
+        <v>-283.7468001835062</v>
       </c>
     </row>
     <row r="177">
@@ -2367,10 +2367,10 @@
         <v>45889</v>
       </c>
       <c r="B177" t="n">
-        <v>-2.173270023250737</v>
+        <v>3.482471997016169</v>
       </c>
       <c r="C177" t="n">
-        <v>-206.6153168022483</v>
+        <v>310.0529062060054</v>
       </c>
     </row>
     <row r="178">
@@ -2378,10 +2378,10 @@
         <v>45890</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.5686049288831715</v>
+        <v>-0.08799063462428967</v>
       </c>
       <c r="C178" t="n">
-        <v>-95.82636502965497</v>
+        <v>114.3283543171528</v>
       </c>
     </row>
     <row r="179">
@@ -2389,10 +2389,10 @@
         <v>45891</v>
       </c>
       <c r="B179" t="n">
-        <v>1.26041985431246</v>
+        <v>-2.838736568920916</v>
       </c>
       <c r="C179" t="n">
-        <v>116.3517994350975</v>
+        <v>-189.2733299329059</v>
       </c>
     </row>
     <row r="180">
@@ -2400,10 +2400,10 @@
         <v>45894</v>
       </c>
       <c r="B180" t="n">
-        <v>-2.971456720512025</v>
+        <v>5.961907813686081</v>
       </c>
       <c r="C180" t="n">
-        <v>-276.9162782718743</v>
+        <v>421.2918133056244</v>
       </c>
     </row>
     <row r="181">
@@ -2411,10 +2411,10 @@
         <v>45895</v>
       </c>
       <c r="B181" t="n">
-        <v>-3.214915752024393</v>
+        <v>5.824674441863754</v>
       </c>
       <c r="C181" t="n">
-        <v>-323.2183399593014</v>
+        <v>467.3813865222174</v>
       </c>
     </row>
     <row r="182">
@@ -2422,10 +2422,10 @@
         <v>45896</v>
       </c>
       <c r="B182" t="n">
-        <v>-1.073321623254885</v>
+        <v>2.971077222322296</v>
       </c>
       <c r="C182" t="n">
-        <v>-34.67054603440095</v>
+        <v>107.4902512664757</v>
       </c>
     </row>
     <row r="183">
@@ -2433,10 +2433,10 @@
         <v>45897</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.5493903085023391</v>
+        <v>0.2538022158557318</v>
       </c>
       <c r="C183" t="n">
-        <v>-79.94530972151395</v>
+        <v>97.20322693518904</v>
       </c>
     </row>
     <row r="184">
@@ -2444,10 +2444,10 @@
         <v>45898</v>
       </c>
       <c r="B184" t="n">
-        <v>-3.447728371325899</v>
+        <v>5.893527119455492</v>
       </c>
       <c r="C184" t="n">
-        <v>-367.7195334943841</v>
+        <v>500.2571817280419</v>
       </c>
     </row>
     <row r="185">
@@ -2455,10 +2455,10 @@
         <v>45901</v>
       </c>
       <c r="B185" t="n">
-        <v>-3.696311447055777</v>
+        <v>6.035549210558008</v>
       </c>
       <c r="C185" t="n">
-        <v>-388.1368784976249</v>
+        <v>523.6631982238677</v>
       </c>
     </row>
     <row r="186">
@@ -2466,10 +2466,10 @@
         <v>45902</v>
       </c>
       <c r="B186" t="n">
-        <v>0.4279641229209725</v>
+        <v>-2.748042584160815</v>
       </c>
       <c r="C186" t="n">
-        <v>-1.170449286697265</v>
+        <v>-34.13077267235801</v>
       </c>
     </row>
     <row r="187">
@@ -2477,10 +2477,10 @@
         <v>45903</v>
       </c>
       <c r="B187" t="n">
-        <v>-3.025827823056569</v>
+        <v>5.417102083953507</v>
       </c>
       <c r="C187" t="n">
-        <v>-341.7725926716067</v>
+        <v>457.8870653964094</v>
       </c>
     </row>
     <row r="188">
@@ -2488,10 +2488,10 @@
         <v>45904</v>
       </c>
       <c r="B188" t="n">
-        <v>-2.251808256564417</v>
+        <v>5.108524388820856</v>
       </c>
       <c r="C188" t="n">
-        <v>-162.0055708038819</v>
+        <v>287.5263748857198</v>
       </c>
     </row>
     <row r="189">
@@ -2499,10 +2499,10 @@
         <v>45905</v>
       </c>
       <c r="B189" t="n">
-        <v>1.71065797356899</v>
+        <v>-4.748109455574225</v>
       </c>
       <c r="C189" t="n">
-        <v>129.982910370436</v>
+        <v>-232.2036027250637</v>
       </c>
     </row>
     <row r="190">
@@ -2510,10 +2510,10 @@
         <v>45908</v>
       </c>
       <c r="B190" t="n">
-        <v>-2.183515219080632</v>
+        <v>3.716816994757737</v>
       </c>
       <c r="C190" t="n">
-        <v>-204.242712261173</v>
+        <v>305.6469732032293</v>
       </c>
     </row>
     <row r="191">
@@ -2521,10 +2521,10 @@
         <v>45909</v>
       </c>
       <c r="B191" t="n">
-        <v>-4.738346932046585</v>
+        <v>8.76684784597575</v>
       </c>
       <c r="C191" t="n">
-        <v>-448.9418003292924</v>
+        <v>637.4625545139018</v>
       </c>
     </row>
     <row r="192">
@@ -2532,10 +2532,10 @@
         <v>45910</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.6844969033321631</v>
+        <v>0.8728456149897941</v>
       </c>
       <c r="C192" t="n">
-        <v>-77.53079925727296</v>
+        <v>118.9246936143749</v>
       </c>
     </row>
     <row r="193">
@@ -2543,10 +2543,10 @@
         <v>45911</v>
       </c>
       <c r="B193" t="n">
-        <v>-1.0614145930621</v>
+        <v>1.732540460996448</v>
       </c>
       <c r="C193" t="n">
-        <v>-158.9157735300428</v>
+        <v>199.7694550544519</v>
       </c>
     </row>
     <row r="194">
@@ -2554,10 +2554,10 @@
         <v>45912</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.6054606104436144</v>
+        <v>1.469708613335118</v>
       </c>
       <c r="C194" t="n">
-        <v>-95.60177700230948</v>
+        <v>125.141426893921</v>
       </c>
     </row>
     <row r="195">
@@ -2565,10 +2565,10 @@
         <v>45915</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.6212781170781537</v>
+        <v>1.089320712283038</v>
       </c>
       <c r="C195" t="n">
-        <v>-89.41543950722553</v>
+        <v>123.3070932945258</v>
       </c>
     </row>
     <row r="196">
@@ -2576,10 +2576,10 @@
         <v>45916</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.674177874516192</v>
+        <v>2.992709152342205</v>
       </c>
       <c r="C196" t="n">
-        <v>-180.699479830435</v>
+        <v>256.2881920651399</v>
       </c>
     </row>
     <row r="197">
@@ -2587,10 +2587,10 @@
         <v>45917</v>
       </c>
       <c r="B197" t="n">
-        <v>2.450071817647831</v>
+        <v>-4.609274151656233</v>
       </c>
       <c r="C197" t="n">
-        <v>242.3110138267404</v>
+        <v>-369.3920218154635</v>
       </c>
     </row>
     <row r="198">
@@ -2598,10 +2598,10 @@
         <v>45918</v>
       </c>
       <c r="B198" t="n">
-        <v>-2.534533387660709</v>
+        <v>4.908844075428929</v>
       </c>
       <c r="C198" t="n">
-        <v>-216.539332349985</v>
+        <v>353.1868421542956</v>
       </c>
     </row>
     <row r="199">
@@ -2609,10 +2609,10 @@
         <v>45919</v>
       </c>
       <c r="B199" t="n">
-        <v>-2.949629524719738</v>
+        <v>5.567801147676679</v>
       </c>
       <c r="C199" t="n">
-        <v>-300.5614977091316</v>
+        <v>426.1970046641331</v>
       </c>
     </row>
     <row r="200">
@@ -2620,10 +2620,10 @@
         <v>45922</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.9075042323142011</v>
+        <v>0.9622710526926119</v>
       </c>
       <c r="C200" t="n">
-        <v>-101.9983191039635</v>
+        <v>149.5578281837422</v>
       </c>
     </row>
     <row r="201">
@@ -2631,10 +2631,10 @@
         <v>45923</v>
       </c>
       <c r="B201" t="n">
-        <v>0.5834739280411964</v>
+        <v>-1.41900833932156</v>
       </c>
       <c r="C201" t="n">
-        <v>33.45287166531951</v>
+        <v>-60.50079691441974</v>
       </c>
     </row>
     <row r="202">
@@ -2642,10 +2642,10 @@
         <v>45924</v>
       </c>
       <c r="B202" t="n">
-        <v>-6.297547292174846</v>
+        <v>11.0512765989542</v>
       </c>
       <c r="C202" t="n">
-        <v>-600.3667854248064</v>
+        <v>817.8520601454475</v>
       </c>
     </row>
     <row r="203">
@@ -2653,10 +2653,10 @@
         <v>45925</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.3219742040988771</v>
+        <v>0.7362259429081353</v>
       </c>
       <c r="C203" t="n">
-        <v>-15.02075221332981</v>
+        <v>49.77972532824637</v>
       </c>
     </row>
     <row r="204">
@@ -2664,10 +2664,10 @@
         <v>45926</v>
       </c>
       <c r="B204" t="n">
-        <v>-2.531299790123219</v>
+        <v>4.326577434296061</v>
       </c>
       <c r="C204" t="n">
-        <v>-291.0468485516909</v>
+        <v>401.4136273427496</v>
       </c>
     </row>
     <row r="205">
@@ -2675,10 +2675,10 @@
         <v>45929</v>
       </c>
       <c r="B205" t="n">
-        <v>0.3954251139512736</v>
+        <v>-0.8449521183629511</v>
       </c>
       <c r="C205" t="n">
-        <v>61.61125962028012</v>
+        <v>-78.90020346572432</v>
       </c>
     </row>
     <row r="206">
@@ -2686,10 +2686,10 @@
         <v>45930</v>
       </c>
       <c r="B206" t="n">
-        <v>-2.914273539202701</v>
+        <v>4.886039880647311</v>
       </c>
       <c r="C206" t="n">
-        <v>-280.0315646028581</v>
+        <v>403.3606389476354</v>
       </c>
     </row>
     <row r="207">
@@ -2697,10 +2697,10 @@
         <v>45931</v>
       </c>
       <c r="B207" t="n">
-        <v>-1.710866044102786</v>
+        <v>2.988471084546784</v>
       </c>
       <c r="C207" t="n">
-        <v>-173.5838742535057</v>
+        <v>259.9877470697772</v>
       </c>
     </row>
     <row r="208">
@@ -2708,10 +2708,10 @@
         <v>45932</v>
       </c>
       <c r="B208" t="n">
-        <v>-2.087351741023841</v>
+        <v>3.104003412433172</v>
       </c>
       <c r="C208" t="n">
-        <v>-220.64580159369</v>
+        <v>310.8650491002873</v>
       </c>
     </row>
     <row r="209">
@@ -2719,10 +2719,10 @@
         <v>45933</v>
       </c>
       <c r="B209" t="n">
-        <v>-1.050806023613709</v>
+        <v>3.370879627725478</v>
       </c>
       <c r="C209" t="n">
-        <v>52.34555363891481</v>
+        <v>64.73072134693142</v>
       </c>
     </row>
     <row r="210">
@@ -2730,10 +2730,10 @@
         <v>45936</v>
       </c>
       <c r="B210" t="n">
-        <v>-1.634711930726086</v>
+        <v>3.196240509082936</v>
       </c>
       <c r="C210" t="n">
-        <v>-168.0624332609274</v>
+        <v>255.4811151929014</v>
       </c>
     </row>
     <row r="211">
@@ -2741,10 +2741,10 @@
         <v>45937</v>
       </c>
       <c r="B211" t="n">
-        <v>-2.070941604286682</v>
+        <v>3.638994954024823</v>
       </c>
       <c r="C211" t="n">
-        <v>-170.6412804933755</v>
+        <v>270.0099165459039</v>
       </c>
     </row>
     <row r="212">
@@ -2752,10 +2752,10 @@
         <v>45938</v>
       </c>
       <c r="B212" t="n">
-        <v>-2.276599590014448</v>
+        <v>3.930625717250782</v>
       </c>
       <c r="C212" t="n">
-        <v>-219.9816188983654</v>
+        <v>328.3053148071715</v>
       </c>
     </row>
     <row r="213">
@@ -2763,10 +2763,10 @@
         <v>45939</v>
       </c>
       <c r="B213" t="n">
-        <v>0.04782401717377755</v>
+        <v>-0.02741992539971154</v>
       </c>
       <c r="C213" t="n">
-        <v>-53.5421156197746</v>
+        <v>37.9291337373408</v>
       </c>
     </row>
     <row r="214">
@@ -2774,10 +2774,10 @@
         <v>45940</v>
       </c>
       <c r="B214" t="n">
-        <v>2.140759533504715</v>
+        <v>-5.131804971052766</v>
       </c>
       <c r="C214" t="n">
-        <v>164.8212778007998</v>
+        <v>-283.7888813654057</v>
       </c>
     </row>
     <row r="215">
@@ -2785,10 +2785,10 @@
         <v>45943</v>
       </c>
       <c r="B215" t="n">
-        <v>-2.07575330060977</v>
+        <v>3.728966559256195</v>
       </c>
       <c r="C215" t="n">
-        <v>-259.197479036761</v>
+        <v>345.7026475318119</v>
       </c>
     </row>
     <row r="216">
@@ -2796,10 +2796,10 @@
         <v>45944</v>
       </c>
       <c r="B216" t="n">
-        <v>0.6999949440902908</v>
+        <v>-1.000299505903742</v>
       </c>
       <c r="C216" t="n">
-        <v>32.70079078879211</v>
+        <v>-74.27982745634297</v>
       </c>
     </row>
     <row r="217">
@@ -2807,10 +2807,10 @@
         <v>45945</v>
       </c>
       <c r="B217" t="n">
-        <v>1.900657639780356</v>
+        <v>-3.659915325120792</v>
       </c>
       <c r="C217" t="n">
-        <v>154.7050442938688</v>
+        <v>-257.6264343449637</v>
       </c>
     </row>
     <row r="218">
@@ -2818,10 +2818,10 @@
         <v>45946</v>
       </c>
       <c r="B218" t="n">
-        <v>1.777282034853192</v>
+        <v>-2.713546783891437</v>
       </c>
       <c r="C218" t="n">
-        <v>207.0811629601205</v>
+        <v>-281.8606617417799</v>
       </c>
     </row>
     <row r="219">
@@ -2829,10 +2829,10 @@
         <v>45947</v>
       </c>
       <c r="B219" t="n">
-        <v>0.01502874014037494</v>
+        <v>-0.284450777415736</v>
       </c>
       <c r="C219" t="n">
-        <v>-12.23772593719135</v>
+        <v>15.14681914635043</v>
       </c>
     </row>
     <row r="220">
@@ -2840,10 +2840,10 @@
         <v>45950</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.9209903079025001</v>
+        <v>1.609877277578335</v>
       </c>
       <c r="C220" t="n">
-        <v>-114.8513023193756</v>
+        <v>157.4760619490542</v>
       </c>
     </row>
     <row r="221">
@@ -2851,10 +2851,10 @@
         <v>45951</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.753507707855174</v>
+        <v>1.849317727983196</v>
       </c>
       <c r="C221" t="n">
-        <v>-70.91952328162749</v>
+        <v>122.3588050316175</v>
       </c>
     </row>
     <row r="222">
@@ -2862,10 +2862,10 @@
         <v>45952</v>
       </c>
       <c r="B222" t="n">
-        <v>0.5999867806664464</v>
+        <v>-1.000780414999209</v>
       </c>
       <c r="C222" t="n">
-        <v>8.086341509576869</v>
+        <v>-41.96147568537875</v>
       </c>
     </row>
     <row r="223">
@@ -2873,10 +2873,10 @@
         <v>45953</v>
       </c>
       <c r="B223" t="n">
-        <v>-1.247159067284244</v>
+        <v>1.676208576146675</v>
       </c>
       <c r="C223" t="n">
-        <v>-145.6582821990026</v>
+        <v>209.0265855602048</v>
       </c>
     </row>
     <row r="224">
@@ -2884,10 +2884,10 @@
         <v>45954</v>
       </c>
       <c r="B224" t="n">
-        <v>-2.369563193156486</v>
+        <v>3.321138608992827</v>
       </c>
       <c r="C224" t="n">
-        <v>-290.7294766737102</v>
+        <v>379.010155990409</v>
       </c>
     </row>
     <row r="225">
@@ -2895,10 +2895,10 @@
         <v>45957</v>
       </c>
       <c r="B225" t="n">
-        <v>0.3522100428762269</v>
+        <v>-1.73291650174577</v>
       </c>
       <c r="C225" t="n">
-        <v>6.56604750801356</v>
+        <v>-38.18064706636174</v>
       </c>
     </row>
     <row r="226">
@@ -2906,10 +2906,10 @@
         <v>45958</v>
       </c>
       <c r="B226" t="n">
-        <v>-2.581426835899712</v>
+        <v>5.549085036140089</v>
       </c>
       <c r="C226" t="n">
-        <v>-242.0356259351008</v>
+        <v>368.0370547255938</v>
       </c>
     </row>
     <row r="227">
@@ -2917,10 +2917,10 @@
         <v>45959</v>
       </c>
       <c r="B227" t="n">
-        <v>-1.721717037881546</v>
+        <v>3.180627803702885</v>
       </c>
       <c r="C227" t="n">
-        <v>-153.1938253848064</v>
+        <v>245.8187078142313</v>
       </c>
     </row>
     <row r="228">
@@ -2928,10 +2928,10 @@
         <v>45960</v>
       </c>
       <c r="B228" t="n">
-        <v>-4.5351475842247</v>
+        <v>7.823989228847082</v>
       </c>
       <c r="C228" t="n">
-        <v>-451.8358770790173</v>
+        <v>613.8902923679681</v>
       </c>
     </row>
     <row r="229">
@@ -2939,10 +2939,10 @@
         <v>45961</v>
       </c>
       <c r="B229" t="n">
-        <v>-2.98838231108765</v>
+        <v>5.836859938669091</v>
       </c>
       <c r="C229" t="n">
-        <v>-306.0832446904229</v>
+        <v>443.4762158825372</v>
       </c>
     </row>
     <row r="230">
@@ -2950,10 +2950,10 @@
         <v>45964</v>
       </c>
       <c r="B230" t="n">
-        <v>-2.346188083418166</v>
+        <v>3.43315070150887</v>
       </c>
       <c r="C230" t="n">
-        <v>-272.4953686469079</v>
+        <v>357.6157814963842</v>
       </c>
     </row>
     <row r="231">
@@ -2961,10 +2961,10 @@
         <v>45965</v>
       </c>
       <c r="B231" t="n">
-        <v>-3.681116842820394</v>
+        <v>7.270013278461952</v>
       </c>
       <c r="C231" t="n">
-        <v>-321.3565354468044</v>
+        <v>491.6776883986567</v>
       </c>
     </row>
     <row r="232">
@@ -2972,10 +2972,10 @@
         <v>45966</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.3306020568159274</v>
+        <v>1.308442695986503</v>
       </c>
       <c r="C232" t="n">
-        <v>-66.37704619112628</v>
+        <v>61.28838695357823</v>
       </c>
     </row>
     <row r="233">
@@ -2983,10 +2983,10 @@
         <v>45967</v>
       </c>
       <c r="B233" t="n">
-        <v>-1.907894865084573</v>
+        <v>4.051298472608657</v>
       </c>
       <c r="C233" t="n">
-        <v>-125.8721739716102</v>
+        <v>245.5816039807152</v>
       </c>
     </row>
     <row r="234">
@@ -2994,10 +2994,10 @@
         <v>45968</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.8868557723981649</v>
+        <v>2.416840025287019</v>
       </c>
       <c r="C234" t="n">
-        <v>-102.4997319491659</v>
+        <v>153.0709854543665</v>
       </c>
     </row>
     <row r="235">
@@ -3005,10 +3005,10 @@
         <v>45971</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.9922395903927509</v>
+        <v>1.948384557771417</v>
       </c>
       <c r="C235" t="n">
-        <v>-62.11129775327263</v>
+        <v>127.9370011553645</v>
       </c>
     </row>
     <row r="236">
@@ -3016,10 +3016,10 @@
         <v>45972</v>
       </c>
       <c r="B236" t="n">
-        <v>0.6309887456354399</v>
+        <v>-1.709864556998218</v>
       </c>
       <c r="C236" t="n">
-        <v>8.577255125309057</v>
+        <v>-49.88295781347892</v>
       </c>
     </row>
     <row r="237">
@@ -3027,10 +3027,10 @@
         <v>45973</v>
       </c>
       <c r="B237" t="n">
-        <v>-1.406785027630518</v>
+        <v>3.265378975845286</v>
       </c>
       <c r="C237" t="n">
-        <v>-132.3132660627956</v>
+        <v>206.7109390359292</v>
       </c>
     </row>
     <row r="238">
@@ -3038,10 +3038,10 @@
         <v>45974</v>
       </c>
       <c r="B238" t="n">
-        <v>1.461067756312908</v>
+        <v>-2.443912347038425</v>
       </c>
       <c r="C238" t="n">
-        <v>170.4405805435204</v>
+        <v>-224.9120071084492</v>
       </c>
     </row>
     <row r="239">
@@ -3049,10 +3049,10 @@
         <v>45975</v>
       </c>
       <c r="B239" t="n">
-        <v>1.291498772492993</v>
+        <v>-1.563809605014748</v>
       </c>
       <c r="C239" t="n">
-        <v>92.27849266572662</v>
+        <v>-162.886683378117</v>
       </c>
     </row>
     <row r="240">
@@ -3060,10 +3060,10 @@
         <v>45978</v>
       </c>
       <c r="B240" t="n">
-        <v>-0.5350855210267859</v>
+        <v>1.843483591206507</v>
       </c>
       <c r="C240" t="n">
-        <v>-61.0786936881163</v>
+        <v>93.6001951241787</v>
       </c>
     </row>
     <row r="241">
@@ -3071,10 +3071,10 @@
         <v>45979</v>
       </c>
       <c r="B241" t="n">
-        <v>-1.573354455210081</v>
+        <v>3.027538313652547</v>
       </c>
       <c r="C241" t="n">
-        <v>-189.3387479898957</v>
+        <v>262.7061905234667</v>
       </c>
     </row>
     <row r="242">
@@ -3082,10 +3082,10 @@
         <v>45980</v>
       </c>
       <c r="B242" t="n">
-        <v>-3.389281172677512</v>
+        <v>6.872611515165445</v>
       </c>
       <c r="C242" t="n">
-        <v>-232.907570436641</v>
+        <v>408.332169196344</v>
       </c>
     </row>
     <row r="243">
@@ -3093,10 +3093,10 @@
         <v>45982</v>
       </c>
       <c r="B243" t="n">
-        <v>1.104153806226211</v>
+        <v>-2.117608017228803</v>
       </c>
       <c r="C243" t="n">
-        <v>47.0903075467972</v>
+        <v>-117.338962228998</v>
       </c>
     </row>
     <row r="244">
@@ -3104,10 +3104,10 @@
         <v>45985</v>
       </c>
       <c r="B244" t="n">
-        <v>-2.451338484446031</v>
+        <v>4.288994296934245</v>
       </c>
       <c r="C244" t="n">
-        <v>-245.7330051709098</v>
+        <v>359.4580191471755</v>
       </c>
     </row>
     <row r="245">
@@ -3115,10 +3115,10 @@
         <v>45986</v>
       </c>
       <c r="B245" t="n">
-        <v>0.3633446751339967</v>
+        <v>-1.141839571348519</v>
       </c>
       <c r="C245" t="n">
-        <v>-18.29752809121415</v>
+        <v>-11.91888866335373</v>
       </c>
     </row>
     <row r="246">
@@ -3126,10 +3126,10 @@
         <v>45987</v>
       </c>
       <c r="B246" t="n">
-        <v>-1.505049851505921</v>
+        <v>3.433741458292041</v>
       </c>
       <c r="C246" t="n">
-        <v>-94.35124907615327</v>
+        <v>179.5723565919373</v>
       </c>
     </row>
     <row r="247">
@@ -3137,10 +3137,10 @@
         <v>45988</v>
       </c>
       <c r="B247" t="n">
-        <v>-7.009968677461611</v>
+        <v>11.78332167847231</v>
       </c>
       <c r="C247" t="n">
-        <v>-733.0934107153095</v>
+        <v>928.614040202858</v>
       </c>
     </row>
     <row r="248">
@@ -3148,10 +3148,10 @@
         <v>45989</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.217288329701981</v>
+        <v>2.425987369426313</v>
       </c>
       <c r="C248" t="n">
-        <v>-148.4537363691403</v>
+        <v>213.0877341315795</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/scores_LQdFPC_vs_dFPC.xlsx
+++ b/data/processed/scores_LQdFPC_vs_dFPC.xlsx
@@ -442,10 +442,10 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>-2.006633394345457</v>
+        <v>0.2821326660627726</v>
       </c>
       <c r="C2" t="n">
-        <v>-328.6022003258042</v>
+        <v>-676.9270678869931</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>-1.69863111722018</v>
+        <v>0.1361968425291906</v>
       </c>
       <c r="C3" t="n">
-        <v>-97.69839097279157</v>
+        <v>-233.1488990349846</v>
       </c>
     </row>
     <row r="4">
@@ -464,10 +464,10 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7504726312310206</v>
+        <v>0.1192486583423305</v>
       </c>
       <c r="C4" t="n">
-        <v>-80.09310097907786</v>
+        <v>-272.6790261305664</v>
       </c>
     </row>
     <row r="5">
@@ -475,10 +475,10 @@
         <v>45631</v>
       </c>
       <c r="B5" t="n">
-        <v>2.214950382811713</v>
+        <v>-0.01981220149593619</v>
       </c>
       <c r="C5" t="n">
-        <v>146.7734941673269</v>
+        <v>-47.38902710729386</v>
       </c>
     </row>
     <row r="6">
@@ -486,10 +486,10 @@
         <v>45632</v>
       </c>
       <c r="B6" t="n">
-        <v>1.975190185627391</v>
+        <v>-0.01893373355113359</v>
       </c>
       <c r="C6" t="n">
-        <v>93.86544482765854</v>
+        <v>6.089921835278679</v>
       </c>
     </row>
     <row r="7">
@@ -497,10 +497,10 @@
         <v>45635</v>
       </c>
       <c r="B7" t="n">
-        <v>-1.115379130520231</v>
+        <v>0.05121361916942991</v>
       </c>
       <c r="C7" t="n">
-        <v>-109.035078892553</v>
+        <v>-136.216917008579</v>
       </c>
     </row>
     <row r="8">
@@ -508,10 +508,10 @@
         <v>45636</v>
       </c>
       <c r="B8" t="n">
-        <v>1.806403463695434</v>
+        <v>-0.05841344262343538</v>
       </c>
       <c r="C8" t="n">
-        <v>108.3259000436015</v>
+        <v>28.25328462825348</v>
       </c>
     </row>
     <row r="9">
@@ -519,10 +519,10 @@
         <v>45637</v>
       </c>
       <c r="B9" t="n">
-        <v>-10.17432154652104</v>
+        <v>0.2599922744982764</v>
       </c>
       <c r="C9" t="n">
-        <v>-541.3536573989444</v>
+        <v>-359.2283415903883</v>
       </c>
     </row>
     <row r="10">
@@ -530,10 +530,10 @@
         <v>45638</v>
       </c>
       <c r="B10" t="n">
-        <v>-2.531870838538045</v>
+        <v>0.1355053255416902</v>
       </c>
       <c r="C10" t="n">
-        <v>-224.0278382636907</v>
+        <v>-320.2362241951163</v>
       </c>
     </row>
     <row r="11">
@@ -541,10 +541,10 @@
         <v>45639</v>
       </c>
       <c r="B11" t="n">
-        <v>2.258735389985342</v>
+        <v>0.004888165429490229</v>
       </c>
       <c r="C11" t="n">
-        <v>108.3352450268928</v>
+        <v>-50.73137407460567</v>
       </c>
     </row>
     <row r="12">
@@ -552,10 +552,10 @@
         <v>45642</v>
       </c>
       <c r="B12" t="n">
-        <v>2.622930471071168</v>
+        <v>-0.03702116916296824</v>
       </c>
       <c r="C12" t="n">
-        <v>126.265807067926</v>
+        <v>-14.79452406261914</v>
       </c>
     </row>
     <row r="13">
@@ -563,10 +563,10 @@
         <v>45643</v>
       </c>
       <c r="B13" t="n">
-        <v>-6.211999923070231</v>
+        <v>0.3439159407446131</v>
       </c>
       <c r="C13" t="n">
-        <v>-521.7983519036489</v>
+        <v>-484.7518795282328</v>
       </c>
     </row>
     <row r="14">
@@ -574,10 +574,10 @@
         <v>45644</v>
       </c>
       <c r="B14" t="n">
-        <v>-4.252572568769071</v>
+        <v>0.2708511722892337</v>
       </c>
       <c r="C14" t="n">
-        <v>-467.5759632629653</v>
+        <v>-564.8400564889067</v>
       </c>
     </row>
     <row r="15">
@@ -585,10 +585,10 @@
         <v>45645</v>
       </c>
       <c r="B15" t="n">
-        <v>-2.595676141199938</v>
+        <v>0.1767620045796244</v>
       </c>
       <c r="C15" t="n">
-        <v>-216.4845225195966</v>
+        <v>-287.2180837760146</v>
       </c>
     </row>
     <row r="16">
@@ -596,10 +596,10 @@
         <v>45646</v>
       </c>
       <c r="B16" t="n">
-        <v>-2.721747771055405</v>
+        <v>0.2098957736521708</v>
       </c>
       <c r="C16" t="n">
-        <v>-210.8981452347402</v>
+        <v>-277.5903206458269</v>
       </c>
     </row>
     <row r="17">
@@ -607,10 +607,10 @@
         <v>45649</v>
       </c>
       <c r="B17" t="n">
-        <v>1.143240353202331</v>
+        <v>0.06929235339076263</v>
       </c>
       <c r="C17" t="n">
-        <v>85.36558777659761</v>
+        <v>-108.0187343611274</v>
       </c>
     </row>
     <row r="18">
@@ -618,10 +618,10 @@
         <v>45652</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5154314617883302</v>
+        <v>0.06392672689680237</v>
       </c>
       <c r="C18" t="n">
-        <v>-15.11334747364093</v>
+        <v>-96.76492595564167</v>
       </c>
     </row>
     <row r="19">
@@ -629,10 +629,10 @@
         <v>45653</v>
       </c>
       <c r="B19" t="n">
-        <v>-1.931358322290735</v>
+        <v>0.1740745786201389</v>
       </c>
       <c r="C19" t="n">
-        <v>-291.123933355711</v>
+        <v>-401.7551196757236</v>
       </c>
     </row>
     <row r="20">
@@ -640,10 +640,10 @@
         <v>45656</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9745828131046468</v>
+        <v>0.08742391616275701</v>
       </c>
       <c r="C20" t="n">
-        <v>-99.28423357764348</v>
+        <v>-279.1460972415647</v>
       </c>
     </row>
     <row r="21">
@@ -651,10 +651,10 @@
         <v>45659</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.030494608216963</v>
+        <v>0.2029313628432965</v>
       </c>
       <c r="C21" t="n">
-        <v>-333.4453080102134</v>
+        <v>-392.0548147705115</v>
       </c>
     </row>
     <row r="22">
@@ -662,10 +662,10 @@
         <v>45660</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.05661025446422672</v>
+        <v>0.03769517485637008</v>
       </c>
       <c r="C22" t="n">
-        <v>40.66243161741001</v>
+        <v>-75.3733446890506</v>
       </c>
     </row>
     <row r="23">
@@ -673,10 +673,10 @@
         <v>45663</v>
       </c>
       <c r="B23" t="n">
-        <v>-4.932690479768279</v>
+        <v>0.1978569353714391</v>
       </c>
       <c r="C23" t="n">
-        <v>-276.3264758777318</v>
+        <v>-339.5594929120733</v>
       </c>
     </row>
     <row r="24">
@@ -684,10 +684,10 @@
         <v>45664</v>
       </c>
       <c r="B24" t="n">
-        <v>0.7915936178563658</v>
+        <v>0.01982664730358508</v>
       </c>
       <c r="C24" t="n">
-        <v>50.06755228476621</v>
+        <v>-4.107225829215239</v>
       </c>
     </row>
     <row r="25">
@@ -695,10 +695,10 @@
         <v>45665</v>
       </c>
       <c r="B25" t="n">
-        <v>1.101268170514453</v>
+        <v>-0.0133778832738144</v>
       </c>
       <c r="C25" t="n">
-        <v>67.94351646475478</v>
+        <v>6.200189376194305</v>
       </c>
     </row>
     <row r="26">
@@ -706,10 +706,10 @@
         <v>45666</v>
       </c>
       <c r="B26" t="n">
-        <v>4.56079544404723</v>
+        <v>-0.1482171917142642</v>
       </c>
       <c r="C26" t="n">
-        <v>300.243849493477</v>
+        <v>234.1661645421092</v>
       </c>
     </row>
     <row r="27">
@@ -717,10 +717,10 @@
         <v>45667</v>
       </c>
       <c r="B27" t="n">
-        <v>-2.659115716978549</v>
+        <v>0.0522318503530357</v>
       </c>
       <c r="C27" t="n">
-        <v>-145.2523986192917</v>
+        <v>-61.14920160868949</v>
       </c>
     </row>
     <row r="28">
@@ -728,10 +728,10 @@
         <v>45670</v>
       </c>
       <c r="B28" t="n">
-        <v>1.290384880384979</v>
+        <v>-0.08456143473844764</v>
       </c>
       <c r="C28" t="n">
-        <v>87.79410782460741</v>
+        <v>151.6487967834051</v>
       </c>
     </row>
     <row r="29">
@@ -739,10 +739,10 @@
         <v>45671</v>
       </c>
       <c r="B29" t="n">
-        <v>-4.944617096165411</v>
+        <v>0.1468728013142586</v>
       </c>
       <c r="C29" t="n">
-        <v>-347.7932960828746</v>
+        <v>-220.313064628663</v>
       </c>
     </row>
     <row r="30">
@@ -750,10 +750,10 @@
         <v>45672</v>
       </c>
       <c r="B30" t="n">
-        <v>-2.662382922769793</v>
+        <v>0.09087978119143962</v>
       </c>
       <c r="C30" t="n">
-        <v>-174.0164363969481</v>
+        <v>-157.3602203054787</v>
       </c>
     </row>
     <row r="31">
@@ -761,10 +761,10 @@
         <v>45673</v>
       </c>
       <c r="B31" t="n">
-        <v>2.353367519817517</v>
+        <v>-0.008435141946986134</v>
       </c>
       <c r="C31" t="n">
-        <v>77.3691809374192</v>
+        <v>-42.1561380582426</v>
       </c>
     </row>
     <row r="32">
@@ -772,10 +772,10 @@
         <v>45674</v>
       </c>
       <c r="B32" t="n">
-        <v>1.782504896803305</v>
+        <v>-0.03226942660009176</v>
       </c>
       <c r="C32" t="n">
-        <v>102.5210588480534</v>
+        <v>32.97607909799304</v>
       </c>
     </row>
     <row r="33">
@@ -783,10 +783,10 @@
         <v>45677</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2234111220570207</v>
+        <v>0.05578407660744766</v>
       </c>
       <c r="C33" t="n">
-        <v>-81.1229799598413</v>
+        <v>-227.2321051801969</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         <v>45678</v>
       </c>
       <c r="B34" t="n">
-        <v>1.775756747283255</v>
+        <v>-0.01470268120688359</v>
       </c>
       <c r="C34" t="n">
-        <v>34.73834302481301</v>
+        <v>-108.5675569309455</v>
       </c>
     </row>
     <row r="35">
@@ -805,10 +805,10 @@
         <v>45679</v>
       </c>
       <c r="B35" t="n">
-        <v>2.275386396176594</v>
+        <v>-0.08126749938261685</v>
       </c>
       <c r="C35" t="n">
-        <v>111.2090301577908</v>
+        <v>1.291796108375347</v>
       </c>
     </row>
     <row r="36">
@@ -816,10 +816,10 @@
         <v>45680</v>
       </c>
       <c r="B36" t="n">
-        <v>-2.463367900363986</v>
+        <v>0.04412088233277407</v>
       </c>
       <c r="C36" t="n">
-        <v>-178.3176470499194</v>
+        <v>-201.5146234671632</v>
       </c>
     </row>
     <row r="37">
@@ -827,10 +827,10 @@
         <v>45681</v>
       </c>
       <c r="B37" t="n">
-        <v>3.165223146724338</v>
+        <v>-0.05124189730017822</v>
       </c>
       <c r="C37" t="n">
-        <v>98.40190469910445</v>
+        <v>-130.392906728963</v>
       </c>
     </row>
     <row r="38">
@@ -838,10 +838,10 @@
         <v>45684</v>
       </c>
       <c r="B38" t="n">
-        <v>-1.140911884744513</v>
+        <v>0.04036173387015034</v>
       </c>
       <c r="C38" t="n">
-        <v>-107.1259905657375</v>
+        <v>-164.8671439798531</v>
       </c>
     </row>
     <row r="39">
@@ -849,10 +849,10 @@
         <v>45685</v>
       </c>
       <c r="B39" t="n">
-        <v>3.74151772593736</v>
+        <v>-0.1515537826046625</v>
       </c>
       <c r="C39" t="n">
-        <v>276.6851884559315</v>
+        <v>185.4068817235712</v>
       </c>
     </row>
     <row r="40">
@@ -860,10 +860,10 @@
         <v>45686</v>
       </c>
       <c r="B40" t="n">
-        <v>1.501014622777574</v>
+        <v>-0.02691825941640765</v>
       </c>
       <c r="C40" t="n">
-        <v>-32.49753838015749</v>
+        <v>-187.8086973220626</v>
       </c>
     </row>
     <row r="41">
@@ -871,10 +871,10 @@
         <v>45687</v>
       </c>
       <c r="B41" t="n">
-        <v>-3.029108896171412</v>
+        <v>0.06600774346988864</v>
       </c>
       <c r="C41" t="n">
-        <v>-184.5071378762299</v>
+        <v>-116.7250578797424</v>
       </c>
     </row>
     <row r="42">
@@ -882,10 +882,10 @@
         <v>45688</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7204089894531632</v>
+        <v>0.01511102398391146</v>
       </c>
       <c r="C42" t="n">
-        <v>-64.69888794515271</v>
+        <v>-159.732559561699</v>
       </c>
     </row>
     <row r="43">
@@ -893,10 +893,10 @@
         <v>45691</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.05176207369789</v>
+        <v>0.09782089499673959</v>
       </c>
       <c r="C43" t="n">
-        <v>-236.1543575935328</v>
+        <v>-331.2811509465358</v>
       </c>
     </row>
     <row r="44">
@@ -904,10 +904,10 @@
         <v>45692</v>
       </c>
       <c r="B44" t="n">
-        <v>-0.6765495811758773</v>
+        <v>0.02117344989617493</v>
       </c>
       <c r="C44" t="n">
-        <v>8.823564711069727</v>
+        <v>-51.4521125474842</v>
       </c>
     </row>
     <row r="45">
@@ -915,10 +915,10 @@
         <v>45693</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.653087522249954</v>
+        <v>0.08875864919972205</v>
       </c>
       <c r="C45" t="n">
-        <v>-102.189788985628</v>
+        <v>-242.527401645918</v>
       </c>
     </row>
     <row r="46">
@@ -926,10 +926,10 @@
         <v>45694</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1061569610706832</v>
+        <v>0.06106520671047466</v>
       </c>
       <c r="C46" t="n">
-        <v>-48.55771526517876</v>
+        <v>-177.5822493179261</v>
       </c>
     </row>
     <row r="47">
@@ -937,10 +937,10 @@
         <v>45695</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2480358355610003</v>
+        <v>0.1014755593370867</v>
       </c>
       <c r="C47" t="n">
-        <v>-131.5868716115598</v>
+        <v>-328.4423441292449</v>
       </c>
     </row>
     <row r="48">
@@ -948,10 +948,10 @@
         <v>45698</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.0331516850894781</v>
+        <v>-0.01055038972535258</v>
       </c>
       <c r="C48" t="n">
-        <v>47.55528503260076</v>
+        <v>-11.51747598817533</v>
       </c>
     </row>
     <row r="49">
@@ -959,10 +959,10 @@
         <v>45699</v>
       </c>
       <c r="B49" t="n">
-        <v>2.347662042862233</v>
+        <v>-0.1425587040518214</v>
       </c>
       <c r="C49" t="n">
-        <v>274.8431160674321</v>
+        <v>309.6182464516298</v>
       </c>
     </row>
     <row r="50">
@@ -970,10 +970,10 @@
         <v>45700</v>
       </c>
       <c r="B50" t="n">
-        <v>-5.589571586281059</v>
+        <v>0.1749658111797474</v>
       </c>
       <c r="C50" t="n">
-        <v>-362.9402351690296</v>
+        <v>-290.6012175669017</v>
       </c>
     </row>
     <row r="51">
@@ -981,10 +981,10 @@
         <v>45701</v>
       </c>
       <c r="B51" t="n">
-        <v>1.770188509559536</v>
+        <v>-0.02861243290079307</v>
       </c>
       <c r="C51" t="n">
-        <v>75.75299330868499</v>
+        <v>-52.44853485098707</v>
       </c>
     </row>
     <row r="52">
@@ -992,10 +992,10 @@
         <v>45702</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.02777332397786845</v>
+        <v>-0.06924915619565263</v>
       </c>
       <c r="C52" t="n">
-        <v>69.81810559970339</v>
+        <v>208.3386821205462</v>
       </c>
     </row>
     <row r="53">
@@ -1003,10 +1003,10 @@
         <v>45705</v>
       </c>
       <c r="B53" t="n">
-        <v>6.452506446573011</v>
+        <v>-0.215573342358935</v>
       </c>
       <c r="C53" t="n">
-        <v>408.5945935306785</v>
+        <v>346.4830966379295</v>
       </c>
     </row>
     <row r="54">
@@ -1014,10 +1014,10 @@
         <v>45706</v>
       </c>
       <c r="B54" t="n">
-        <v>2.955630800838541</v>
+        <v>-0.1660320771069764</v>
       </c>
       <c r="C54" t="n">
-        <v>257.2634001902556</v>
+        <v>283.6316645511267</v>
       </c>
     </row>
     <row r="55">
@@ -1025,10 +1025,10 @@
         <v>45707</v>
       </c>
       <c r="B55" t="n">
-        <v>2.670345928681336</v>
+        <v>-0.1718566939349986</v>
       </c>
       <c r="C55" t="n">
-        <v>192.1365096273763</v>
+        <v>327.0014700914956</v>
       </c>
     </row>
     <row r="56">
@@ -1036,10 +1036,10 @@
         <v>45708</v>
       </c>
       <c r="B56" t="n">
-        <v>3.011939780069228</v>
+        <v>-0.1972239168941018</v>
       </c>
       <c r="C56" t="n">
-        <v>218.8931466396187</v>
+        <v>323.5215830364856</v>
       </c>
     </row>
     <row r="57">
@@ -1047,10 +1047,10 @@
         <v>45709</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.4055652861896114</v>
+        <v>-0.06212920224911111</v>
       </c>
       <c r="C57" t="n">
-        <v>-79.18647893273169</v>
+        <v>67.87662115209838</v>
       </c>
     </row>
     <row r="58">
@@ -1058,10 +1058,10 @@
         <v>45712</v>
       </c>
       <c r="B58" t="n">
-        <v>0.71036984354651</v>
+        <v>-0.070996077968789</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3877541727016605</v>
+        <v>108.0023111807123</v>
       </c>
     </row>
     <row r="59">
@@ -1069,10 +1069,10 @@
         <v>45713</v>
       </c>
       <c r="B59" t="n">
-        <v>-0.1585156079680797</v>
+        <v>0.0620966873640305</v>
       </c>
       <c r="C59" t="n">
-        <v>-168.6790059422137</v>
+        <v>-221.3894753020504</v>
       </c>
     </row>
     <row r="60">
@@ -1080,10 +1080,10 @@
         <v>45714</v>
       </c>
       <c r="B60" t="n">
-        <v>2.370663670180016</v>
+        <v>-0.02983243334724842</v>
       </c>
       <c r="C60" t="n">
-        <v>63.12773516219679</v>
+        <v>-79.14499656111157</v>
       </c>
     </row>
     <row r="61">
@@ -1091,10 +1091,10 @@
         <v>45715</v>
       </c>
       <c r="B61" t="n">
-        <v>0.3477280193383002</v>
+        <v>0.01991771226714071</v>
       </c>
       <c r="C61" t="n">
-        <v>-10.42574485403287</v>
+        <v>-150.290815945588</v>
       </c>
     </row>
     <row r="62">
@@ -1102,10 +1102,10 @@
         <v>45716</v>
       </c>
       <c r="B62" t="n">
-        <v>-1.760075572321569</v>
+        <v>0.06790491990376839</v>
       </c>
       <c r="C62" t="n">
-        <v>-146.0516917983404</v>
+        <v>-158.8920489962713</v>
       </c>
     </row>
     <row r="63">
@@ -1113,10 +1113,10 @@
         <v>45722</v>
       </c>
       <c r="B63" t="n">
-        <v>-7.752262985699446</v>
+        <v>0.3064156146981225</v>
       </c>
       <c r="C63" t="n">
-        <v>-565.1662193274753</v>
+        <v>-578.0399511697548</v>
       </c>
     </row>
     <row r="64">
@@ -1124,10 +1124,10 @@
         <v>45723</v>
       </c>
       <c r="B64" t="n">
-        <v>-5.797329400334047</v>
+        <v>0.2430958551167186</v>
       </c>
       <c r="C64" t="n">
-        <v>-371.3944859431891</v>
+        <v>-386.0777860776172</v>
       </c>
     </row>
     <row r="65">
@@ -1135,10 +1135,10 @@
         <v>45726</v>
       </c>
       <c r="B65" t="n">
-        <v>-2.976787387531346</v>
+        <v>0.2011295486047781</v>
       </c>
       <c r="C65" t="n">
-        <v>-219.303176590108</v>
+        <v>-342.4187621321535</v>
       </c>
     </row>
     <row r="66">
@@ -1146,10 +1146,10 @@
         <v>45727</v>
       </c>
       <c r="B66" t="n">
-        <v>0.4605349168169706</v>
+        <v>0.07114924255110286</v>
       </c>
       <c r="C66" t="n">
-        <v>44.94550742134248</v>
+        <v>-134.9525756342203</v>
       </c>
     </row>
     <row r="67">
@@ -1157,10 +1157,10 @@
         <v>45728</v>
       </c>
       <c r="B67" t="n">
-        <v>-1.656979367162924</v>
+        <v>0.2306556863333392</v>
       </c>
       <c r="C67" t="n">
-        <v>-250.0414212841408</v>
+        <v>-426.9736118060816</v>
       </c>
     </row>
     <row r="68">
@@ -1168,10 +1168,10 @@
         <v>45729</v>
       </c>
       <c r="B68" t="n">
-        <v>1.359644181725009</v>
+        <v>-0.02441231514599105</v>
       </c>
       <c r="C68" t="n">
-        <v>144.9203547797435</v>
+        <v>54.32413104468364</v>
       </c>
     </row>
     <row r="69">
@@ -1179,10 +1179,10 @@
         <v>45730</v>
       </c>
       <c r="B69" t="n">
-        <v>0.4990001035693637</v>
+        <v>0.01386670857730008</v>
       </c>
       <c r="C69" t="n">
-        <v>-6.396486326737774</v>
+        <v>-23.51667729037399</v>
       </c>
     </row>
     <row r="70">
@@ -1190,10 +1190,10 @@
         <v>45733</v>
       </c>
       <c r="B70" t="n">
-        <v>1.550457094232317</v>
+        <v>-0.06914458150291564</v>
       </c>
       <c r="C70" t="n">
-        <v>111.1770589178681</v>
+        <v>60.11405994930151</v>
       </c>
     </row>
     <row r="71">
@@ -1201,10 +1201,10 @@
         <v>45734</v>
       </c>
       <c r="B71" t="n">
-        <v>-3.053573027047911</v>
+        <v>0.1024698719115919</v>
       </c>
       <c r="C71" t="n">
-        <v>-216.5236762832164</v>
+        <v>-134.7805842445453</v>
       </c>
     </row>
     <row r="72">
@@ -1212,10 +1212,10 @@
         <v>45735</v>
       </c>
       <c r="B72" t="n">
-        <v>-0.6237326299969035</v>
+        <v>0.01835448866583714</v>
       </c>
       <c r="C72" t="n">
-        <v>-71.06190635760387</v>
+        <v>-3.962897109693724</v>
       </c>
     </row>
     <row r="73">
@@ -1223,10 +1223,10 @@
         <v>45736</v>
       </c>
       <c r="B73" t="n">
-        <v>3.398186620089535</v>
+        <v>-0.143607191595945</v>
       </c>
       <c r="C73" t="n">
-        <v>264.5987571779311</v>
+        <v>291.2263294715491</v>
       </c>
     </row>
     <row r="74">
@@ -1234,10 +1234,10 @@
         <v>45737</v>
       </c>
       <c r="B74" t="n">
-        <v>3.604777679140551</v>
+        <v>-0.1712054580283473</v>
       </c>
       <c r="C74" t="n">
-        <v>277.7418888239928</v>
+        <v>310.1037527698296</v>
       </c>
     </row>
     <row r="75">
@@ -1245,10 +1245,10 @@
         <v>45740</v>
       </c>
       <c r="B75" t="n">
-        <v>0.4647685545256413</v>
+        <v>-0.1182295638093926</v>
       </c>
       <c r="C75" t="n">
-        <v>139.7042782973037</v>
+        <v>246.9947190494842</v>
       </c>
     </row>
     <row r="76">
@@ -1256,10 +1256,10 @@
         <v>45741</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.2591947808190816</v>
+        <v>-0.09741646801408908</v>
       </c>
       <c r="C76" t="n">
-        <v>34.48051543592364</v>
+        <v>233.2677876604538</v>
       </c>
     </row>
     <row r="77">
@@ -1267,10 +1267,10 @@
         <v>45742</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2155148177854758</v>
+        <v>-0.1038033326342487</v>
       </c>
       <c r="C77" t="n">
-        <v>39.17413368739821</v>
+        <v>266.9107736138578</v>
       </c>
     </row>
     <row r="78">
@@ -1278,10 +1278,10 @@
         <v>45743</v>
       </c>
       <c r="B78" t="n">
-        <v>-2.556291150369133</v>
+        <v>-0.02986273542859296</v>
       </c>
       <c r="C78" t="n">
-        <v>-71.91185125195338</v>
+        <v>93.35570137375127</v>
       </c>
     </row>
     <row r="79">
@@ -1289,10 +1289,10 @@
         <v>45744</v>
       </c>
       <c r="B79" t="n">
-        <v>-1.91220041520139</v>
+        <v>0.01456611950641527</v>
       </c>
       <c r="C79" t="n">
-        <v>-88.05980303965121</v>
+        <v>65.15186597531286</v>
       </c>
     </row>
     <row r="80">
@@ -1300,10 +1300,10 @@
         <v>45747</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.04933596607231816</v>
+        <v>-0.02058057452887709</v>
       </c>
       <c r="C80" t="n">
-        <v>9.036423128350005</v>
+        <v>29.65780109429744</v>
       </c>
     </row>
     <row r="81">
@@ -1311,10 +1311,10 @@
         <v>45748</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.4475562715287616</v>
+        <v>-0.006244022350382373</v>
       </c>
       <c r="C81" t="n">
-        <v>1.548218196653885</v>
+        <v>78.41844208216416</v>
       </c>
     </row>
     <row r="82">
@@ -1322,10 +1322,10 @@
         <v>45749</v>
       </c>
       <c r="B82" t="n">
-        <v>1.854048774242071</v>
+        <v>-0.1005484962078494</v>
       </c>
       <c r="C82" t="n">
-        <v>187.1342835848201</v>
+        <v>157.3001818679755</v>
       </c>
     </row>
     <row r="83">
@@ -1333,10 +1333,10 @@
         <v>45750</v>
       </c>
       <c r="B83" t="n">
-        <v>-8.857591663744252</v>
+        <v>0.2632314321103676</v>
       </c>
       <c r="C83" t="n">
-        <v>-521.6373133282217</v>
+        <v>-345.5123461882808</v>
       </c>
     </row>
     <row r="84">
@@ -1344,10 +1344,10 @@
         <v>45751</v>
       </c>
       <c r="B84" t="n">
-        <v>-13.71633687469764</v>
+        <v>0.5048831925665174</v>
       </c>
       <c r="C84" t="n">
-        <v>-775.021859094202</v>
+        <v>-578.8651703839713</v>
       </c>
     </row>
     <row r="85">
@@ -1355,10 +1355,10 @@
         <v>45754</v>
       </c>
       <c r="B85" t="n">
-        <v>-21.04078534484285</v>
+        <v>0.8455429399037894</v>
       </c>
       <c r="C85" t="n">
-        <v>-976.3195716846582</v>
+        <v>-804.9072013471533</v>
       </c>
     </row>
     <row r="86">
@@ -1366,10 +1366,10 @@
         <v>45755</v>
       </c>
       <c r="B86" t="n">
-        <v>-13.90027934044885</v>
+        <v>0.822828399161913</v>
       </c>
       <c r="C86" t="n">
-        <v>-835.06061635344</v>
+        <v>-829.7147340828724</v>
       </c>
     </row>
     <row r="87">
@@ -1377,10 +1377,10 @@
         <v>45756</v>
       </c>
       <c r="B87" t="n">
-        <v>-20.83538688241709</v>
+        <v>1.153764522581482</v>
       </c>
       <c r="C87" t="n">
-        <v>-979.5404589447497</v>
+        <v>-1142.589547186003</v>
       </c>
     </row>
     <row r="88">
@@ -1388,10 +1388,10 @@
         <v>45757</v>
       </c>
       <c r="B88" t="n">
-        <v>-13.78767857897568</v>
+        <v>1.056999767282792</v>
       </c>
       <c r="C88" t="n">
-        <v>-912.4842073015703</v>
+        <v>-1221.043605127301</v>
       </c>
     </row>
     <row r="89">
@@ -1399,10 +1399,10 @@
         <v>45758</v>
       </c>
       <c r="B89" t="n">
-        <v>-9.626929437155654</v>
+        <v>0.8281250680663214</v>
       </c>
       <c r="C89" t="n">
-        <v>-686.3446015820999</v>
+        <v>-1090.484704388089</v>
       </c>
     </row>
     <row r="90">
@@ -1410,10 +1410,10 @@
         <v>45761</v>
       </c>
       <c r="B90" t="n">
-        <v>-6.442405177496946</v>
+        <v>0.6231865659779406</v>
       </c>
       <c r="C90" t="n">
-        <v>-487.5817677271463</v>
+        <v>-885.513460465383</v>
       </c>
     </row>
     <row r="91">
@@ -1421,10 +1421,10 @@
         <v>45762</v>
       </c>
       <c r="B91" t="n">
-        <v>-3.57256116039238</v>
+        <v>0.4698684376427613</v>
       </c>
       <c r="C91" t="n">
-        <v>-317.4894021320558</v>
+        <v>-669.1009970376138</v>
       </c>
     </row>
     <row r="92">
@@ -1432,10 +1432,10 @@
         <v>45763</v>
       </c>
       <c r="B92" t="n">
-        <v>-6.214522256945862</v>
+        <v>0.544063002190586</v>
       </c>
       <c r="C92" t="n">
-        <v>-530.9696943974407</v>
+        <v>-775.118031658494</v>
       </c>
     </row>
     <row r="93">
@@ -1443,10 +1443,10 @@
         <v>45764</v>
       </c>
       <c r="B93" t="n">
-        <v>-3.087896449956135</v>
+        <v>0.3539128882714861</v>
       </c>
       <c r="C93" t="n">
-        <v>-289.2397386688562</v>
+        <v>-526.2504722889042</v>
       </c>
     </row>
     <row r="94">
@@ -1454,10 +1454,10 @@
         <v>45769</v>
       </c>
       <c r="B94" t="n">
-        <v>-2.832867734609572</v>
+        <v>0.310478731212094</v>
       </c>
       <c r="C94" t="n">
-        <v>-300.3244171418455</v>
+        <v>-542.5345683163262</v>
       </c>
     </row>
     <row r="95">
@@ -1465,10 +1465,10 @@
         <v>45770</v>
       </c>
       <c r="B95" t="n">
-        <v>-5.646917552449637</v>
+        <v>0.3916655087368283</v>
       </c>
       <c r="C95" t="n">
-        <v>-454.6405524925922</v>
+        <v>-601.10479396234</v>
       </c>
     </row>
     <row r="96">
@@ -1476,10 +1476,10 @@
         <v>45771</v>
       </c>
       <c r="B96" t="n">
-        <v>-2.629419643242011</v>
+        <v>0.2458890128312182</v>
       </c>
       <c r="C96" t="n">
-        <v>-196.030615847166</v>
+        <v>-386.3668205505892</v>
       </c>
     </row>
     <row r="97">
@@ -1487,10 +1487,10 @@
         <v>45772</v>
       </c>
       <c r="B97" t="n">
-        <v>0.525692616493759</v>
+        <v>0.1063122299702835</v>
       </c>
       <c r="C97" t="n">
-        <v>-16.96796617982003</v>
+        <v>-233.4360146748986</v>
       </c>
     </row>
     <row r="98">
@@ -1498,10 +1498,10 @@
         <v>45775</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.4412306685380978</v>
+        <v>0.1018261968228473</v>
       </c>
       <c r="C98" t="n">
-        <v>-48.07824084852557</v>
+        <v>-209.6103430817067</v>
       </c>
     </row>
     <row r="99">
@@ -1509,10 +1509,10 @@
         <v>45776</v>
       </c>
       <c r="B99" t="n">
-        <v>0.6809051120701772</v>
+        <v>0.06152570531190765</v>
       </c>
       <c r="C99" t="n">
-        <v>-18.54986021859151</v>
+        <v>-165.2736316093551</v>
       </c>
     </row>
     <row r="100">
@@ -1520,10 +1520,10 @@
         <v>45777</v>
       </c>
       <c r="B100" t="n">
-        <v>-2.265041562707024</v>
+        <v>0.1160912202648417</v>
       </c>
       <c r="C100" t="n">
-        <v>-178.1197254495219</v>
+        <v>-210.8823053216047</v>
       </c>
     </row>
     <row r="101">
@@ -1531,10 +1531,10 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>-1.691555837599752</v>
+        <v>0.08003708907772743</v>
       </c>
       <c r="C101" t="n">
-        <v>-121.4881765318655</v>
+        <v>-176.2742087557242</v>
       </c>
     </row>
     <row r="102">
@@ -1542,10 +1542,10 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>-0.5043097933745269</v>
+        <v>0.02202841335830757</v>
       </c>
       <c r="C102" t="n">
-        <v>-34.2560458822251</v>
+        <v>-137.0792897848946</v>
       </c>
     </row>
     <row r="103">
@@ -1553,10 +1553,10 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>0.8504734100434332</v>
+        <v>0.02912770134832982</v>
       </c>
       <c r="C103" t="n">
-        <v>0.3769715264994269</v>
+        <v>-142.6019856075162</v>
       </c>
     </row>
     <row r="104">
@@ -1564,10 +1564,10 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>1.661404205931486</v>
+        <v>0.0004595918653193551</v>
       </c>
       <c r="C104" t="n">
-        <v>58.05440393712158</v>
+        <v>-30.06794897309588</v>
       </c>
     </row>
     <row r="105">
@@ -1575,10 +1575,10 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>-6.982938908685049</v>
+        <v>0.2226844485375475</v>
       </c>
       <c r="C105" t="n">
-        <v>-423.1661454028888</v>
+        <v>-347.9661514451623</v>
       </c>
     </row>
     <row r="106">
@@ -1586,10 +1586,10 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>4.020354756149344</v>
+        <v>-0.1502146861671533</v>
       </c>
       <c r="C106" t="n">
-        <v>326.1979241317166</v>
+        <v>350.3896938931555</v>
       </c>
     </row>
     <row r="107">
@@ -1597,10 +1597,10 @@
         <v>45789</v>
       </c>
       <c r="B107" t="n">
-        <v>-1.030347581797169</v>
+        <v>0.02878074175349769</v>
       </c>
       <c r="C107" t="n">
-        <v>-57.14592369672582</v>
+        <v>-1.335673437938835</v>
       </c>
     </row>
     <row r="108">
@@ -1608,10 +1608,10 @@
         <v>45790</v>
       </c>
       <c r="B108" t="n">
-        <v>0.3694461324886809</v>
+        <v>-0.0004967562413503693</v>
       </c>
       <c r="C108" t="n">
-        <v>-19.64499462307355</v>
+        <v>57.41270805820025</v>
       </c>
     </row>
     <row r="109">
@@ -1619,10 +1619,10 @@
         <v>45791</v>
       </c>
       <c r="B109" t="n">
-        <v>1.093178748502707</v>
+        <v>0.01402002465320694</v>
       </c>
       <c r="C109" t="n">
-        <v>-5.74191510876066</v>
+        <v>-1.792185742487922</v>
       </c>
     </row>
     <row r="110">
@@ -1630,10 +1630,10 @@
         <v>45792</v>
       </c>
       <c r="B110" t="n">
-        <v>-1.494329986933975</v>
+        <v>0.08677186516358927</v>
       </c>
       <c r="C110" t="n">
-        <v>-196.0411561652218</v>
+        <v>-131.6396915264471</v>
       </c>
     </row>
     <row r="111">
@@ -1641,10 +1641,10 @@
         <v>45793</v>
       </c>
       <c r="B111" t="n">
-        <v>-3.145038892566254</v>
+        <v>0.168260239666116</v>
       </c>
       <c r="C111" t="n">
-        <v>-256.4032004356965</v>
+        <v>-278.7259504765821</v>
       </c>
     </row>
     <row r="112">
@@ -1652,10 +1652,10 @@
         <v>45796</v>
       </c>
       <c r="B112" t="n">
-        <v>2.611063664189384</v>
+        <v>-0.006318561637842245</v>
       </c>
       <c r="C112" t="n">
-        <v>94.46230521612065</v>
+        <v>-137.8978320151574</v>
       </c>
     </row>
     <row r="113">
@@ -1663,10 +1663,10 @@
         <v>45797</v>
       </c>
       <c r="B113" t="n">
-        <v>0.7708424596949111</v>
+        <v>0.06034836822870143</v>
       </c>
       <c r="C113" t="n">
-        <v>-50.12173113872061</v>
+        <v>-268.3154778915106</v>
       </c>
     </row>
     <row r="114">
@@ -1674,10 +1674,10 @@
         <v>45798</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.5181195605479377</v>
+        <v>0.1240577804057286</v>
       </c>
       <c r="C114" t="n">
-        <v>-163.2806973838176</v>
+        <v>-307.7043599030822</v>
       </c>
     </row>
     <row r="115">
@@ -1685,10 +1685,10 @@
         <v>45799</v>
       </c>
       <c r="B115" t="n">
-        <v>-3.631081035506907</v>
+        <v>0.1721233129918538</v>
       </c>
       <c r="C115" t="n">
-        <v>-276.1556190152284</v>
+        <v>-362.3509731911612</v>
       </c>
     </row>
     <row r="116">
@@ -1696,10 +1696,10 @@
         <v>45800</v>
       </c>
       <c r="B116" t="n">
-        <v>-8.217947066679724</v>
+        <v>0.3189036422552745</v>
       </c>
       <c r="C116" t="n">
-        <v>-552.1237553470916</v>
+        <v>-540.9805387190976</v>
       </c>
     </row>
     <row r="117">
@@ -1707,10 +1707,10 @@
         <v>45803</v>
       </c>
       <c r="B117" t="n">
-        <v>1.232656895492062</v>
+        <v>-0.02627671854608504</v>
       </c>
       <c r="C117" t="n">
-        <v>178.9609613302002</v>
+        <v>128.3368842259933</v>
       </c>
     </row>
     <row r="118">
@@ -1718,10 +1718,10 @@
         <v>45804</v>
       </c>
       <c r="B118" t="n">
-        <v>-2.836928169444979</v>
+        <v>0.1718220532181002</v>
       </c>
       <c r="C118" t="n">
-        <v>-192.7589912289127</v>
+        <v>-257.4295631613413</v>
       </c>
     </row>
     <row r="119">
@@ -1729,10 +1729,10 @@
         <v>45805</v>
       </c>
       <c r="B119" t="n">
-        <v>2.090361560105866</v>
+        <v>-0.02099488140844974</v>
       </c>
       <c r="C119" t="n">
-        <v>156.8682508695815</v>
+        <v>46.12133145892561</v>
       </c>
     </row>
     <row r="120">
@@ -1740,10 +1740,10 @@
         <v>45806</v>
       </c>
       <c r="B120" t="n">
-        <v>-0.06981452497487424</v>
+        <v>0.06504454705932024</v>
       </c>
       <c r="C120" t="n">
-        <v>-58.97366171963015</v>
+        <v>-95.84890754490289</v>
       </c>
     </row>
     <row r="121">
@@ -1751,10 +1751,10 @@
         <v>45807</v>
       </c>
       <c r="B121" t="n">
-        <v>-1.272563356557896</v>
+        <v>0.09854868415906781</v>
       </c>
       <c r="C121" t="n">
-        <v>-194.9152694660424</v>
+        <v>-254.5745742880351</v>
       </c>
     </row>
     <row r="122">
@@ -1762,10 +1762,10 @@
         <v>45810</v>
       </c>
       <c r="B122" t="n">
-        <v>-4.668604973480686</v>
+        <v>0.1799545549307318</v>
       </c>
       <c r="C122" t="n">
-        <v>-294.9606636066221</v>
+        <v>-296.1334564389725</v>
       </c>
     </row>
     <row r="123">
@@ -1773,10 +1773,10 @@
         <v>45811</v>
       </c>
       <c r="B123" t="n">
-        <v>-1.479088269586642</v>
+        <v>0.01655799569366794</v>
       </c>
       <c r="C123" t="n">
-        <v>-10.95991895464176</v>
+        <v>15.98482172931866</v>
       </c>
     </row>
     <row r="124">
@@ -1784,10 +1784,10 @@
         <v>45812</v>
       </c>
       <c r="B124" t="n">
-        <v>-1.886894750495536</v>
+        <v>0.1533845866521059</v>
       </c>
       <c r="C124" t="n">
-        <v>-207.950624312778</v>
+        <v>-290.1705985343185</v>
       </c>
     </row>
     <row r="125">
@@ -1795,10 +1795,10 @@
         <v>45813</v>
       </c>
       <c r="B125" t="n">
-        <v>1.284024024779573</v>
+        <v>0.04944437234136236</v>
       </c>
       <c r="C125" t="n">
-        <v>-3.778894685287907</v>
+        <v>-146.9024764386415</v>
       </c>
     </row>
     <row r="126">
@@ -1806,10 +1806,10 @@
         <v>45814</v>
       </c>
       <c r="B126" t="n">
-        <v>-1.446756723139216</v>
+        <v>0.1052753454947454</v>
       </c>
       <c r="C126" t="n">
-        <v>-125.7671215138738</v>
+        <v>-171.1103335975553</v>
       </c>
     </row>
     <row r="127">
@@ -1817,10 +1817,10 @@
         <v>45817</v>
       </c>
       <c r="B127" t="n">
-        <v>-3.794773351191459</v>
+        <v>0.1414582487657005</v>
       </c>
       <c r="C127" t="n">
-        <v>-235.7779118157591</v>
+        <v>-213.4601431781341</v>
       </c>
     </row>
     <row r="128">
@@ -1828,10 +1828,10 @@
         <v>45818</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.4835829067568562</v>
+        <v>0.08318496971076685</v>
       </c>
       <c r="C128" t="n">
-        <v>-64.19166638193768</v>
+        <v>-117.7449970471175</v>
       </c>
     </row>
     <row r="129">
@@ -1839,10 +1839,10 @@
         <v>45819</v>
       </c>
       <c r="B129" t="n">
-        <v>-3.867879975633832</v>
+        <v>0.2061861205293944</v>
       </c>
       <c r="C129" t="n">
-        <v>-321.074968764453</v>
+        <v>-330.6582883925609</v>
       </c>
     </row>
     <row r="130">
@@ -1850,10 +1850,10 @@
         <v>45820</v>
       </c>
       <c r="B130" t="n">
-        <v>0.4067597668413697</v>
+        <v>0.07056970618340216</v>
       </c>
       <c r="C130" t="n">
-        <v>-32.56802139852535</v>
+        <v>-149.3007863115981</v>
       </c>
     </row>
     <row r="131">
@@ -1861,10 +1861,10 @@
         <v>45821</v>
       </c>
       <c r="B131" t="n">
-        <v>-0.6843635298676521</v>
+        <v>0.02953343614693172</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3802996463394546</v>
+        <v>-48.26909645594314</v>
       </c>
     </row>
     <row r="132">
@@ -1872,10 +1872,10 @@
         <v>45824</v>
       </c>
       <c r="B132" t="n">
-        <v>1.423961437089044</v>
+        <v>-0.02655901985411836</v>
       </c>
       <c r="C132" t="n">
-        <v>102.5407425381143</v>
+        <v>58.45990826235894</v>
       </c>
     </row>
     <row r="133">
@@ -1883,10 +1883,10 @@
         <v>45825</v>
       </c>
       <c r="B133" t="n">
-        <v>1.86896658968343</v>
+        <v>-0.01769425317638542</v>
       </c>
       <c r="C133" t="n">
-        <v>74.95736240616426</v>
+        <v>0.9393459461140433</v>
       </c>
     </row>
     <row r="134">
@@ -1894,10 +1894,10 @@
         <v>45826</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.4625085509628304</v>
+        <v>0.05379218015006391</v>
       </c>
       <c r="C134" t="n">
-        <v>-119.8414869808794</v>
+        <v>-121.1826806884708</v>
       </c>
     </row>
     <row r="135">
@@ -1905,10 +1905,10 @@
         <v>45828</v>
       </c>
       <c r="B135" t="n">
-        <v>-1.299579864781375</v>
+        <v>0.04807624477599784</v>
       </c>
       <c r="C135" t="n">
-        <v>-95.39157056682249</v>
+        <v>-68.43106496806645</v>
       </c>
     </row>
     <row r="136">
@@ -1916,10 +1916,10 @@
         <v>45831</v>
       </c>
       <c r="B136" t="n">
-        <v>3.966316056216108</v>
+        <v>-0.1146550835482331</v>
       </c>
       <c r="C136" t="n">
-        <v>195.6816337081363</v>
+        <v>-5.682099741637889</v>
       </c>
     </row>
     <row r="137">
@@ -1927,10 +1927,10 @@
         <v>45832</v>
       </c>
       <c r="B137" t="n">
-        <v>-1.006545083876223</v>
+        <v>0.02907384690406389</v>
       </c>
       <c r="C137" t="n">
-        <v>-74.18615500082295</v>
+        <v>-99.67464882271923</v>
       </c>
     </row>
     <row r="138">
@@ -1938,10 +1938,10 @@
         <v>45833</v>
       </c>
       <c r="B138" t="n">
-        <v>1.298866359812219</v>
+        <v>-0.04148892142992826</v>
       </c>
       <c r="C138" t="n">
-        <v>82.49102302607382</v>
+        <v>-5.313655217414069</v>
       </c>
     </row>
     <row r="139">
@@ -1949,10 +1949,10 @@
         <v>45834</v>
       </c>
       <c r="B139" t="n">
-        <v>3.394723693122898</v>
+        <v>-0.1149455542085683</v>
       </c>
       <c r="C139" t="n">
-        <v>208.2178261211774</v>
+        <v>121.9285312870202</v>
       </c>
     </row>
     <row r="140">
@@ -1960,10 +1960,10 @@
         <v>45835</v>
       </c>
       <c r="B140" t="n">
-        <v>2.277640572177042</v>
+        <v>-0.1123005645379645</v>
       </c>
       <c r="C140" t="n">
-        <v>155.3401529437562</v>
+        <v>166.5099384095761</v>
       </c>
     </row>
     <row r="141">
@@ -1971,10 +1971,10 @@
         <v>45838</v>
       </c>
       <c r="B141" t="n">
-        <v>-0.7099423812016167</v>
+        <v>0.009960473745093021</v>
       </c>
       <c r="C141" t="n">
-        <v>-100.6065306802798</v>
+        <v>-146.4114040132648</v>
       </c>
     </row>
     <row r="142">
@@ -1982,10 +1982,10 @@
         <v>45839</v>
       </c>
       <c r="B142" t="n">
-        <v>1.891236282292674</v>
+        <v>-0.04872476216290732</v>
       </c>
       <c r="C142" t="n">
-        <v>46.5938513168433</v>
+        <v>-88.64432753045359</v>
       </c>
     </row>
     <row r="143">
@@ -1993,10 +1993,10 @@
         <v>45840</v>
       </c>
       <c r="B143" t="n">
-        <v>1.503389925694478</v>
+        <v>-0.1102317639391638</v>
       </c>
       <c r="C143" t="n">
-        <v>159.7629097695554</v>
+        <v>117.6657582516705</v>
       </c>
     </row>
     <row r="144">
@@ -2004,10 +2004,10 @@
         <v>45841</v>
       </c>
       <c r="B144" t="n">
-        <v>0.7976457015634488</v>
+        <v>-0.0917792477279579</v>
       </c>
       <c r="C144" t="n">
-        <v>122.4338973664214</v>
+        <v>139.6012333903091</v>
       </c>
     </row>
     <row r="145">
@@ -2015,10 +2015,10 @@
         <v>45842</v>
       </c>
       <c r="B145" t="n">
-        <v>9.462284055037781</v>
+        <v>-0.4297111819554323</v>
       </c>
       <c r="C145" t="n">
-        <v>750.8001332158851</v>
+        <v>728.4338000944801</v>
       </c>
     </row>
     <row r="146">
@@ -2026,10 +2026,10 @@
         <v>45845</v>
       </c>
       <c r="B146" t="n">
-        <v>4.652032038423202</v>
+        <v>-0.2462496070745798</v>
       </c>
       <c r="C146" t="n">
-        <v>301.5869156507804</v>
+        <v>432.937109293432</v>
       </c>
     </row>
     <row r="147">
@@ -2037,10 +2037,10 @@
         <v>45846</v>
       </c>
       <c r="B147" t="n">
-        <v>0.3802934526488015</v>
+        <v>-0.1053670284103708</v>
       </c>
       <c r="C147" t="n">
-        <v>-25.94638909160066</v>
+        <v>153.8424828060042</v>
       </c>
     </row>
     <row r="148">
@@ -2048,10 +2048,10 @@
         <v>45847</v>
       </c>
       <c r="B148" t="n">
-        <v>2.037804062523072</v>
+        <v>-0.2030312418719014</v>
       </c>
       <c r="C148" t="n">
-        <v>173.2813483306986</v>
+        <v>384.7134974144089</v>
       </c>
     </row>
     <row r="149">
@@ -2059,10 +2059,10 @@
         <v>45848</v>
       </c>
       <c r="B149" t="n">
-        <v>-4.563015470806369</v>
+        <v>0.03353108042481119</v>
       </c>
       <c r="C149" t="n">
-        <v>-285.8282889890628</v>
+        <v>-1.845249626465286</v>
       </c>
     </row>
     <row r="150">
@@ -2070,10 +2070,10 @@
         <v>45849</v>
       </c>
       <c r="B150" t="n">
-        <v>3.479182408988788</v>
+        <v>-0.1629803293788029</v>
       </c>
       <c r="C150" t="n">
-        <v>270.6897379411297</v>
+        <v>312.8376123481504</v>
       </c>
     </row>
     <row r="151">
@@ -2081,10 +2081,10 @@
         <v>45852</v>
       </c>
       <c r="B151" t="n">
-        <v>2.190393313878433</v>
+        <v>-0.1388112513516579</v>
       </c>
       <c r="C151" t="n">
-        <v>219.2758062402822</v>
+        <v>224.8500705498747</v>
       </c>
     </row>
     <row r="152">
@@ -2092,10 +2092,10 @@
         <v>45853</v>
       </c>
       <c r="B152" t="n">
-        <v>-0.8199398360856824</v>
+        <v>0.000329044685442042</v>
       </c>
       <c r="C152" t="n">
-        <v>-74.2537150035668</v>
+        <v>13.97364091105158</v>
       </c>
     </row>
     <row r="153">
@@ -2103,10 +2103,10 @@
         <v>45854</v>
       </c>
       <c r="B153" t="n">
-        <v>-1.773587833392475</v>
+        <v>0.03789057554088147</v>
       </c>
       <c r="C153" t="n">
-        <v>-110.1766923048222</v>
+        <v>-41.21970626069919</v>
       </c>
     </row>
     <row r="154">
@@ -2114,10 +2114,10 @@
         <v>45855</v>
       </c>
       <c r="B154" t="n">
-        <v>-1.110417481093018</v>
+        <v>0.05282155337434827</v>
       </c>
       <c r="C154" t="n">
-        <v>-151.8454171944886</v>
+        <v>-137.3233151712027</v>
       </c>
     </row>
     <row r="155">
@@ -2125,10 +2125,10 @@
         <v>45856</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.3173562694420948</v>
+        <v>-0.0009852775463075466</v>
       </c>
       <c r="C155" t="n">
-        <v>-5.33163384585681</v>
+        <v>-25.69085590930568</v>
       </c>
     </row>
     <row r="156">
@@ -2136,10 +2136,10 @@
         <v>45859</v>
       </c>
       <c r="B156" t="n">
-        <v>0.4889779382766768</v>
+        <v>0.01032174159694871</v>
       </c>
       <c r="C156" t="n">
-        <v>1.404195732134372</v>
+        <v>-97.50624274671299</v>
       </c>
     </row>
     <row r="157">
@@ -2147,10 +2147,10 @@
         <v>45860</v>
       </c>
       <c r="B157" t="n">
-        <v>0.1068829103345189</v>
+        <v>0.07855246348782768</v>
       </c>
       <c r="C157" t="n">
-        <v>-116.381551068521</v>
+        <v>-236.0063122577194</v>
       </c>
     </row>
     <row r="158">
@@ -2158,10 +2158,10 @@
         <v>45861</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.1389037398526872</v>
+        <v>-0.004640039078549864</v>
       </c>
       <c r="C158" t="n">
-        <v>28.18744387963879</v>
+        <v>-44.70331455430198</v>
       </c>
     </row>
     <row r="159">
@@ -2169,10 +2169,10 @@
         <v>45862</v>
       </c>
       <c r="B159" t="n">
-        <v>4.313782215036052</v>
+        <v>-0.1637727984295882</v>
       </c>
       <c r="C159" t="n">
-        <v>324.0367919642745</v>
+        <v>268.4535702219125</v>
       </c>
     </row>
     <row r="160">
@@ -2180,10 +2180,10 @@
         <v>45863</v>
       </c>
       <c r="B160" t="n">
-        <v>3.653326587663688</v>
+        <v>-0.141911365228346</v>
       </c>
       <c r="C160" t="n">
-        <v>246.7714990413627</v>
+        <v>233.3861420328568</v>
       </c>
     </row>
     <row r="161">
@@ -2191,10 +2191,10 @@
         <v>45866</v>
       </c>
       <c r="B161" t="n">
-        <v>2.77161924504975</v>
+        <v>-0.1953000292354294</v>
       </c>
       <c r="C161" t="n">
-        <v>269.028322375981</v>
+        <v>336.8791317839843</v>
       </c>
     </row>
     <row r="162">
@@ -2202,10 +2202,10 @@
         <v>45867</v>
       </c>
       <c r="B162" t="n">
-        <v>4.533825585574937</v>
+        <v>-0.2521765909832155</v>
       </c>
       <c r="C162" t="n">
-        <v>344.421304033272</v>
+        <v>464.9666786323837</v>
       </c>
     </row>
     <row r="163">
@@ -2213,10 +2213,10 @@
         <v>45868</v>
       </c>
       <c r="B163" t="n">
-        <v>-10.37578554875634</v>
+        <v>0.2040620505075545</v>
       </c>
       <c r="C163" t="n">
-        <v>-604.2537583554611</v>
+        <v>-194.9379575307135</v>
       </c>
     </row>
     <row r="164">
@@ -2224,10 +2224,10 @@
         <v>45869</v>
       </c>
       <c r="B164" t="n">
-        <v>-2.998054824407309</v>
+        <v>0.09415615423728331</v>
       </c>
       <c r="C164" t="n">
-        <v>-230.1915030636591</v>
+        <v>-81.00368364433839</v>
       </c>
     </row>
     <row r="165">
@@ -2235,10 +2235,10 @@
         <v>45873</v>
       </c>
       <c r="B165" t="n">
-        <v>-4.023300671073682</v>
+        <v>0.1397577650626506</v>
       </c>
       <c r="C165" t="n">
-        <v>-241.0096355460459</v>
+        <v>-159.107945041034</v>
       </c>
     </row>
     <row r="166">
@@ -2246,10 +2246,10 @@
         <v>45874</v>
       </c>
       <c r="B166" t="n">
-        <v>-2.464922784072057</v>
+        <v>0.1891095739951157</v>
       </c>
       <c r="C166" t="n">
-        <v>-232.2417319438808</v>
+        <v>-281.6066370933092</v>
       </c>
     </row>
     <row r="167">
@@ -2257,10 +2257,10 @@
         <v>45875</v>
       </c>
       <c r="B167" t="n">
-        <v>-2.103874239373782</v>
+        <v>0.2010328479383444</v>
       </c>
       <c r="C167" t="n">
-        <v>-176.0580583004421</v>
+        <v>-357.516206844726</v>
       </c>
     </row>
     <row r="168">
@@ -2268,10 +2268,10 @@
         <v>45876</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.6085475475171371</v>
+        <v>0.1143829670700692</v>
       </c>
       <c r="C168" t="n">
-        <v>-78.67696349140489</v>
+        <v>-236.7784265412981</v>
       </c>
     </row>
     <row r="169">
@@ -2279,10 +2279,10 @@
         <v>45877</v>
       </c>
       <c r="B169" t="n">
-        <v>1.637932504809495</v>
+        <v>0.04588093638143429</v>
       </c>
       <c r="C169" t="n">
-        <v>32.32147511264827</v>
+        <v>-203.5433345448703</v>
       </c>
     </row>
     <row r="170">
@@ -2290,10 +2290,10 @@
         <v>45880</v>
       </c>
       <c r="B170" t="n">
-        <v>1.832489709126789</v>
+        <v>-0.01995920627469302</v>
       </c>
       <c r="C170" t="n">
-        <v>111.0011499081572</v>
+        <v>6.669618059505808</v>
       </c>
     </row>
     <row r="171">
@@ -2301,10 +2301,10 @@
         <v>45881</v>
       </c>
       <c r="B171" t="n">
-        <v>-1.898060788485386</v>
+        <v>0.08421047779785745</v>
       </c>
       <c r="C171" t="n">
-        <v>-139.2619587470824</v>
+        <v>-161.4021167766267</v>
       </c>
     </row>
     <row r="172">
@@ -2312,10 +2312,10 @@
         <v>45882</v>
       </c>
       <c r="B172" t="n">
-        <v>2.127343704444425</v>
+        <v>-0.04527901791613874</v>
       </c>
       <c r="C172" t="n">
-        <v>107.4832273763246</v>
+        <v>-26.79641135421756</v>
       </c>
     </row>
     <row r="173">
@@ -2323,10 +2323,10 @@
         <v>45883</v>
       </c>
       <c r="B173" t="n">
-        <v>-2.003330058537357</v>
+        <v>0.05952841977620652</v>
       </c>
       <c r="C173" t="n">
-        <v>-127.8966579265923</v>
+        <v>-98.05674936942364</v>
       </c>
     </row>
     <row r="174">
@@ -2334,10 +2334,10 @@
         <v>45884</v>
       </c>
       <c r="B174" t="n">
-        <v>1.542618460769455</v>
+        <v>0.005514894803715128</v>
       </c>
       <c r="C174" t="n">
-        <v>22.28278301939874</v>
+        <v>-37.74212785906288</v>
       </c>
     </row>
     <row r="175">
@@ -2345,10 +2345,10 @@
         <v>45887</v>
       </c>
       <c r="B175" t="n">
-        <v>4.485139529388952</v>
+        <v>-0.1775282651888689</v>
       </c>
       <c r="C175" t="n">
-        <v>354.81839718958</v>
+        <v>258.9218558016409</v>
       </c>
     </row>
     <row r="176">
@@ -2356,10 +2356,10 @@
         <v>45888</v>
       </c>
       <c r="B176" t="n">
-        <v>-4.1539929321573</v>
+        <v>0.1226067663117323</v>
       </c>
       <c r="C176" t="n">
-        <v>-283.7468001835062</v>
+        <v>-209.0787174053756</v>
       </c>
     </row>
     <row r="177">
@@ -2367,10 +2367,10 @@
         <v>45889</v>
       </c>
       <c r="B177" t="n">
-        <v>3.482471997016169</v>
+        <v>-0.1688057145869944</v>
       </c>
       <c r="C177" t="n">
-        <v>310.0529062060054</v>
+        <v>266.415647304074</v>
       </c>
     </row>
     <row r="178">
@@ -2378,10 +2378,10 @@
         <v>45890</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.08799063462428967</v>
+        <v>-0.1196055434115626</v>
       </c>
       <c r="C178" t="n">
-        <v>114.3283543171528</v>
+        <v>198.6628775569741</v>
       </c>
     </row>
     <row r="179">
@@ -2389,10 +2389,10 @@
         <v>45891</v>
       </c>
       <c r="B179" t="n">
-        <v>-2.838736568920916</v>
+        <v>0.04687389917074106</v>
       </c>
       <c r="C179" t="n">
-        <v>-189.2733299329059</v>
+        <v>-56.78886878402383</v>
       </c>
     </row>
     <row r="180">
@@ -2400,10 +2400,10 @@
         <v>45894</v>
       </c>
       <c r="B180" t="n">
-        <v>5.961907813686081</v>
+        <v>-0.2195010622732331</v>
       </c>
       <c r="C180" t="n">
-        <v>421.2918133056244</v>
+        <v>372.2746158110531</v>
       </c>
     </row>
     <row r="181">
@@ -2411,10 +2411,10 @@
         <v>45895</v>
       </c>
       <c r="B181" t="n">
-        <v>5.824674441863754</v>
+        <v>-0.2992086068637245</v>
       </c>
       <c r="C181" t="n">
-        <v>467.3813865222174</v>
+        <v>508.7542912163954</v>
       </c>
     </row>
     <row r="182">
@@ -2422,10 +2422,10 @@
         <v>45896</v>
       </c>
       <c r="B182" t="n">
-        <v>2.971077222322296</v>
+        <v>-0.126498456722697</v>
       </c>
       <c r="C182" t="n">
-        <v>107.4902512664757</v>
+        <v>128.1553300390887</v>
       </c>
     </row>
     <row r="183">
@@ -2433,10 +2433,10 @@
         <v>45897</v>
       </c>
       <c r="B183" t="n">
-        <v>0.2538022158557318</v>
+        <v>-0.14375631507178</v>
       </c>
       <c r="C183" t="n">
-        <v>97.20322693518904</v>
+        <v>248.5745908434426</v>
       </c>
     </row>
     <row r="184">
@@ -2444,10 +2444,10 @@
         <v>45898</v>
       </c>
       <c r="B184" t="n">
-        <v>5.893527119455492</v>
+        <v>-0.3603264531526427</v>
       </c>
       <c r="C184" t="n">
-        <v>500.2571817280419</v>
+        <v>607.3570940573888</v>
       </c>
     </row>
     <row r="185">
@@ -2455,10 +2455,10 @@
         <v>45901</v>
       </c>
       <c r="B185" t="n">
-        <v>6.035549210558008</v>
+        <v>-0.3783446114104213</v>
       </c>
       <c r="C185" t="n">
-        <v>523.6631982238677</v>
+        <v>633.8723095769277</v>
       </c>
     </row>
     <row r="186">
@@ -2466,10 +2466,10 @@
         <v>45902</v>
       </c>
       <c r="B186" t="n">
-        <v>-2.748042584160815</v>
+        <v>-0.1182342852655772</v>
       </c>
       <c r="C186" t="n">
-        <v>-34.13077267235801</v>
+        <v>230.8514026310649</v>
       </c>
     </row>
     <row r="187">
@@ -2477,10 +2477,10 @@
         <v>45903</v>
       </c>
       <c r="B187" t="n">
-        <v>5.417102083953507</v>
+        <v>-0.3646133164085937</v>
       </c>
       <c r="C187" t="n">
-        <v>457.8870653964094</v>
+        <v>670.1840827320639</v>
       </c>
     </row>
     <row r="188">
@@ -2488,10 +2488,10 @@
         <v>45904</v>
       </c>
       <c r="B188" t="n">
-        <v>5.108524388820856</v>
+        <v>-0.2667846873523189</v>
       </c>
       <c r="C188" t="n">
-        <v>287.5263748857198</v>
+        <v>422.6399913913842</v>
       </c>
     </row>
     <row r="189">
@@ -2499,10 +2499,10 @@
         <v>45905</v>
       </c>
       <c r="B189" t="n">
-        <v>-4.748109455574225</v>
+        <v>-0.007949315478976782</v>
       </c>
       <c r="C189" t="n">
-        <v>-232.2036027250637</v>
+        <v>82.52811998263628</v>
       </c>
     </row>
     <row r="190">
@@ -2510,10 +2510,10 @@
         <v>45908</v>
       </c>
       <c r="B190" t="n">
-        <v>3.716816994757737</v>
+        <v>-0.2067272808312185</v>
       </c>
       <c r="C190" t="n">
-        <v>305.6469732032293</v>
+        <v>358.3676570173591</v>
       </c>
     </row>
     <row r="191">
@@ -2521,10 +2521,10 @@
         <v>45909</v>
       </c>
       <c r="B191" t="n">
-        <v>8.76684784597575</v>
+        <v>-0.4024612569384927</v>
       </c>
       <c r="C191" t="n">
-        <v>637.4625545139018</v>
+        <v>680.7250051763376</v>
       </c>
     </row>
     <row r="192">
@@ -2532,10 +2532,10 @@
         <v>45910</v>
       </c>
       <c r="B192" t="n">
-        <v>0.8728456149897941</v>
+        <v>-0.1581556892515101</v>
       </c>
       <c r="C192" t="n">
-        <v>118.9246936143749</v>
+        <v>284.4774020608213</v>
       </c>
     </row>
     <row r="193">
@@ -2543,10 +2543,10 @@
         <v>45911</v>
       </c>
       <c r="B193" t="n">
-        <v>1.732540460996448</v>
+        <v>-0.2023784934286524</v>
       </c>
       <c r="C193" t="n">
-        <v>199.7694550544519</v>
+        <v>414.1443579269615</v>
       </c>
     </row>
     <row r="194">
@@ -2554,10 +2554,10 @@
         <v>45912</v>
       </c>
       <c r="B194" t="n">
-        <v>1.469708613335118</v>
+        <v>-0.1993283110325867</v>
       </c>
       <c r="C194" t="n">
-        <v>125.141426893921</v>
+        <v>406.861383629365</v>
       </c>
     </row>
     <row r="195">
@@ -2565,10 +2565,10 @@
         <v>45915</v>
       </c>
       <c r="B195" t="n">
-        <v>1.089320712283038</v>
+        <v>-0.1835862231721446</v>
       </c>
       <c r="C195" t="n">
-        <v>123.3070932945258</v>
+        <v>332.7855048487661</v>
       </c>
     </row>
     <row r="196">
@@ -2576,10 +2576,10 @@
         <v>45916</v>
       </c>
       <c r="B196" t="n">
-        <v>2.992709152342205</v>
+        <v>-0.2179660854258138</v>
       </c>
       <c r="C196" t="n">
-        <v>256.2881920651399</v>
+        <v>357.853120814365</v>
       </c>
     </row>
     <row r="197">
@@ -2587,10 +2587,10 @@
         <v>45917</v>
       </c>
       <c r="B197" t="n">
-        <v>-4.609274151656233</v>
+        <v>0.1194326882841057</v>
       </c>
       <c r="C197" t="n">
-        <v>-369.3920218154635</v>
+        <v>-192.2540838800096</v>
       </c>
     </row>
     <row r="198">
@@ -2598,10 +2598,10 @@
         <v>45918</v>
       </c>
       <c r="B198" t="n">
-        <v>4.908844075428929</v>
+        <v>-0.2019651281014698</v>
       </c>
       <c r="C198" t="n">
-        <v>353.1868421542956</v>
+        <v>314.8995767591004</v>
       </c>
     </row>
     <row r="199">
@@ -2609,10 +2609,10 @@
         <v>45919</v>
       </c>
       <c r="B199" t="n">
-        <v>5.567801147676679</v>
+        <v>-0.2621330482881801</v>
       </c>
       <c r="C199" t="n">
-        <v>426.1970046641331</v>
+        <v>417.7682257298188</v>
       </c>
     </row>
     <row r="200">
@@ -2620,10 +2620,10 @@
         <v>45922</v>
       </c>
       <c r="B200" t="n">
-        <v>0.9622710526926119</v>
+        <v>-0.1492865119418017</v>
       </c>
       <c r="C200" t="n">
-        <v>149.5578281837422</v>
+        <v>261.4060418253425</v>
       </c>
     </row>
     <row r="201">
@@ -2631,10 +2631,10 @@
         <v>45923</v>
       </c>
       <c r="B201" t="n">
-        <v>-1.41900833932156</v>
+        <v>-0.04414932299484202</v>
       </c>
       <c r="C201" t="n">
-        <v>-60.50079691441974</v>
+        <v>87.940664858585</v>
       </c>
     </row>
     <row r="202">
@@ -2642,10 +2642,10 @@
         <v>45924</v>
       </c>
       <c r="B202" t="n">
-        <v>11.0512765989542</v>
+        <v>-0.4941451112577341</v>
       </c>
       <c r="C202" t="n">
-        <v>817.8520601454475</v>
+        <v>837.6490693974207</v>
       </c>
     </row>
     <row r="203">
@@ -2653,10 +2653,10 @@
         <v>45925</v>
       </c>
       <c r="B203" t="n">
-        <v>0.7362259429081353</v>
+        <v>-0.1530942749441769</v>
       </c>
       <c r="C203" t="n">
-        <v>49.77972532824637</v>
+        <v>250.2155404032273</v>
       </c>
     </row>
     <row r="204">
@@ -2664,10 +2664,10 @@
         <v>45926</v>
       </c>
       <c r="B204" t="n">
-        <v>4.326577434296061</v>
+        <v>-0.3155635200033899</v>
       </c>
       <c r="C204" t="n">
-        <v>401.4136273427496</v>
+        <v>594.4666062906042</v>
       </c>
     </row>
     <row r="205">
@@ -2675,10 +2675,10 @@
         <v>45929</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.8449521183629511</v>
+        <v>-0.07435369745446668</v>
       </c>
       <c r="C205" t="n">
-        <v>-78.90020346572432</v>
+        <v>144.7990433581538</v>
       </c>
     </row>
     <row r="206">
@@ -2686,10 +2686,10 @@
         <v>45930</v>
       </c>
       <c r="B206" t="n">
-        <v>4.886039880647311</v>
+        <v>-0.3127129870048886</v>
       </c>
       <c r="C206" t="n">
-        <v>403.3606389476354</v>
+        <v>533.4005836664434</v>
       </c>
     </row>
     <row r="207">
@@ -2697,10 +2697,10 @@
         <v>45931</v>
       </c>
       <c r="B207" t="n">
-        <v>2.988471084546784</v>
+        <v>-0.2053494840824015</v>
       </c>
       <c r="C207" t="n">
-        <v>259.9877470697772</v>
+        <v>365.962678514567</v>
       </c>
     </row>
     <row r="208">
@@ -2708,10 +2708,10 @@
         <v>45932</v>
       </c>
       <c r="B208" t="n">
-        <v>3.104003412433172</v>
+        <v>-0.2588621384485807</v>
       </c>
       <c r="C208" t="n">
-        <v>310.8650491002873</v>
+        <v>414.9690464942562</v>
       </c>
     </row>
     <row r="209">
@@ -2719,10 +2719,10 @@
         <v>45933</v>
       </c>
       <c r="B209" t="n">
-        <v>3.370879627725478</v>
+        <v>-0.09416446102114821</v>
       </c>
       <c r="C209" t="n">
-        <v>64.73072134693142</v>
+        <v>-53.26183627692828</v>
       </c>
     </row>
     <row r="210">
@@ -2730,10 +2730,10 @@
         <v>45936</v>
       </c>
       <c r="B210" t="n">
-        <v>3.196240509082936</v>
+        <v>-0.214718463444179</v>
       </c>
       <c r="C210" t="n">
-        <v>255.4811151929014</v>
+        <v>340.9709934866206</v>
       </c>
     </row>
     <row r="211">
@@ -2741,10 +2741,10 @@
         <v>45937</v>
       </c>
       <c r="B211" t="n">
-        <v>3.638994954024823</v>
+        <v>-0.207048229659546</v>
       </c>
       <c r="C211" t="n">
-        <v>270.0099165459039</v>
+        <v>277.817807497627</v>
       </c>
     </row>
     <row r="212">
@@ -2752,10 +2752,10 @@
         <v>45938</v>
       </c>
       <c r="B212" t="n">
-        <v>3.930625717250782</v>
+        <v>-0.2392137047286522</v>
       </c>
       <c r="C212" t="n">
-        <v>328.3053148071715</v>
+        <v>349.8339712403977</v>
       </c>
     </row>
     <row r="213">
@@ -2763,10 +2763,10 @@
         <v>45939</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.02741992539971154</v>
+        <v>-0.1180402826823772</v>
       </c>
       <c r="C213" t="n">
-        <v>37.9291337373408</v>
+        <v>202.3467190848069</v>
       </c>
     </row>
     <row r="214">
@@ -2774,10 +2774,10 @@
         <v>45940</v>
       </c>
       <c r="B214" t="n">
-        <v>-5.131804971052766</v>
+        <v>0.04733108697251027</v>
       </c>
       <c r="C214" t="n">
-        <v>-283.7888813654057</v>
+        <v>-12.3831536884054</v>
       </c>
     </row>
     <row r="215">
@@ -2785,10 +2785,10 @@
         <v>45943</v>
       </c>
       <c r="B215" t="n">
-        <v>3.728966559256195</v>
+        <v>-0.2404708261425824</v>
       </c>
       <c r="C215" t="n">
-        <v>345.7026475318119</v>
+        <v>472.4902775840799</v>
       </c>
     </row>
     <row r="216">
@@ -2796,10 +2796,10 @@
         <v>45944</v>
       </c>
       <c r="B216" t="n">
-        <v>-1.000299505903742</v>
+        <v>-0.01949542452847295</v>
       </c>
       <c r="C216" t="n">
-        <v>-74.27982745634297</v>
+        <v>97.42829821943754</v>
       </c>
     </row>
     <row r="217">
@@ -2807,10 +2807,10 @@
         <v>45945</v>
       </c>
       <c r="B217" t="n">
-        <v>-3.659915325120792</v>
+        <v>0.1211289791604526</v>
       </c>
       <c r="C217" t="n">
-        <v>-257.6264343449637</v>
+        <v>-114.3428647311893</v>
       </c>
     </row>
     <row r="218">
@@ -2818,10 +2818,10 @@
         <v>45946</v>
       </c>
       <c r="B218" t="n">
-        <v>-2.713546783891437</v>
+        <v>0.1585467567281258</v>
       </c>
       <c r="C218" t="n">
-        <v>-281.8606617417799</v>
+        <v>-287.8549781698721</v>
       </c>
     </row>
     <row r="219">
@@ -2829,10 +2829,10 @@
         <v>45947</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.284450777415736</v>
+        <v>-0.003397723397727973</v>
       </c>
       <c r="C219" t="n">
-        <v>15.14681914635043</v>
+        <v>8.269116296407963</v>
       </c>
     </row>
     <row r="220">
@@ -2840,10 +2840,10 @@
         <v>45950</v>
       </c>
       <c r="B220" t="n">
-        <v>1.609877277578335</v>
+        <v>-0.05107161727361834</v>
       </c>
       <c r="C220" t="n">
-        <v>157.4760619490542</v>
+        <v>120.7928365468442</v>
       </c>
     </row>
     <row r="221">
@@ -2851,10 +2851,10 @@
         <v>45951</v>
       </c>
       <c r="B221" t="n">
-        <v>1.849317727983196</v>
+        <v>-0.04165383183316496</v>
       </c>
       <c r="C221" t="n">
-        <v>122.3588050316175</v>
+        <v>90.04591031698963</v>
       </c>
     </row>
     <row r="222">
@@ -2862,10 +2862,10 @@
         <v>45952</v>
       </c>
       <c r="B222" t="n">
-        <v>-1.000780414999209</v>
+        <v>0.00551132296097021</v>
       </c>
       <c r="C222" t="n">
-        <v>-41.96147568537875</v>
+        <v>46.40157325926742</v>
       </c>
     </row>
     <row r="223">
@@ -2873,10 +2873,10 @@
         <v>45953</v>
       </c>
       <c r="B223" t="n">
-        <v>1.676208576146675</v>
+        <v>-0.1540253077069443</v>
       </c>
       <c r="C223" t="n">
-        <v>209.0265855602048</v>
+        <v>293.2142468503139</v>
       </c>
     </row>
     <row r="224">
@@ -2884,10 +2884,10 @@
         <v>45954</v>
       </c>
       <c r="B224" t="n">
-        <v>3.321138608992827</v>
+        <v>-0.2797734359793893</v>
       </c>
       <c r="C224" t="n">
-        <v>379.010155990409</v>
+        <v>530.6335645464342</v>
       </c>
     </row>
     <row r="225">
@@ -2895,10 +2895,10 @@
         <v>45957</v>
       </c>
       <c r="B225" t="n">
-        <v>-1.73291650174577</v>
+        <v>-0.06031030579055199</v>
       </c>
       <c r="C225" t="n">
-        <v>-38.18064706636174</v>
+        <v>143.2313870855955</v>
       </c>
     </row>
     <row r="226">
@@ -2906,10 +2906,10 @@
         <v>45958</v>
       </c>
       <c r="B226" t="n">
-        <v>5.549085036140089</v>
+        <v>-0.2387569924391744</v>
       </c>
       <c r="C226" t="n">
-        <v>368.0370547255938</v>
+        <v>440.5396058413566</v>
       </c>
     </row>
     <row r="227">
@@ -2917,10 +2917,10 @@
         <v>45959</v>
       </c>
       <c r="B227" t="n">
-        <v>3.180627803702885</v>
+        <v>-0.207349189834831</v>
       </c>
       <c r="C227" t="n">
-        <v>245.8187078142313</v>
+        <v>365.9719003657344</v>
       </c>
     </row>
     <row r="228">
@@ -2928,10 +2928,10 @@
         <v>45960</v>
       </c>
       <c r="B228" t="n">
-        <v>7.823989228847082</v>
+        <v>-0.4094376152682719</v>
       </c>
       <c r="C228" t="n">
-        <v>613.8902923679681</v>
+        <v>675.5315280530951</v>
       </c>
     </row>
     <row r="229">
@@ -2939,10 +2939,10 @@
         <v>45961</v>
       </c>
       <c r="B229" t="n">
-        <v>5.836859938669091</v>
+        <v>-0.3317842320012797</v>
       </c>
       <c r="C229" t="n">
-        <v>443.4762158825372</v>
+        <v>602.6379973981457</v>
       </c>
     </row>
     <row r="230">
@@ -2950,10 +2950,10 @@
         <v>45964</v>
       </c>
       <c r="B230" t="n">
-        <v>3.43315070150887</v>
+        <v>-0.3466155226505833</v>
       </c>
       <c r="C230" t="n">
-        <v>357.6157814963842</v>
+        <v>613.931152464822</v>
       </c>
     </row>
     <row r="231">
@@ -2961,10 +2961,10 @@
         <v>45965</v>
       </c>
       <c r="B231" t="n">
-        <v>7.270013278461952</v>
+        <v>-0.3909710268861553</v>
       </c>
       <c r="C231" t="n">
-        <v>491.6776883986567</v>
+        <v>550.4064676596976</v>
       </c>
     </row>
     <row r="232">
@@ -2972,10 +2972,10 @@
         <v>45966</v>
       </c>
       <c r="B232" t="n">
-        <v>1.308442695986503</v>
+        <v>-0.2230011270509072</v>
       </c>
       <c r="C232" t="n">
-        <v>61.28838695357823</v>
+        <v>436.4097479446803</v>
       </c>
     </row>
     <row r="233">
@@ -2983,10 +2983,10 @@
         <v>45967</v>
       </c>
       <c r="B233" t="n">
-        <v>4.051298472608657</v>
+        <v>-0.2455543835147191</v>
       </c>
       <c r="C233" t="n">
-        <v>245.5816039807152</v>
+        <v>355.343039286819</v>
       </c>
     </row>
     <row r="234">
@@ -2994,10 +2994,10 @@
         <v>45968</v>
       </c>
       <c r="B234" t="n">
-        <v>2.416840025287019</v>
+        <v>-0.1872841219627767</v>
       </c>
       <c r="C234" t="n">
-        <v>153.0709854543665</v>
+        <v>354.8967638055949</v>
       </c>
     </row>
     <row r="235">
@@ -3005,10 +3005,10 @@
         <v>45971</v>
       </c>
       <c r="B235" t="n">
-        <v>1.948384557771417</v>
+        <v>-0.1487595383565499</v>
       </c>
       <c r="C235" t="n">
-        <v>127.9370011553645</v>
+        <v>203.3041884923348</v>
       </c>
     </row>
     <row r="236">
@@ -3016,10 +3016,10 @@
         <v>45972</v>
       </c>
       <c r="B236" t="n">
-        <v>-1.709864556998218</v>
+        <v>-0.04047761743818878</v>
       </c>
       <c r="C236" t="n">
-        <v>-49.88295781347892</v>
+        <v>136.9765079923555</v>
       </c>
     </row>
     <row r="237">
@@ -3027,10 +3027,10 @@
         <v>45973</v>
       </c>
       <c r="B237" t="n">
-        <v>3.265378975845286</v>
+        <v>-0.1635495720455494</v>
       </c>
       <c r="C237" t="n">
-        <v>206.7109390359292</v>
+        <v>238.2560274902198</v>
       </c>
     </row>
     <row r="238">
@@ -3038,10 +3038,10 @@
         <v>45974</v>
       </c>
       <c r="B238" t="n">
-        <v>-2.443912347038425</v>
+        <v>0.07298764712649584</v>
       </c>
       <c r="C238" t="n">
-        <v>-224.9120071084492</v>
+        <v>-147.9305505633409</v>
       </c>
     </row>
     <row r="239">
@@ -3049,10 +3049,10 @@
         <v>45975</v>
       </c>
       <c r="B239" t="n">
-        <v>-1.563809605014748</v>
+        <v>0.07680676590881344</v>
       </c>
       <c r="C239" t="n">
-        <v>-162.886683378117</v>
+        <v>-66.99389146799919</v>
       </c>
     </row>
     <row r="240">
@@ -3060,10 +3060,10 @@
         <v>45978</v>
       </c>
       <c r="B240" t="n">
-        <v>1.843483591206507</v>
+        <v>-0.04170936343949316</v>
       </c>
       <c r="C240" t="n">
-        <v>93.6001951241787</v>
+        <v>129.054477368779</v>
       </c>
     </row>
     <row r="241">
@@ -3071,10 +3071,10 @@
         <v>45979</v>
       </c>
       <c r="B241" t="n">
-        <v>3.027538313652547</v>
+        <v>-0.143430327010257</v>
       </c>
       <c r="C241" t="n">
-        <v>262.7061905234667</v>
+        <v>325.6697847339925</v>
       </c>
     </row>
     <row r="242">
@@ -3082,10 +3082,10 @@
         <v>45980</v>
       </c>
       <c r="B242" t="n">
-        <v>6.872611515165445</v>
+        <v>-0.2287794128571413</v>
       </c>
       <c r="C242" t="n">
-        <v>408.332169196344</v>
+        <v>207.0193465273334</v>
       </c>
     </row>
     <row r="243">
@@ -3093,10 +3093,10 @@
         <v>45982</v>
       </c>
       <c r="B243" t="n">
-        <v>-2.117608017228803</v>
+        <v>-0.0133135174521691</v>
       </c>
       <c r="C243" t="n">
-        <v>-117.338962228998</v>
+        <v>103.2858155048812</v>
       </c>
     </row>
     <row r="244">
@@ -3104,10 +3104,10 @@
         <v>45985</v>
       </c>
       <c r="B244" t="n">
-        <v>4.288994296934245</v>
+        <v>-0.2606018007689596</v>
       </c>
       <c r="C244" t="n">
-        <v>359.4580191471755</v>
+        <v>403.4916205678089</v>
       </c>
     </row>
     <row r="245">
@@ -3115,10 +3115,10 @@
         <v>45986</v>
       </c>
       <c r="B245" t="n">
-        <v>-1.141839571348519</v>
+        <v>-0.1045848674549458</v>
       </c>
       <c r="C245" t="n">
-        <v>-11.91888866335373</v>
+        <v>196.2405528950914</v>
       </c>
     </row>
     <row r="246">
@@ -3126,10 +3126,10 @@
         <v>45987</v>
       </c>
       <c r="B246" t="n">
-        <v>3.433741458292041</v>
+        <v>-0.1682912588440969</v>
       </c>
       <c r="C246" t="n">
-        <v>179.5723565919373</v>
+        <v>161.6902565655133</v>
       </c>
     </row>
     <row r="247">
@@ -3137,10 +3137,10 @@
         <v>45988</v>
       </c>
       <c r="B247" t="n">
-        <v>11.78332167847231</v>
+        <v>-0.5578121145619934</v>
       </c>
       <c r="C247" t="n">
-        <v>928.614040202858</v>
+        <v>955.6482897836734</v>
       </c>
     </row>
     <row r="248">
@@ -3148,10 +3148,10 @@
         <v>45989</v>
       </c>
       <c r="B248" t="n">
-        <v>2.425987369426313</v>
+        <v>-0.2557828600675879</v>
       </c>
       <c r="C248" t="n">
-        <v>213.0877341315795</v>
+        <v>490.0117626815207</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/scores_LQdFPC_vs_dFPC.xlsx
+++ b/data/processed/scores_LQdFPC_vs_dFPC.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C248"/>
+  <dimension ref="A1:C237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,10 +442,10 @@
         <v>45628</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2821326660627726</v>
+        <v>-0.3199677806040407</v>
       </c>
       <c r="C2" t="n">
-        <v>-676.9270678869931</v>
+        <v>308.0928456591641</v>
       </c>
     </row>
     <row r="3">
@@ -453,10 +453,10 @@
         <v>45629</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1361968425291906</v>
+        <v>-0.3060079160948328</v>
       </c>
       <c r="C3" t="n">
-        <v>-233.1488990349846</v>
+        <v>241.5784208821212</v>
       </c>
     </row>
     <row r="4">
@@ -464,1066 +464,1066 @@
         <v>45630</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1192486583423305</v>
+        <v>-0.1051362981424056</v>
       </c>
       <c r="C4" t="n">
-        <v>-272.6790261305664</v>
+        <v>126.8350301706176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45631</v>
+        <v>45638</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.01981220149593619</v>
+        <v>-0.2378156479428799</v>
       </c>
       <c r="C5" t="n">
-        <v>-47.38902710729386</v>
+        <v>244.6784609953906</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.01893373355113359</v>
+        <v>-0.081720565554804</v>
       </c>
       <c r="C6" t="n">
-        <v>6.089921835278679</v>
+        <v>82.02481644143023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45635</v>
+        <v>45642</v>
       </c>
       <c r="B7" t="n">
-        <v>0.05121361916942991</v>
+        <v>-0.08905944614156563</v>
       </c>
       <c r="C7" t="n">
-        <v>-136.216917008579</v>
+        <v>110.1767421492495</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45636</v>
+        <v>45643</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.05841344262343538</v>
+        <v>-0.1033259062648123</v>
       </c>
       <c r="C8" t="n">
-        <v>28.25328462825348</v>
+        <v>112.3831226613289</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45637</v>
+        <v>45644</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2599922744982764</v>
+        <v>-0.1431688566972308</v>
       </c>
       <c r="C9" t="n">
-        <v>-359.2283415903883</v>
+        <v>117.4949833279959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45638</v>
+        <v>45645</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1355053255416902</v>
+        <v>-0.4521731425197795</v>
       </c>
       <c r="C10" t="n">
-        <v>-320.2362241951163</v>
+        <v>275.6812582631231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45639</v>
+        <v>45649</v>
       </c>
       <c r="B11" t="n">
-        <v>0.004888165429490229</v>
+        <v>-0.3021484054402842</v>
       </c>
       <c r="C11" t="n">
-        <v>-50.73137407460567</v>
+        <v>223.7526935221946</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45642</v>
+        <v>45653</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.03702116916296824</v>
+        <v>-0.2265171236596509</v>
       </c>
       <c r="C12" t="n">
-        <v>-14.79452406261914</v>
+        <v>200.5938861222197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45643</v>
+        <v>45656</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3439159407446131</v>
+        <v>-0.2271600275843491</v>
       </c>
       <c r="C13" t="n">
-        <v>-484.7518795282328</v>
+        <v>207.9728397230554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45644</v>
+        <v>45657</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2708511722892337</v>
+        <v>-0.234533468626389</v>
       </c>
       <c r="C14" t="n">
-        <v>-564.8400564889067</v>
+        <v>137.1445498432955</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45645</v>
+        <v>45658</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1767620045796244</v>
+        <v>0.1354761898034141</v>
       </c>
       <c r="C15" t="n">
-        <v>-287.2180837760146</v>
+        <v>-117.3582357713789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45646</v>
+        <v>45659</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2098957736521708</v>
+        <v>-0.2092619667228674</v>
       </c>
       <c r="C16" t="n">
-        <v>-277.5903206458269</v>
+        <v>177.4861725779405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45649</v>
+        <v>45660</v>
       </c>
       <c r="B17" t="n">
-        <v>0.06929235339076263</v>
+        <v>-0.008241449981804353</v>
       </c>
       <c r="C17" t="n">
-        <v>-108.0187343611274</v>
+        <v>39.02454942262531</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45652</v>
+        <v>45663</v>
       </c>
       <c r="B18" t="n">
-        <v>0.06392672689680237</v>
+        <v>-0.01581827609165904</v>
       </c>
       <c r="C18" t="n">
-        <v>-96.76492595564167</v>
+        <v>-4.530425074404599</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45653</v>
+        <v>45664</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1740745786201389</v>
+        <v>-0.06379336866931298</v>
       </c>
       <c r="C19" t="n">
-        <v>-401.7551196757236</v>
+        <v>59.04440353660017</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45656</v>
+        <v>45665</v>
       </c>
       <c r="B20" t="n">
-        <v>0.08742391616275701</v>
+        <v>-0.2486904513701181</v>
       </c>
       <c r="C20" t="n">
-        <v>-279.1460972415647</v>
+        <v>127.6871691862489</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45659</v>
+        <v>45666</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2029313628432965</v>
+        <v>-0.2437422286107258</v>
       </c>
       <c r="C21" t="n">
-        <v>-392.0548147705115</v>
+        <v>134.679466200154</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45660</v>
+        <v>45667</v>
       </c>
       <c r="B22" t="n">
-        <v>0.03769517485637008</v>
+        <v>-0.4602534290208659</v>
       </c>
       <c r="C22" t="n">
-        <v>-75.3733446890506</v>
+        <v>253.8095888579915</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45663</v>
+        <v>45670</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1978569353714391</v>
+        <v>-0.5684706078473156</v>
       </c>
       <c r="C23" t="n">
-        <v>-339.5594929120733</v>
+        <v>366.4670998303531</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01982664730358508</v>
+        <v>-0.3511914676100349</v>
       </c>
       <c r="C24" t="n">
-        <v>-4.107225829215239</v>
+        <v>219.2739927624886</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45665</v>
+        <v>45672</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.0133778832738144</v>
+        <v>-0.2567882592662593</v>
       </c>
       <c r="C25" t="n">
-        <v>6.200189376194305</v>
+        <v>146.5931095430471</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45666</v>
+        <v>45673</v>
       </c>
       <c r="B26" t="n">
-        <v>-0.1482171917142642</v>
+        <v>-0.3741780795891652</v>
       </c>
       <c r="C26" t="n">
-        <v>234.1661645421092</v>
+        <v>287.4696760393116</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45667</v>
+        <v>45674</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0522318503530357</v>
+        <v>-0.1328003621599119</v>
       </c>
       <c r="C27" t="n">
-        <v>-61.14920160868949</v>
+        <v>135.9651661137425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45670</v>
+        <v>45677</v>
       </c>
       <c r="B28" t="n">
-        <v>-0.08456143473844764</v>
+        <v>-0.4800305474015321</v>
       </c>
       <c r="C28" t="n">
-        <v>151.6487967834051</v>
+        <v>266.3131812962266</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45671</v>
+        <v>45678</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1468728013142586</v>
+        <v>-0.3765962124958895</v>
       </c>
       <c r="C29" t="n">
-        <v>-220.313064628663</v>
+        <v>299.2513993982092</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45672</v>
+        <v>45679</v>
       </c>
       <c r="B30" t="n">
-        <v>0.09087978119143962</v>
+        <v>-0.1993123235463702</v>
       </c>
       <c r="C30" t="n">
-        <v>-157.3602203054787</v>
+        <v>137.542262117175</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45673</v>
+        <v>45680</v>
       </c>
       <c r="B31" t="n">
-        <v>-0.008435141946986134</v>
+        <v>-0.5571834182964642</v>
       </c>
       <c r="C31" t="n">
-        <v>-42.1561380582426</v>
+        <v>325.5688596873226</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45674</v>
+        <v>45681</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.03226942660009176</v>
+        <v>-0.4469390622718725</v>
       </c>
       <c r="C32" t="n">
-        <v>32.97607909799304</v>
+        <v>278.1975198915557</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45677</v>
+        <v>45684</v>
       </c>
       <c r="B33" t="n">
-        <v>0.05578407660744766</v>
+        <v>-0.4994350772028276</v>
       </c>
       <c r="C33" t="n">
-        <v>-227.2321051801969</v>
+        <v>325.9122143784767</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45678</v>
+        <v>45685</v>
       </c>
       <c r="B34" t="n">
-        <v>-0.01470268120688359</v>
+        <v>-0.1707809127725929</v>
       </c>
       <c r="C34" t="n">
-        <v>-108.5675569309455</v>
+        <v>105.2966209409537</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45679</v>
+        <v>45686</v>
       </c>
       <c r="B35" t="n">
-        <v>-0.08126749938261685</v>
+        <v>-0.2233043122333733</v>
       </c>
       <c r="C35" t="n">
-        <v>1.291796108375347</v>
+        <v>124.4250466242582</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45680</v>
+        <v>45687</v>
       </c>
       <c r="B36" t="n">
-        <v>0.04412088233277407</v>
+        <v>0.04888696438762318</v>
       </c>
       <c r="C36" t="n">
-        <v>-201.5146234671632</v>
+        <v>-25.63766568794761</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45681</v>
+        <v>45688</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.05124189730017822</v>
+        <v>-0.2098563781317687</v>
       </c>
       <c r="C37" t="n">
-        <v>-130.392906728963</v>
+        <v>153.9649516410616</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45684</v>
+        <v>45691</v>
       </c>
       <c r="B38" t="n">
-        <v>0.04036173387015034</v>
+        <v>-0.3819521536124371</v>
       </c>
       <c r="C38" t="n">
-        <v>-164.8671439798531</v>
+        <v>249.3013070558788</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45685</v>
+        <v>45692</v>
       </c>
       <c r="B39" t="n">
-        <v>-0.1515537826046625</v>
+        <v>-0.3378049025699097</v>
       </c>
       <c r="C39" t="n">
-        <v>185.4068817235712</v>
+        <v>228.3094665648313</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45686</v>
+        <v>45693</v>
       </c>
       <c r="B40" t="n">
-        <v>-0.02691825941640765</v>
+        <v>-0.2185892031167993</v>
       </c>
       <c r="C40" t="n">
-        <v>-187.8086973220626</v>
+        <v>176.8095700445841</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45687</v>
+        <v>45694</v>
       </c>
       <c r="B41" t="n">
-        <v>0.06600774346988864</v>
+        <v>-0.2718758576003417</v>
       </c>
       <c r="C41" t="n">
-        <v>-116.7250578797424</v>
+        <v>195.3064734452598</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45695</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01511102398391146</v>
+        <v>-0.3001871347017108</v>
       </c>
       <c r="C42" t="n">
-        <v>-159.732559561699</v>
+        <v>179.8957423383904</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45691</v>
+        <v>45698</v>
       </c>
       <c r="B43" t="n">
-        <v>0.09782089499673959</v>
+        <v>-0.3761729506625765</v>
       </c>
       <c r="C43" t="n">
-        <v>-331.2811509465358</v>
+        <v>252.9893738633033</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45692</v>
+        <v>45699</v>
       </c>
       <c r="B44" t="n">
-        <v>0.02117344989617493</v>
+        <v>-0.02247679661228501</v>
       </c>
       <c r="C44" t="n">
-        <v>-51.4521125474842</v>
+        <v>23.49707813761365</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45693</v>
+        <v>45700</v>
       </c>
       <c r="B45" t="n">
-        <v>0.08875864919972205</v>
+        <v>-0.2865288181892691</v>
       </c>
       <c r="C45" t="n">
-        <v>-242.527401645918</v>
+        <v>148.9788716050124</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45694</v>
+        <v>45701</v>
       </c>
       <c r="B46" t="n">
-        <v>0.06106520671047466</v>
+        <v>0.03498380977894412</v>
       </c>
       <c r="C46" t="n">
-        <v>-177.5822493179261</v>
+        <v>-39.55925183462405</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45695</v>
+        <v>45702</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1014755593370867</v>
+        <v>-0.2390180689736287</v>
       </c>
       <c r="C47" t="n">
-        <v>-328.4423441292449</v>
+        <v>85.8239102248188</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45698</v>
+        <v>45706</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.01055038972535258</v>
+        <v>-0.2779055125967744</v>
       </c>
       <c r="C48" t="n">
-        <v>-11.51747598817533</v>
+        <v>126.4817869802914</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45699</v>
+        <v>45707</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.1425587040518214</v>
+        <v>0.1436301890164844</v>
       </c>
       <c r="C49" t="n">
-        <v>309.6182464516298</v>
+        <v>-128.6161498645413</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45700</v>
+        <v>45708</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1749658111797474</v>
+        <v>0.2656584742794825</v>
       </c>
       <c r="C50" t="n">
-        <v>-290.6012175669017</v>
+        <v>-183.919505454381</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45701</v>
+        <v>45709</v>
       </c>
       <c r="B51" t="n">
-        <v>-0.02861243290079307</v>
+        <v>-0.104167119637611</v>
       </c>
       <c r="C51" t="n">
-        <v>-52.44853485098707</v>
+        <v>43.30363560561891</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45702</v>
+        <v>45712</v>
       </c>
       <c r="B52" t="n">
-        <v>-0.06924915619565263</v>
+        <v>-0.02887031279300326</v>
       </c>
       <c r="C52" t="n">
-        <v>208.3386821205462</v>
+        <v>34.24127654779355</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45705</v>
+        <v>45713</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.215573342358935</v>
+        <v>-0.3907503178631961</v>
       </c>
       <c r="C53" t="n">
-        <v>346.4830966379295</v>
+        <v>242.3620651718807</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45706</v>
+        <v>45714</v>
       </c>
       <c r="B54" t="n">
-        <v>-0.1660320771069764</v>
+        <v>-0.4876648986734305</v>
       </c>
       <c r="C54" t="n">
-        <v>283.6316645511267</v>
+        <v>257.3976024223554</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45707</v>
+        <v>45715</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.1718566939349986</v>
+        <v>-0.395133940920147</v>
       </c>
       <c r="C55" t="n">
-        <v>327.0014700914956</v>
+        <v>255.0856105893383</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45708</v>
+        <v>45716</v>
       </c>
       <c r="B56" t="n">
-        <v>-0.1972239168941018</v>
+        <v>-0.6840938079649932</v>
       </c>
       <c r="C56" t="n">
-        <v>323.5215830364856</v>
+        <v>415.9980038845237</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45709</v>
+        <v>45719</v>
       </c>
       <c r="B57" t="n">
-        <v>-0.06212920224911111</v>
+        <v>-0.7198335836149667</v>
       </c>
       <c r="C57" t="n">
-        <v>67.87662115209838</v>
+        <v>418.5748059711757</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45712</v>
+        <v>45720</v>
       </c>
       <c r="B58" t="n">
-        <v>-0.070996077968789</v>
+        <v>-0.8632343164038055</v>
       </c>
       <c r="C58" t="n">
-        <v>108.0023111807123</v>
+        <v>472.4112368467376</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45713</v>
+        <v>45721</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0620966873640305</v>
+        <v>-0.7093338067115401</v>
       </c>
       <c r="C59" t="n">
-        <v>-221.3894753020504</v>
+        <v>416.2835905988775</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45714</v>
+        <v>45722</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.02983243334724842</v>
+        <v>-0.6063743376051851</v>
       </c>
       <c r="C60" t="n">
-        <v>-79.14499656111157</v>
+        <v>374.7048284885073</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45715</v>
+        <v>45723</v>
       </c>
       <c r="B61" t="n">
-        <v>0.01991771226714071</v>
+        <v>-0.8536466616093125</v>
       </c>
       <c r="C61" t="n">
-        <v>-150.290815945588</v>
+        <v>472.7143773121626</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45716</v>
+        <v>45726</v>
       </c>
       <c r="B62" t="n">
-        <v>0.06790491990376839</v>
+        <v>-0.7543425588476442</v>
       </c>
       <c r="C62" t="n">
-        <v>-158.8920489962713</v>
+        <v>406.4329989820421</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="B63" t="n">
-        <v>0.3064156146981225</v>
+        <v>-0.712022996778503</v>
       </c>
       <c r="C63" t="n">
-        <v>-578.0399511697548</v>
+        <v>396.2106877439817</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45723</v>
+        <v>45728</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2430958551167186</v>
+        <v>-0.4492466834521562</v>
       </c>
       <c r="C64" t="n">
-        <v>-386.0777860776172</v>
+        <v>264.7314673393208</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45726</v>
+        <v>45729</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2011295486047781</v>
+        <v>-0.3419823341761549</v>
       </c>
       <c r="C65" t="n">
-        <v>-342.4187621321535</v>
+        <v>254.3298041771559</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45727</v>
+        <v>45730</v>
       </c>
       <c r="B66" t="n">
-        <v>0.07114924255110286</v>
+        <v>-0.3018552726416857</v>
       </c>
       <c r="C66" t="n">
-        <v>-134.9525756342203</v>
+        <v>175.1272045625196</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45728</v>
+        <v>45733</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2306556863333392</v>
+        <v>-0.1670049310600873</v>
       </c>
       <c r="C67" t="n">
-        <v>-426.9736118060816</v>
+        <v>148.6588717563104</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>45729</v>
+        <v>45734</v>
       </c>
       <c r="B68" t="n">
-        <v>-0.02441231514599105</v>
+        <v>-0.1835447711601708</v>
       </c>
       <c r="C68" t="n">
-        <v>54.32413104468364</v>
+        <v>135.2460515444195</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>45730</v>
+        <v>45735</v>
       </c>
       <c r="B69" t="n">
-        <v>0.01386670857730008</v>
+        <v>-0.2193770267579351</v>
       </c>
       <c r="C69" t="n">
-        <v>-23.51667729037399</v>
+        <v>169.4335943214889</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45733</v>
+        <v>45736</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.06914458150291564</v>
+        <v>-0.2544413863689938</v>
       </c>
       <c r="C70" t="n">
-        <v>60.11405994930151</v>
+        <v>241.4195987320905</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>45734</v>
+        <v>45737</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1024698719115919</v>
+        <v>-0.1313865419138924</v>
       </c>
       <c r="C71" t="n">
-        <v>-134.7805842445453</v>
+        <v>174.0874119154529</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45735</v>
+        <v>45740</v>
       </c>
       <c r="B72" t="n">
-        <v>0.01835448866583714</v>
+        <v>-0.09319554261242248</v>
       </c>
       <c r="C72" t="n">
-        <v>-3.962897109693724</v>
+        <v>148.5587813766869</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>45736</v>
+        <v>45741</v>
       </c>
       <c r="B73" t="n">
-        <v>-0.143607191595945</v>
+        <v>-0.01779584822712086</v>
       </c>
       <c r="C73" t="n">
-        <v>291.2263294715491</v>
+        <v>68.21335101425289</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>45737</v>
+        <v>45742</v>
       </c>
       <c r="B74" t="n">
-        <v>-0.1712054580283473</v>
+        <v>-0.01785429105531975</v>
       </c>
       <c r="C74" t="n">
-        <v>310.1037527698296</v>
+        <v>100.6319633058685</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>45740</v>
+        <v>45743</v>
       </c>
       <c r="B75" t="n">
-        <v>-0.1182295638093926</v>
+        <v>0.0916027248154663</v>
       </c>
       <c r="C75" t="n">
-        <v>246.9947190494842</v>
+        <v>-59.65453968676257</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>45741</v>
+        <v>45744</v>
       </c>
       <c r="B76" t="n">
-        <v>-0.09741646801408908</v>
+        <v>0.009458663551778917</v>
       </c>
       <c r="C76" t="n">
-        <v>233.2677876604538</v>
+        <v>78.96232426808035</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>45742</v>
+        <v>45747</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.1038033326342487</v>
+        <v>-0.1818198032803027</v>
       </c>
       <c r="C77" t="n">
-        <v>266.9107736138578</v>
+        <v>143.4078847677864</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>45743</v>
+        <v>45748</v>
       </c>
       <c r="B78" t="n">
-        <v>-0.02986273542859296</v>
+        <v>-0.03927938895888396</v>
       </c>
       <c r="C78" t="n">
-        <v>93.35570137375127</v>
+        <v>58.45197712650116</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>45744</v>
+        <v>45749</v>
       </c>
       <c r="B79" t="n">
-        <v>0.01456611950641527</v>
+        <v>-0.08293372495466897</v>
       </c>
       <c r="C79" t="n">
-        <v>65.15186597531286</v>
+        <v>34.40842101670836</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45747</v>
+        <v>45750</v>
       </c>
       <c r="B80" t="n">
-        <v>-0.02058057452887709</v>
+        <v>-0.1814235015904798</v>
       </c>
       <c r="C80" t="n">
-        <v>29.65780109429744</v>
+        <v>130.6292441979426</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>45748</v>
+        <v>45751</v>
       </c>
       <c r="B81" t="n">
-        <v>-0.006244022350382373</v>
+        <v>-0.3438179471638066</v>
       </c>
       <c r="C81" t="n">
-        <v>78.41844208216416</v>
+        <v>205.8936849885475</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>45749</v>
+        <v>45754</v>
       </c>
       <c r="B82" t="n">
-        <v>-0.1005484962078494</v>
+        <v>-0.4812070647732836</v>
       </c>
       <c r="C82" t="n">
-        <v>157.3001818679755</v>
+        <v>282.7575201969217</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45750</v>
+        <v>45755</v>
       </c>
       <c r="B83" t="n">
-        <v>0.2632314321103676</v>
+        <v>-0.3652320839212648</v>
       </c>
       <c r="C83" t="n">
-        <v>-345.5123461882808</v>
+        <v>256.4227051003579</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>45751</v>
+        <v>45756</v>
       </c>
       <c r="B84" t="n">
-        <v>0.5048831925665174</v>
+        <v>-0.5347011337963895</v>
       </c>
       <c r="C84" t="n">
-        <v>-578.8651703839713</v>
+        <v>338.6218922500148</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45754</v>
+        <v>45757</v>
       </c>
       <c r="B85" t="n">
-        <v>0.8455429399037894</v>
+        <v>-0.3846781440840868</v>
       </c>
       <c r="C85" t="n">
-        <v>-804.9072013471533</v>
+        <v>270.4828517470399</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>45755</v>
+        <v>45758</v>
       </c>
       <c r="B86" t="n">
-        <v>0.822828399161913</v>
+        <v>-0.2414041833737891</v>
       </c>
       <c r="C86" t="n">
-        <v>-829.7147340828724</v>
+        <v>146.5057976884592</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>45756</v>
+        <v>45761</v>
       </c>
       <c r="B87" t="n">
-        <v>1.153764522581482</v>
+        <v>-0.2188346467123609</v>
       </c>
       <c r="C87" t="n">
-        <v>-1142.589547186003</v>
+        <v>135.0579765367908</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>45757</v>
+        <v>45762</v>
       </c>
       <c r="B88" t="n">
-        <v>1.056999767282792</v>
+        <v>-0.05164163007603431</v>
       </c>
       <c r="C88" t="n">
-        <v>-1221.043605127301</v>
+        <v>34.97159349949514</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>45758</v>
+        <v>45763</v>
       </c>
       <c r="B89" t="n">
-        <v>0.8281250680663214</v>
+        <v>-0.2033439108224901</v>
       </c>
       <c r="C89" t="n">
-        <v>-1090.484704388089</v>
+        <v>186.6743630193548</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45761</v>
+        <v>45764</v>
       </c>
       <c r="B90" t="n">
-        <v>0.6231865659779406</v>
+        <v>0.0560180007477968</v>
       </c>
       <c r="C90" t="n">
-        <v>-885.513460465383</v>
+        <v>25.75236457221618</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45762</v>
+        <v>45765</v>
       </c>
       <c r="B91" t="n">
-        <v>0.4698684376427613</v>
+        <v>0.5964003120077263</v>
       </c>
       <c r="C91" t="n">
-        <v>-669.1009970376138</v>
+        <v>-452.6462790093543</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>45763</v>
+        <v>45768</v>
       </c>
       <c r="B92" t="n">
-        <v>0.544063002190586</v>
+        <v>0.2067647292064463</v>
       </c>
       <c r="C92" t="n">
-        <v>-775.118031658494</v>
+        <v>-164.027528023148</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>45764</v>
+        <v>45769</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3539128882714861</v>
+        <v>0.09724247855779146</v>
       </c>
       <c r="C93" t="n">
-        <v>-526.2504722889042</v>
+        <v>-75.7342946451226</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45769</v>
+        <v>45770</v>
       </c>
       <c r="B94" t="n">
-        <v>0.310478731212094</v>
+        <v>0.1538880822012863</v>
       </c>
       <c r="C94" t="n">
-        <v>-542.5345683163262</v>
+        <v>-135.3071660248387</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="B95" t="n">
-        <v>0.3916655087368283</v>
+        <v>0.2487951197789274</v>
       </c>
       <c r="C95" t="n">
-        <v>-601.10479396234</v>
+        <v>-194.6218647264641</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>45771</v>
+        <v>45772</v>
       </c>
       <c r="B96" t="n">
-        <v>0.2458890128312182</v>
+        <v>0.0345920128924516</v>
       </c>
       <c r="C96" t="n">
-        <v>-386.3668205505892</v>
+        <v>10.66967608380225</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45772</v>
+        <v>45775</v>
       </c>
       <c r="B97" t="n">
-        <v>0.1063122299702835</v>
+        <v>0.07092263369258622</v>
       </c>
       <c r="C97" t="n">
-        <v>-233.4360146748986</v>
+        <v>-26.13209837999606</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1018261968228473</v>
+        <v>0.2548683258490437</v>
       </c>
       <c r="C98" t="n">
-        <v>-209.6103430817067</v>
+        <v>-180.9119822440405</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="B99" t="n">
-        <v>0.06152570531190765</v>
+        <v>0.2060567717445685</v>
       </c>
       <c r="C99" t="n">
-        <v>-165.2736316093551</v>
+        <v>-142.5141246504641</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>45777</v>
+        <v>45778</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1160912202648417</v>
+        <v>0.1895696216159836</v>
       </c>
       <c r="C100" t="n">
-        <v>-210.8823053216047</v>
+        <v>-101.0368330017361</v>
       </c>
     </row>
     <row r="101">
@@ -1531,10 +1531,10 @@
         <v>45779</v>
       </c>
       <c r="B101" t="n">
-        <v>0.08003708907772743</v>
+        <v>0.189771824626576</v>
       </c>
       <c r="C101" t="n">
-        <v>-176.2742087557242</v>
+        <v>-98.5577455496886</v>
       </c>
     </row>
     <row r="102">
@@ -1542,10 +1542,10 @@
         <v>45782</v>
       </c>
       <c r="B102" t="n">
-        <v>0.02202841335830757</v>
+        <v>0.2452048914343493</v>
       </c>
       <c r="C102" t="n">
-        <v>-137.0792897848946</v>
+        <v>-154.2362349957019</v>
       </c>
     </row>
     <row r="103">
@@ -1553,10 +1553,10 @@
         <v>45783</v>
       </c>
       <c r="B103" t="n">
-        <v>0.02912770134832982</v>
+        <v>0.191779225793571</v>
       </c>
       <c r="C103" t="n">
-        <v>-142.6019856075162</v>
+        <v>-120.5916092436028</v>
       </c>
     </row>
     <row r="104">
@@ -1564,10 +1564,10 @@
         <v>45784</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0004595918653193551</v>
+        <v>0.1220107854401788</v>
       </c>
       <c r="C104" t="n">
-        <v>-30.06794897309588</v>
+        <v>-89.85004697829082</v>
       </c>
     </row>
     <row r="105">
@@ -1575,10 +1575,10 @@
         <v>45785</v>
       </c>
       <c r="B105" t="n">
-        <v>0.2226844485375475</v>
+        <v>0.2167093125175734</v>
       </c>
       <c r="C105" t="n">
-        <v>-347.9661514451623</v>
+        <v>-153.8288482236489</v>
       </c>
     </row>
     <row r="106">
@@ -1586,1572 +1586,1451 @@
         <v>45786</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.1502146861671533</v>
+        <v>0.2211247601550591</v>
       </c>
       <c r="C106" t="n">
-        <v>350.3896938931555</v>
+        <v>-159.5699965293234</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>45789</v>
+        <v>45790</v>
       </c>
       <c r="B107" t="n">
-        <v>0.02878074175349769</v>
+        <v>0.09681812860163813</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.335673437938835</v>
+        <v>-36.24689734795857</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>45790</v>
+        <v>45791</v>
       </c>
       <c r="B108" t="n">
-        <v>-0.0004967562413503693</v>
+        <v>0.1120799603017509</v>
       </c>
       <c r="C108" t="n">
-        <v>57.41270805820025</v>
+        <v>-31.75104188003104</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
       <c r="B109" t="n">
-        <v>0.01402002465320694</v>
+        <v>0.02140307271114902</v>
       </c>
       <c r="C109" t="n">
-        <v>-1.792185742487922</v>
+        <v>72.13086051732076</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>45792</v>
+        <v>45797</v>
       </c>
       <c r="B110" t="n">
-        <v>0.08677186516358927</v>
+        <v>0.04399077207449174</v>
       </c>
       <c r="C110" t="n">
-        <v>-131.6396915264471</v>
+        <v>37.40037718044669</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45793</v>
+        <v>45798</v>
       </c>
       <c r="B111" t="n">
-        <v>0.168260239666116</v>
+        <v>-0.1837730736037162</v>
       </c>
       <c r="C111" t="n">
-        <v>-278.7259504765821</v>
+        <v>158.5175888214317</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>45796</v>
+        <v>45799</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.006318561637842245</v>
+        <v>0.03235242478030414</v>
       </c>
       <c r="C112" t="n">
-        <v>-137.8978320151574</v>
+        <v>31.00482325339929</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>45797</v>
+        <v>45800</v>
       </c>
       <c r="B113" t="n">
-        <v>0.06034836822870143</v>
+        <v>-0.0950156285740904</v>
       </c>
       <c r="C113" t="n">
-        <v>-268.3154778915106</v>
+        <v>138.3274555736327</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>45798</v>
+        <v>45803</v>
       </c>
       <c r="B114" t="n">
-        <v>0.1240577804057286</v>
+        <v>0.3178437859653455</v>
       </c>
       <c r="C114" t="n">
-        <v>-307.7043599030822</v>
+        <v>-272.9110799119821</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>45799</v>
+        <v>45804</v>
       </c>
       <c r="B115" t="n">
-        <v>0.1721233129918538</v>
+        <v>0.1049059348244398</v>
       </c>
       <c r="C115" t="n">
-        <v>-362.3509731911612</v>
+        <v>-103.8564605710029</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45800</v>
+        <v>45805</v>
       </c>
       <c r="B116" t="n">
-        <v>0.3189036422552745</v>
+        <v>0.270908461778029</v>
       </c>
       <c r="C116" t="n">
-        <v>-540.9805387190976</v>
+        <v>-220.4198867504339</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>45803</v>
+        <v>45806</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.02627671854608504</v>
+        <v>0.05350424412474802</v>
       </c>
       <c r="C117" t="n">
-        <v>128.3368842259933</v>
+        <v>-55.10435634767272</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>45804</v>
+        <v>45807</v>
       </c>
       <c r="B118" t="n">
-        <v>0.1718220532181002</v>
+        <v>0.1774457777206888</v>
       </c>
       <c r="C118" t="n">
-        <v>-257.4295631613413</v>
+        <v>-156.0782185466323</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>45805</v>
+        <v>45810</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.02099488140844974</v>
+        <v>0.1719423159559202</v>
       </c>
       <c r="C119" t="n">
-        <v>46.12133145892561</v>
+        <v>-125.893518370731</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>45806</v>
+        <v>45811</v>
       </c>
       <c r="B120" t="n">
-        <v>0.06504454705932024</v>
+        <v>0.2129472117332323</v>
       </c>
       <c r="C120" t="n">
-        <v>-95.84890754490289</v>
+        <v>-156.3797221055849</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45807</v>
+        <v>45812</v>
       </c>
       <c r="B121" t="n">
-        <v>0.09854868415906781</v>
+        <v>0.4240759003851126</v>
       </c>
       <c r="C121" t="n">
-        <v>-254.5745742880351</v>
+        <v>-319.4878771047855</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>45810</v>
+        <v>45813</v>
       </c>
       <c r="B122" t="n">
-        <v>0.1799545549307318</v>
+        <v>0.06146826161380686</v>
       </c>
       <c r="C122" t="n">
-        <v>-296.1334564389725</v>
+        <v>-40.73271772124195</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>45811</v>
+        <v>45814</v>
       </c>
       <c r="B123" t="n">
-        <v>0.01655799569366794</v>
+        <v>0.2695222027952907</v>
       </c>
       <c r="C123" t="n">
-        <v>15.98482172931866</v>
+        <v>-215.7090463586487</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>45812</v>
+        <v>45817</v>
       </c>
       <c r="B124" t="n">
-        <v>0.1533845866521059</v>
+        <v>0.2097123566269942</v>
       </c>
       <c r="C124" t="n">
-        <v>-290.1705985343185</v>
+        <v>-131.6364860106995</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>45813</v>
+        <v>45818</v>
       </c>
       <c r="B125" t="n">
-        <v>0.04944437234136236</v>
+        <v>0.2573269351719343</v>
       </c>
       <c r="C125" t="n">
-        <v>-146.9024764386415</v>
+        <v>-162.8123560991993</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45814</v>
+        <v>45819</v>
       </c>
       <c r="B126" t="n">
-        <v>0.1052753454947454</v>
+        <v>0.142556838442016</v>
       </c>
       <c r="C126" t="n">
-        <v>-171.1103335975553</v>
+        <v>-67.80596575300905</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45817</v>
+        <v>45820</v>
       </c>
       <c r="B127" t="n">
-        <v>0.1414582487657005</v>
+        <v>0.1970066692820742</v>
       </c>
       <c r="C127" t="n">
-        <v>-213.4601431781341</v>
+        <v>-163.4099197844779</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>45818</v>
+        <v>45821</v>
       </c>
       <c r="B128" t="n">
-        <v>0.08318496971076685</v>
+        <v>0.07837477634623052</v>
       </c>
       <c r="C128" t="n">
-        <v>-117.7449970471175</v>
+        <v>-49.65767049142369</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>45819</v>
+        <v>45824</v>
       </c>
       <c r="B129" t="n">
-        <v>0.2061861205293944</v>
+        <v>0.2542256386254508</v>
       </c>
       <c r="C129" t="n">
-        <v>-330.6582883925609</v>
+        <v>-155.1990429570978</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>45820</v>
+        <v>45825</v>
       </c>
       <c r="B130" t="n">
-        <v>0.07056970618340216</v>
+        <v>0.06892518871807521</v>
       </c>
       <c r="C130" t="n">
-        <v>-149.3007863115981</v>
+        <v>-34.97111911958358</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>45821</v>
+        <v>45826</v>
       </c>
       <c r="B131" t="n">
-        <v>0.02953343614693172</v>
+        <v>-0.02234019427377158</v>
       </c>
       <c r="C131" t="n">
-        <v>-48.26909645594314</v>
+        <v>27.73524723465484</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>45824</v>
+        <v>45827</v>
       </c>
       <c r="B132" t="n">
-        <v>-0.02655901985411836</v>
+        <v>0.4305367908107437</v>
       </c>
       <c r="C132" t="n">
-        <v>58.45990826235894</v>
+        <v>-302.461815199935</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>45825</v>
+        <v>45828</v>
       </c>
       <c r="B133" t="n">
-        <v>-0.01769425317638542</v>
+        <v>0.1730817104398115</v>
       </c>
       <c r="C133" t="n">
-        <v>0.9393459461140433</v>
+        <v>-132.5789192241226</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>45826</v>
+        <v>45831</v>
       </c>
       <c r="B134" t="n">
-        <v>0.05379218015006391</v>
+        <v>-0.1314832497902327</v>
       </c>
       <c r="C134" t="n">
-        <v>-121.1826806884708</v>
+        <v>86.85395708445763</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45828</v>
+        <v>45832</v>
       </c>
       <c r="B135" t="n">
-        <v>0.04807624477599784</v>
+        <v>0.1322967826206307</v>
       </c>
       <c r="C135" t="n">
-        <v>-68.43106496806645</v>
+        <v>-52.38395103415257</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>45831</v>
+        <v>45833</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.1146550835482331</v>
+        <v>0.1292008327324012</v>
       </c>
       <c r="C136" t="n">
-        <v>-5.682099741637889</v>
+        <v>-81.34795640674196</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>45832</v>
+        <v>45834</v>
       </c>
       <c r="B137" t="n">
-        <v>0.02907384690406389</v>
+        <v>0.2508631058091951</v>
       </c>
       <c r="C137" t="n">
-        <v>-99.67464882271923</v>
+        <v>-202.6022790514809</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>45833</v>
+        <v>45835</v>
       </c>
       <c r="B138" t="n">
-        <v>-0.04148892142992826</v>
+        <v>0.2179046744674823</v>
       </c>
       <c r="C138" t="n">
-        <v>-5.313655217414069</v>
+        <v>-159.9085951594315</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>45834</v>
+        <v>45838</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.1149455542085683</v>
+        <v>0.2577356383604807</v>
       </c>
       <c r="C139" t="n">
-        <v>121.9285312870202</v>
+        <v>-201.2293004345659</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45835</v>
+        <v>45839</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.1123005645379645</v>
+        <v>0.286073626683527</v>
       </c>
       <c r="C140" t="n">
-        <v>166.5099384095761</v>
+        <v>-214.8778475424886</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="B141" t="n">
-        <v>0.009960473745093021</v>
+        <v>0.304727121807174</v>
       </c>
       <c r="C141" t="n">
-        <v>-146.4114040132648</v>
+        <v>-219.655688147272</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>45839</v>
+        <v>45841</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.04872476216290732</v>
+        <v>0.3292087160799029</v>
       </c>
       <c r="C142" t="n">
-        <v>-88.64432753045359</v>
+        <v>-271.8160111071822</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>45840</v>
+        <v>45842</v>
       </c>
       <c r="B143" t="n">
-        <v>-0.1102317639391638</v>
+        <v>0.4989135547465431</v>
       </c>
       <c r="C143" t="n">
-        <v>117.6657582516705</v>
+        <v>-383.1976042083302</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45841</v>
+        <v>45845</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.0917792477279579</v>
+        <v>0.4132147600385603</v>
       </c>
       <c r="C144" t="n">
-        <v>139.6012333903091</v>
+        <v>-325.0430987307318</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>45842</v>
+        <v>45846</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.4297111819554323</v>
+        <v>0.5482539843422695</v>
       </c>
       <c r="C145" t="n">
-        <v>728.4338000944801</v>
+        <v>-429.2981651861473</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>45845</v>
+        <v>45847</v>
       </c>
       <c r="B146" t="n">
-        <v>-0.2462496070745798</v>
+        <v>0.3976595255208734</v>
       </c>
       <c r="C146" t="n">
-        <v>432.937109293432</v>
+        <v>-321.9822826422335</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>45846</v>
+        <v>45848</v>
       </c>
       <c r="B147" t="n">
-        <v>-0.1053670284103708</v>
+        <v>0.2121330492441739</v>
       </c>
       <c r="C147" t="n">
-        <v>153.8424828060042</v>
+        <v>-148.5923661802492</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>45847</v>
+        <v>45849</v>
       </c>
       <c r="B148" t="n">
-        <v>-0.2030312418719014</v>
+        <v>0.3056332031185597</v>
       </c>
       <c r="C148" t="n">
-        <v>384.7134974144089</v>
+        <v>-199.2068108247673</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>45848</v>
+        <v>45852</v>
       </c>
       <c r="B149" t="n">
-        <v>0.03353108042481119</v>
+        <v>0.1519434440610891</v>
       </c>
       <c r="C149" t="n">
-        <v>-1.845249626465286</v>
+        <v>-115.1067402078888</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>45849</v>
+        <v>45853</v>
       </c>
       <c r="B150" t="n">
-        <v>-0.1629803293788029</v>
+        <v>-0.09281642521545347</v>
       </c>
       <c r="C150" t="n">
-        <v>312.8376123481504</v>
+        <v>64.67260121200611</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>45852</v>
+        <v>45854</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.1388112513516579</v>
+        <v>-0.03467677141168738</v>
       </c>
       <c r="C151" t="n">
-        <v>224.8500705498747</v>
+        <v>31.98081020369685</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>45853</v>
+        <v>45855</v>
       </c>
       <c r="B152" t="n">
-        <v>0.000329044685442042</v>
+        <v>0.1004981798647563</v>
       </c>
       <c r="C152" t="n">
-        <v>13.97364091105158</v>
+        <v>-53.28221256905805</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>45854</v>
+        <v>45856</v>
       </c>
       <c r="B153" t="n">
-        <v>0.03789057554088147</v>
+        <v>0.107968147253958</v>
       </c>
       <c r="C153" t="n">
-        <v>-41.21970626069919</v>
+        <v>-66.42225651018741</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>45855</v>
+        <v>45859</v>
       </c>
       <c r="B154" t="n">
-        <v>0.05282155337434827</v>
+        <v>0.1071301608708422</v>
       </c>
       <c r="C154" t="n">
-        <v>-137.3233151712027</v>
+        <v>-29.00996246896006</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>45856</v>
+        <v>45860</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.0009852775463075466</v>
+        <v>0.2675312537309497</v>
       </c>
       <c r="C155" t="n">
-        <v>-25.69085590930568</v>
+        <v>-196.6894995706846</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>45859</v>
+        <v>45861</v>
       </c>
       <c r="B156" t="n">
-        <v>0.01032174159694871</v>
+        <v>0.1883522740824318</v>
       </c>
       <c r="C156" t="n">
-        <v>-97.50624274671299</v>
+        <v>-107.9272435537237</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>45860</v>
+        <v>45862</v>
       </c>
       <c r="B157" t="n">
-        <v>0.07855246348782768</v>
+        <v>0.2166499000633263</v>
       </c>
       <c r="C157" t="n">
-        <v>-236.0063122577194</v>
+        <v>-99.39415909522236</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>45861</v>
+        <v>45863</v>
       </c>
       <c r="B158" t="n">
-        <v>-0.004640039078549864</v>
+        <v>0.2235518117808374</v>
       </c>
       <c r="C158" t="n">
-        <v>-44.70331455430198</v>
+        <v>-64.18604080175133</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>45862</v>
+        <v>45866</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.1637727984295882</v>
+        <v>0.3060482483537511</v>
       </c>
       <c r="C159" t="n">
-        <v>268.4535702219125</v>
+        <v>-190.0857436975897</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>45863</v>
+        <v>45867</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.141911365228346</v>
+        <v>0.3226533429413596</v>
       </c>
       <c r="C160" t="n">
-        <v>233.3861420328568</v>
+        <v>-180.7815714542526</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>45866</v>
+        <v>45868</v>
       </c>
       <c r="B161" t="n">
-        <v>-0.1953000292354294</v>
+        <v>0.2920522253898832</v>
       </c>
       <c r="C161" t="n">
-        <v>336.8791317839843</v>
+        <v>-188.5748647410117</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>45867</v>
+        <v>45869</v>
       </c>
       <c r="B162" t="n">
-        <v>-0.2521765909832155</v>
+        <v>0.3142638472040287</v>
       </c>
       <c r="C162" t="n">
-        <v>464.9666786323837</v>
+        <v>-197.5480838822519</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>45868</v>
+        <v>45870</v>
       </c>
       <c r="B163" t="n">
-        <v>0.2040620505075545</v>
+        <v>0.1258847183088852</v>
       </c>
       <c r="C163" t="n">
-        <v>-194.9379575307135</v>
+        <v>-59.76163512690842</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>45869</v>
+        <v>45873</v>
       </c>
       <c r="B164" t="n">
-        <v>0.09415615423728331</v>
+        <v>0.2744346528569001</v>
       </c>
       <c r="C164" t="n">
-        <v>-81.00368364433839</v>
+        <v>-185.267465781269</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="B165" t="n">
-        <v>0.1397577650626506</v>
+        <v>0.3972742707820967</v>
       </c>
       <c r="C165" t="n">
-        <v>-159.107945041034</v>
+        <v>-323.5396402832804</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="B166" t="n">
-        <v>0.1891095739951157</v>
+        <v>0.3067146139921635</v>
       </c>
       <c r="C166" t="n">
-        <v>-281.6066370933092</v>
+        <v>-219.5282961146577</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="B167" t="n">
-        <v>0.2010328479383444</v>
+        <v>0.355620731750565</v>
       </c>
       <c r="C167" t="n">
-        <v>-357.516206844726</v>
+        <v>-270.8328116545796</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>45876</v>
+        <v>45877</v>
       </c>
       <c r="B168" t="n">
-        <v>0.1143829670700692</v>
+        <v>0.3711415300565933</v>
       </c>
       <c r="C168" t="n">
-        <v>-236.7784265412981</v>
+        <v>-263.3505559801493</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>45877</v>
+        <v>45880</v>
       </c>
       <c r="B169" t="n">
-        <v>0.04588093638143429</v>
+        <v>0.2843411790027912</v>
       </c>
       <c r="C169" t="n">
-        <v>-203.5433345448703</v>
+        <v>-191.2604722778707</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>45880</v>
+        <v>45881</v>
       </c>
       <c r="B170" t="n">
-        <v>-0.01995920627469302</v>
+        <v>0.3009686962980906</v>
       </c>
       <c r="C170" t="n">
-        <v>6.669618059505808</v>
+        <v>-226.2267510741785</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>45881</v>
+        <v>45882</v>
       </c>
       <c r="B171" t="n">
-        <v>0.08421047779785745</v>
+        <v>0.1601986794634593</v>
       </c>
       <c r="C171" t="n">
-        <v>-161.4021167766267</v>
+        <v>-100.5073047839619</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>45882</v>
+        <v>45883</v>
       </c>
       <c r="B172" t="n">
-        <v>-0.04527901791613874</v>
+        <v>0.1185254042101671</v>
       </c>
       <c r="C172" t="n">
-        <v>-26.79641135421756</v>
+        <v>-95.39492437709208</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>45883</v>
+        <v>45884</v>
       </c>
       <c r="B173" t="n">
-        <v>0.05952841977620652</v>
+        <v>0.1994698791143099</v>
       </c>
       <c r="C173" t="n">
-        <v>-98.05674936942364</v>
+        <v>-100.2846723012462</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="B174" t="n">
-        <v>0.005514894803715128</v>
+        <v>0.3433395731227383</v>
       </c>
       <c r="C174" t="n">
-        <v>-37.74212785906288</v>
+        <v>-241.9258222814225</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="B175" t="n">
-        <v>-0.1775282651888689</v>
+        <v>0.2043306819266451</v>
       </c>
       <c r="C175" t="n">
-        <v>258.9218558016409</v>
+        <v>-121.0923848413915</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="B176" t="n">
-        <v>0.1226067663117323</v>
+        <v>0.1101765015316739</v>
       </c>
       <c r="C176" t="n">
-        <v>-209.0787174053756</v>
+        <v>-74.1064363834452</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.1688057145869944</v>
+        <v>0.3150032857667718</v>
       </c>
       <c r="C177" t="n">
-        <v>266.415647304074</v>
+        <v>-203.3197451797771</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>45890</v>
+        <v>45891</v>
       </c>
       <c r="B178" t="n">
-        <v>-0.1196055434115626</v>
+        <v>0.1894654241243623</v>
       </c>
       <c r="C178" t="n">
-        <v>198.6628775569741</v>
+        <v>-172.2851537413492</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>45891</v>
+        <v>45901</v>
       </c>
       <c r="B179" t="n">
-        <v>0.04687389917074106</v>
+        <v>0.4049786175740684</v>
       </c>
       <c r="C179" t="n">
-        <v>-56.78886878402383</v>
+        <v>-275.3405840224241</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>45894</v>
+        <v>45902</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.2195010622732331</v>
+        <v>0.1634874301041986</v>
       </c>
       <c r="C180" t="n">
-        <v>372.2746158110531</v>
+        <v>-83.25698963800801</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45895</v>
+        <v>45903</v>
       </c>
       <c r="B181" t="n">
-        <v>-0.2992086068637245</v>
+        <v>0.2583901946486566</v>
       </c>
       <c r="C181" t="n">
-        <v>508.7542912163954</v>
+        <v>-190.0952725622712</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>45896</v>
+        <v>45904</v>
       </c>
       <c r="B182" t="n">
-        <v>-0.126498456722697</v>
+        <v>0.3870634300040545</v>
       </c>
       <c r="C182" t="n">
-        <v>128.1553300390887</v>
+        <v>-287.1711052222683</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>45897</v>
+        <v>45905</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.14375631507178</v>
+        <v>0.350809796630046</v>
       </c>
       <c r="C183" t="n">
-        <v>248.5745908434426</v>
+        <v>-245.5932800068143</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>45898</v>
+        <v>45908</v>
       </c>
       <c r="B184" t="n">
-        <v>-0.3603264531526427</v>
+        <v>0.4309405447649678</v>
       </c>
       <c r="C184" t="n">
-        <v>607.3570940573888</v>
+        <v>-319.8001514131151</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>45901</v>
+        <v>45909</v>
       </c>
       <c r="B185" t="n">
-        <v>-0.3783446114104213</v>
+        <v>0.3081109079952379</v>
       </c>
       <c r="C185" t="n">
-        <v>633.8723095769277</v>
+        <v>-169.6181170741782</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>45902</v>
+        <v>45910</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.1182342852655772</v>
+        <v>0.3885046229268624</v>
       </c>
       <c r="C186" t="n">
-        <v>230.8514026310649</v>
+        <v>-287.2648111268527</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="B187" t="n">
-        <v>-0.3646133164085937</v>
+        <v>0.5682464943742886</v>
       </c>
       <c r="C187" t="n">
-        <v>670.1840827320639</v>
+        <v>-445.6430930018405</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>45904</v>
+        <v>45912</v>
       </c>
       <c r="B188" t="n">
-        <v>-0.2667846873523189</v>
+        <v>0.440221181654236</v>
       </c>
       <c r="C188" t="n">
-        <v>422.6399913913842</v>
+        <v>-294.2997593576086</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="B189" t="n">
-        <v>-0.007949315478976782</v>
+        <v>0.4454639824489938</v>
       </c>
       <c r="C189" t="n">
-        <v>82.52811998263628</v>
+        <v>-326.2295414223104</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>45908</v>
+        <v>45916</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.2067272808312185</v>
+        <v>0.6038341863861851</v>
       </c>
       <c r="C190" t="n">
-        <v>358.3676570173591</v>
+        <v>-454.7148531559433</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>45909</v>
+        <v>45917</v>
       </c>
       <c r="B191" t="n">
-        <v>-0.4024612569384927</v>
+        <v>0.5137895189215929</v>
       </c>
       <c r="C191" t="n">
-        <v>680.7250051763376</v>
+        <v>-395.3705859553151</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>45910</v>
+        <v>45918</v>
       </c>
       <c r="B192" t="n">
-        <v>-0.1581556892515101</v>
+        <v>0.6866999238438107</v>
       </c>
       <c r="C192" t="n">
-        <v>284.4774020608213</v>
+        <v>-500.0185987812456</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="B193" t="n">
-        <v>-0.2023784934286524</v>
+        <v>0.7084413017892716</v>
       </c>
       <c r="C193" t="n">
-        <v>414.1443579269615</v>
+        <v>-518.9156917492195</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>45912</v>
+        <v>45922</v>
       </c>
       <c r="B194" t="n">
-        <v>-0.1993283110325867</v>
+        <v>0.553292240178282</v>
       </c>
       <c r="C194" t="n">
-        <v>406.861383629365</v>
+        <v>-400.5586707645767</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.1835862231721446</v>
+        <v>0.514168356993788</v>
       </c>
       <c r="C195" t="n">
-        <v>332.7855048487661</v>
+        <v>-288.6891665220822</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>45916</v>
+        <v>45924</v>
       </c>
       <c r="B196" t="n">
-        <v>-0.2179660854258138</v>
+        <v>0.7117309500651899</v>
       </c>
       <c r="C196" t="n">
-        <v>357.853120814365</v>
+        <v>-520.3328732657576</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="B197" t="n">
-        <v>0.1194326882841057</v>
+        <v>0.3165718462277189</v>
       </c>
       <c r="C197" t="n">
-        <v>-192.2540838800096</v>
+        <v>-191.004882783144</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45918</v>
+        <v>45926</v>
       </c>
       <c r="B198" t="n">
-        <v>-0.2019651281014698</v>
+        <v>0.4148211636733577</v>
       </c>
       <c r="C198" t="n">
-        <v>314.8995767591004</v>
+        <v>-282.7797054952134</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>45919</v>
+        <v>45929</v>
       </c>
       <c r="B199" t="n">
-        <v>-0.2621330482881801</v>
+        <v>0.4439901465592353</v>
       </c>
       <c r="C199" t="n">
-        <v>417.7682257298188</v>
+        <v>-344.1233301730189</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45922</v>
+        <v>45933</v>
       </c>
       <c r="B200" t="n">
-        <v>-0.1492865119418017</v>
+        <v>0.1145096103415219</v>
       </c>
       <c r="C200" t="n">
-        <v>261.4060418253425</v>
+        <v>-104.7885048335987</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45923</v>
+        <v>45936</v>
       </c>
       <c r="B201" t="n">
-        <v>-0.04414932299484202</v>
+        <v>0.1779289875821676</v>
       </c>
       <c r="C201" t="n">
-        <v>87.940664858585</v>
+        <v>-108.0450723299252</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>45924</v>
+        <v>45937</v>
       </c>
       <c r="B202" t="n">
-        <v>-0.4941451112577341</v>
+        <v>0.1033250972576974</v>
       </c>
       <c r="C202" t="n">
-        <v>837.6490693974207</v>
+        <v>-77.81815556612536</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>45925</v>
+        <v>45938</v>
       </c>
       <c r="B203" t="n">
-        <v>-0.1530942749441769</v>
+        <v>0.2191881666342848</v>
       </c>
       <c r="C203" t="n">
-        <v>250.2155404032273</v>
+        <v>-178.2977836870407</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>45926</v>
+        <v>45939</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.3155635200033899</v>
+        <v>0.05038700185117891</v>
       </c>
       <c r="C204" t="n">
-        <v>594.4666062906042</v>
+        <v>-39.7803126000098</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>45929</v>
+        <v>45940</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.07435369745446668</v>
+        <v>-0.1109649240888639</v>
       </c>
       <c r="C205" t="n">
-        <v>144.7990433581538</v>
+        <v>86.25452140874194</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>45930</v>
+        <v>45943</v>
       </c>
       <c r="B206" t="n">
-        <v>-0.3127129870048886</v>
+        <v>0.001276023638168636</v>
       </c>
       <c r="C206" t="n">
-        <v>533.4005836664434</v>
+        <v>19.54569325518639</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>45931</v>
+        <v>45946</v>
       </c>
       <c r="B207" t="n">
-        <v>-0.2053494840824015</v>
+        <v>-0.1918470319813767</v>
       </c>
       <c r="C207" t="n">
-        <v>365.962678514567</v>
+        <v>151.1276103461009</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>45932</v>
+        <v>45947</v>
       </c>
       <c r="B208" t="n">
-        <v>-0.2588621384485807</v>
+        <v>-0.17036016117713</v>
       </c>
       <c r="C208" t="n">
-        <v>414.9690464942562</v>
+        <v>127.6561258159038</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45933</v>
+        <v>45950</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.09416446102114821</v>
+        <v>0.07543954125775504</v>
       </c>
       <c r="C209" t="n">
-        <v>-53.26183627692828</v>
+        <v>-88.91209839821201</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>45936</v>
+        <v>45951</v>
       </c>
       <c r="B210" t="n">
-        <v>-0.214718463444179</v>
+        <v>-0.2130375737649703</v>
       </c>
       <c r="C210" t="n">
-        <v>340.9709934866206</v>
+        <v>100.491068040862</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>45937</v>
+        <v>45952</v>
       </c>
       <c r="B211" t="n">
-        <v>-0.207048229659546</v>
+        <v>-0.08216265285428904</v>
       </c>
       <c r="C211" t="n">
-        <v>277.817807497627</v>
+        <v>61.88705323124235</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>45938</v>
+        <v>45953</v>
       </c>
       <c r="B212" t="n">
-        <v>-0.2392137047286522</v>
+        <v>-0.04850959286155766</v>
       </c>
       <c r="C212" t="n">
-        <v>349.8339712403977</v>
+        <v>49.83826640551158</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>45939</v>
+        <v>45954</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.1180402826823772</v>
+        <v>0.2708440723453591</v>
       </c>
       <c r="C213" t="n">
-        <v>202.3467190848069</v>
+        <v>-225.2235457872606</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>45940</v>
+        <v>45957</v>
       </c>
       <c r="B214" t="n">
-        <v>0.04733108697251027</v>
+        <v>0.3312682748525806</v>
       </c>
       <c r="C214" t="n">
-        <v>-12.3831536884054</v>
+        <v>-286.7998712477336</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>45943</v>
+        <v>45958</v>
       </c>
       <c r="B215" t="n">
-        <v>-0.2404708261425824</v>
+        <v>0.164514118133591</v>
       </c>
       <c r="C215" t="n">
-        <v>472.4902775840799</v>
+        <v>-96.21122179987172</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>45944</v>
+        <v>45959</v>
       </c>
       <c r="B216" t="n">
-        <v>-0.01949542452847295</v>
+        <v>0.0205718656642806</v>
       </c>
       <c r="C216" t="n">
-        <v>97.42829821943754</v>
+        <v>25.07003184764201</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>45945</v>
+        <v>45960</v>
       </c>
       <c r="B217" t="n">
-        <v>0.1211289791604526</v>
+        <v>0.1034260266545178</v>
       </c>
       <c r="C217" t="n">
-        <v>-114.3428647311893</v>
+        <v>-100.7492517839727</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>45946</v>
+        <v>45961</v>
       </c>
       <c r="B218" t="n">
-        <v>0.1585467567281258</v>
+        <v>-0.06815429478584033</v>
       </c>
       <c r="C218" t="n">
-        <v>-287.8549781698721</v>
+        <v>95.48968116334149</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>45947</v>
+        <v>45964</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.003397723397727973</v>
+        <v>-0.4197771036207523</v>
       </c>
       <c r="C219" t="n">
-        <v>8.269116296407963</v>
+        <v>247.143238953602</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>45950</v>
+        <v>45965</v>
       </c>
       <c r="B220" t="n">
-        <v>-0.05107161727361834</v>
+        <v>-0.2928092267386864</v>
       </c>
       <c r="C220" t="n">
-        <v>120.7928365468442</v>
+        <v>298.532518131626</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>45951</v>
+        <v>45966</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.04165383183316496</v>
+        <v>-0.07832536616840136</v>
       </c>
       <c r="C221" t="n">
-        <v>90.04591031698963</v>
+        <v>77.77115428981602</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>45952</v>
+        <v>45967</v>
       </c>
       <c r="B222" t="n">
-        <v>0.00551132296097021</v>
+        <v>-0.2634263658874615</v>
       </c>
       <c r="C222" t="n">
-        <v>46.40157325926742</v>
+        <v>198.6615974935282</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>45953</v>
+        <v>45968</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.1540253077069443</v>
+        <v>-0.2462006458390427</v>
       </c>
       <c r="C223" t="n">
-        <v>293.2142468503139</v>
+        <v>167.7983443048238</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>45954</v>
+        <v>45971</v>
       </c>
       <c r="B224" t="n">
-        <v>-0.2797734359793893</v>
+        <v>-0.02013682754763457</v>
       </c>
       <c r="C224" t="n">
-        <v>530.6335645464342</v>
+        <v>55.65389069693428</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>45957</v>
+        <v>45972</v>
       </c>
       <c r="B225" t="n">
-        <v>-0.06031030579055199</v>
+        <v>-0.005567631043737161</v>
       </c>
       <c r="C225" t="n">
-        <v>143.2313870855955</v>
+        <v>22.40135994166965</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>45958</v>
+        <v>45973</v>
       </c>
       <c r="B226" t="n">
-        <v>-0.2387569924391744</v>
+        <v>-0.09281811421711722</v>
       </c>
       <c r="C226" t="n">
-        <v>440.5396058413566</v>
+        <v>106.8848978844729</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>45959</v>
+        <v>45974</v>
       </c>
       <c r="B227" t="n">
-        <v>-0.207349189834831</v>
+        <v>-0.2160653235084511</v>
       </c>
       <c r="C227" t="n">
-        <v>365.9719003657344</v>
+        <v>224.7348106938282</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="B228" t="n">
-        <v>-0.4094376152682719</v>
+        <v>-0.2760265179385705</v>
       </c>
       <c r="C228" t="n">
-        <v>675.5315280530951</v>
+        <v>177.1730555901055</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45961</v>
+        <v>45978</v>
       </c>
       <c r="B229" t="n">
-        <v>-0.3317842320012797</v>
+        <v>-0.2951987907922688</v>
       </c>
       <c r="C229" t="n">
-        <v>602.6379973981457</v>
+        <v>262.2386972930843</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>45964</v>
+        <v>45979</v>
       </c>
       <c r="B230" t="n">
-        <v>-0.3466155226505833</v>
+        <v>-0.2623507915136254</v>
       </c>
       <c r="C230" t="n">
-        <v>613.931152464822</v>
+        <v>249.7934589712856</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>45965</v>
+        <v>45980</v>
       </c>
       <c r="B231" t="n">
-        <v>-0.3909710268861553</v>
+        <v>-0.2120138631904541</v>
       </c>
       <c r="C231" t="n">
-        <v>550.4064676596976</v>
+        <v>203.1224284364415</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>45966</v>
+        <v>45981</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.2230011270509072</v>
+        <v>-0.4630991319898735</v>
       </c>
       <c r="C232" t="n">
-        <v>436.4097479446803</v>
+        <v>369.3738441439997</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>45967</v>
+        <v>45982</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.2455543835147191</v>
+        <v>-0.5633894381133256</v>
       </c>
       <c r="C233" t="n">
-        <v>355.343039286819</v>
+        <v>372.5922637665363</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>45968</v>
+        <v>45985</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.1872841219627767</v>
+        <v>-0.3445923290002894</v>
       </c>
       <c r="C234" t="n">
-        <v>354.8967638055949</v>
+        <v>217.2053934624423</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>45971</v>
+        <v>45987</v>
       </c>
       <c r="B235" t="n">
-        <v>-0.1487595383565499</v>
+        <v>-0.2871260957182097</v>
       </c>
       <c r="C235" t="n">
-        <v>203.3041884923348</v>
+        <v>204.4210113507871</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>45972</v>
+        <v>45988</v>
       </c>
       <c r="B236" t="n">
-        <v>-0.04047761743818878</v>
+        <v>-0.01313795320505007</v>
       </c>
       <c r="C236" t="n">
-        <v>136.9765079923555</v>
+        <v>12.75696843232256</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45973</v>
+        <v>45989</v>
       </c>
       <c r="B237" t="n">
-        <v>-0.1635495720455494</v>
+        <v>-0.1673704032042381</v>
       </c>
       <c r="C237" t="n">
-        <v>238.2560274902198</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="B238" t="n">
-        <v>0.07298764712649584</v>
-      </c>
-      <c r="C238" t="n">
-        <v>-147.9305505633409</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="n">
-        <v>45975</v>
-      </c>
-      <c r="B239" t="n">
-        <v>0.07680676590881344</v>
-      </c>
-      <c r="C239" t="n">
-        <v>-66.99389146799919</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="B240" t="n">
-        <v>-0.04170936343949316</v>
-      </c>
-      <c r="C240" t="n">
-        <v>129.054477368779</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="n">
-        <v>45979</v>
-      </c>
-      <c r="B241" t="n">
-        <v>-0.143430327010257</v>
-      </c>
-      <c r="C241" t="n">
-        <v>325.6697847339925</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="n">
-        <v>45980</v>
-      </c>
-      <c r="B242" t="n">
-        <v>-0.2287794128571413</v>
-      </c>
-      <c r="C242" t="n">
-        <v>207.0193465273334</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="n">
-        <v>45982</v>
-      </c>
-      <c r="B243" t="n">
-        <v>-0.0133135174521691</v>
-      </c>
-      <c r="C243" t="n">
-        <v>103.2858155048812</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="n">
-        <v>45985</v>
-      </c>
-      <c r="B244" t="n">
-        <v>-0.2606018007689596</v>
-      </c>
-      <c r="C244" t="n">
-        <v>403.4916205678089</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="n">
-        <v>45986</v>
-      </c>
-      <c r="B245" t="n">
-        <v>-0.1045848674549458</v>
-      </c>
-      <c r="C245" t="n">
-        <v>196.2405528950914</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="1" t="n">
-        <v>45987</v>
-      </c>
-      <c r="B246" t="n">
-        <v>-0.1682912588440969</v>
-      </c>
-      <c r="C246" t="n">
-        <v>161.6902565655133</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="B247" t="n">
-        <v>-0.5578121145619934</v>
-      </c>
-      <c r="C247" t="n">
-        <v>955.6482897836734</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="n">
-        <v>45989</v>
-      </c>
-      <c r="B248" t="n">
-        <v>-0.2557828600675879</v>
-      </c>
-      <c r="C248" t="n">
-        <v>490.0117626815207</v>
+        <v>140.3803484035454</v>
       </c>
     </row>
   </sheetData>
